--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="READ ME - Coverage &amp; Honesty" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Live Compare DUAL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Staging Live Grid" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Production Live Grid" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Send to Terminal LIVE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Live Compare DUAL" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Staging Live Grid" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Production Live Grid" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -510,9 +511,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -534,9 +533,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
@@ -586,9 +583,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -652,9 +647,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
@@ -683,9 +676,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
@@ -728,9 +719,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
@@ -744,6 +733,424 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SEND TO TERMINAL — LIVE OBSERVED (staging). MAJOR CORRECTION: the control EXISTS in the build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Prior workbook claimed "no Send to Terminal control anywhere in the staging build" (from a source grep).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LIVE: it is the blue "Send to Terminal" button in the New Customer Payment dialog on an invoiced WO with a balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>(Finance tab -&gt; New Payment). Screenshot: live-ui-2026-07-15/staging/Admin/SendToTerminal_dialog.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Staging Role</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Send to Terminal (observed)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Path observed</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Screenshot</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>invoiced WO -&gt; Finance -&gt; New Payment dialog</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Admin/SendToTerminal_dialog.png</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod ST not driven yet)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>invoiced WO -&gt; Finance -&gt; New Payment dialog</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Parts_Manager/SendToTerminal_dialog.png</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod ST not driven yet)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>invoiced WO -&gt; Finance -&gt; New Payment dialog</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Senior_Service_Advisor/SendToTerminal_dialog.png</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod ST not driven yet)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>hidden (no New Payment - no Finance/invoicing access)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>invoiced WO -&gt; Finance -&gt; New Payment dialog</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Technician/SendToTerminal_finance.png</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod ST not driven yet)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>hidden (no New Payment - no Finance/invoicing access)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>invoiced WO -&gt; Finance -&gt; New Payment dialog</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Sales_Representative/SendToTerminal_finance.png</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod ST not driven yet)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (invoiced WO did not render for this role)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>invoiced WO -&gt; Finance -&gt; New Payment dialog</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Office_User/SendToTerminal_finance.png</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod ST not driven yet)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (invoiced WO did not render for this role)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>invoiced WO -&gt; Finance -&gt; New Payment dialog</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Time_Clock_User/SendToTerminal_finance.png</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod ST not driven yet)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>staff/change role-swap blocked by org-context 403 this session</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>staff/change role-swap blocked by org-context 403 this session</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>staff/change role-swap blocked by org-context 403 this session</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>staff/change role-swap blocked by org-context 403 this session</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8261,7 +8668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8889,7 +9296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -511,7 +511,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -533,7 +532,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
@@ -583,7 +581,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -647,7 +644,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
@@ -676,7 +672,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
@@ -719,7 +714,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
@@ -738,145 +732,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SEND TO TERMINAL — LIVE OBSERVED (staging). MAJOR CORRECTION: the control EXISTS in the build.</t>
+          <t>SEND TO TERMINAL — LIVE OBSERVED (both envs). The control EXISTS in the build (prior "not in build" was WRONG).</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Prior workbook claimed "no Send to Terminal control anywhere in the staging build" (from a source grep).</t>
+          <t>It is the blue "Send to Terminal" button in the New Customer Payment dialog (invoiced WO w/ balance -&gt; Finance -&gt; New Payment).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LIVE: it is the blue "Send to Terminal" button in the New Customer Payment dialog on an invoiced WO with a balance</t>
+          <t>KEY: its APPEARANCE is ORG-CONFIG gated (whether a card terminal is set up), not a role/build difference. Staging org</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>(Finance tab -&gt; New Payment). Screenshot: live-ui-2026-07-15/staging/Admin/SendToTerminal_dialog.png</t>
+          <t>"Staging Heavy Duty - 9919" HAS a terminal (button shows); prod test org "Truck Hill 1" has NONE (button absent for all).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Whether a role can even OPEN New Payment is role-gated (invoicing-create + Finance access).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Staging Role</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Send to Terminal (observed)</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Path observed</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Screenshot</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Prod</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Verdict</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Evidence: staging Admin/Parts_Manager/Senior_Service_Advisor/*/SendToTerminal_dialog.png; production/*/SendToTerminal_dialog.png</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>invoiced WO -&gt; Finance -&gt; New Payment dialog</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/staging/Admin/SendToTerminal_dialog.png</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod ST not driven yet)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod pending)</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>invoiced WO -&gt; Finance -&gt; New Payment dialog</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/staging/Parts_Manager/SendToTerminal_dialog.png</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod ST not driven yet)</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod pending)</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>STAGING Send to Terminal (observed)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>PROD Send to Terminal (observed)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Dual verdict</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Senior Service Advisor</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -884,264 +825,289 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>invoiced WO -&gt; Finance -&gt; New Payment dialog</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/staging/Senior_Service_Advisor/SendToTerminal_dialog.png</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod ST not driven yet)</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod pending)</t>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>hidden (New Payment present, NO Send to Terminal button - org has no terminal)</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE (staging has terminal)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>hidden (no New Payment - no Finance/invoicing access)</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>invoiced WO -&gt; Finance -&gt; New Payment dialog</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/staging/Technician/SendToTerminal_finance.png</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod ST not driven yet)</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod pending)</t>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (not observed this session)</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>hidden (no New Payment - no invoicing/finance path)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>hidden (no New Payment - no Finance/invoicing access)</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>invoiced WO -&gt; Finance -&gt; New Payment dialog</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/staging/Sales_Representative/SendToTerminal_finance.png</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod ST not driven yet)</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod pending)</t>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod role not observed this session)</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (invoiced WO did not render for this role)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>invoiced WO -&gt; Finance -&gt; New Payment dialog</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/staging/Office_User/SendToTerminal_finance.png</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod ST not driven yet)</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod pending)</t>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod role not observed this session)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (not observed this session)</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod role not observed this session)</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (not observed this session)</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod role not observed this session)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (invoiced WO did not render for this role)</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod role not observed this session)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (not observed this session)</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod role not observed this session)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>hidden (no New Payment - no Finance/invoicing access)</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod role not observed this session)</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>hidden (no New Payment - no Finance/invoicing access)</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>hidden (no New Payment - no invoicing/finance path)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>MATCH (neither shows)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>Time Clock User</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>NOT VERIFIED (invoiced WO did not render for this role)</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>invoiced WO -&gt; Finance -&gt; New Payment dialog</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/staging/Time_Clock_User/SendToTerminal_finance.png</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod ST not driven yet)</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>staff/change role-swap blocked by org-context 403 this session</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>staff/change role-swap blocked by org-context 403 this session</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>staff/change role-swap blocked by org-context 403 this session</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>staff/change role-swap blocked by org-context 403 this session</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr"/>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod role not observed this session)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
         </is>
       </c>
     </row>

--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -732,14 +732,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -752,72 +751,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>It is the blue "Send to Terminal" button in the New Customer Payment dialog (invoiced WO w/ balance -&gt; Finance -&gt; New Payment).</t>
+          <t>Blue "Send to Terminal" button in the New Customer Payment dialog (invoiced WO w/ balance -&gt; Finance -&gt; New Payment).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KEY: its APPEARANCE is ORG-CONFIG gated (whether a card terminal is set up), not a role/build difference. Staging org</t>
+          <t>KEY: appearance is ORG-CONFIG gated (card terminal set up?), not role/build. Staging "Staging Heavy Duty - 9919" HAS a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>"Staging Heavy Duty - 9919" HAS a terminal (button shows); prod test org "Truck Hill 1" has NONE (button absent for all).</t>
+          <t>terminal (button shows for invoicing roles); prod test org "Truck Hill 1" has NONE (button absent for all prod roles).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Whether a role can even OPEN New Payment is role-gated (invoicing-create + Finance access).</t>
+          <t>Opening New Payment at all is role-gated (invoicing-create + Finance access). Evidence: staging &amp; production /*/SendToTerminal_dialog.png</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Evidence: staging Admin/Parts_Manager/Senior_Service_Advisor/*/SendToTerminal_dialog.png; production/*/SendToTerminal_dialog.png</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>STAGING Send to Terminal (observed)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>PROD Send to Terminal (observed)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Dual verdict</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>STAGING Send to Terminal (observed)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>PROD Send to Terminal (observed)</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Dual verdict</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>hidden (New Payment present, NO Send to Terminal button - org has no terminal)</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE (staging org has terminal)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -827,51 +836,41 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>hidden (New Payment present, NO Send to Terminal button - org has no terminal)</t>
+          <t>hidden (no New Payment - no invoicing/finance path)</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>STAGING-MORE (staging has terminal)</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
+          <t>STAGING-MORE (staging org has terminal)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (not observed this session)</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>hidden (no New Payment - no invoicing/finance path)</t>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod role not observed this session)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
           <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Senior Service Advisor</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -887,18 +886,13 @@
       <c r="D11" s="7" t="inlineStr">
         <is>
           <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -914,23 +908,18 @@
       <c r="D12" s="7" t="inlineStr">
         <is>
           <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>NOT VERIFIED (not observed this session)</t>
+          <t>NOT VERIFIED (not observed)</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -941,23 +930,18 @@
       <c r="D13" s="7" t="inlineStr">
         <is>
           <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>NOT VERIFIED (not observed this session)</t>
+          <t>NOT VERIFIED (invoiced WO did not render for this role/org)</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -968,23 +952,18 @@
       <c r="D14" s="7" t="inlineStr">
         <is>
           <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>NOT VERIFIED (invoiced WO did not render for this role)</t>
+          <t>NOT VERIFIED (not observed)</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -995,23 +974,18 @@
       <c r="D15" s="7" t="inlineStr">
         <is>
           <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (not observed this session)</t>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>hidden (no New Payment - no Finance/invoicing access)</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1022,18 +996,13 @@
       <c r="D16" s="7" t="inlineStr">
         <is>
           <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1041,73 +1010,36 @@
           <t>hidden (no New Payment - no Finance/invoicing access)</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod role not observed this session)</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>hidden (no New Payment - no invoicing/finance path)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>MATCH (neither shows)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>hidden (no New Payment - no Finance/invoicing access)</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>hidden (no New Payment - no invoicing/finance path)</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>MATCH (neither shows)</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
           <t>Time Clock User</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (invoiced WO did not render for this role)</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (invoiced WO did not render for this role/org)</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>NOT VERIFIED (prod role not observed this session)</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>prod=Truck Hill org (no terminal); staging=Heavy Duty org (terminal configured)</t>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
     </row>

--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="READ ME - Coverage &amp; Honesty" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Send to Terminal LIVE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Live Compare DUAL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Staging Live Grid" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Production Live Grid" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Full Dual Matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Send to Terminal LIVE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Live Compare DUAL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Staging Live Grid" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Production Live Grid" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,6 +733,3146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G89"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Staging Role</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Prod role</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Capability</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>PROD</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>STAGING</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Caveat</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment btn)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment btn)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment btn)</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment btn)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment btn)</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment btn)</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment btn)</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment btn)</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment btn)</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment btn)</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment btn)</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -776,9 +3917,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -1048,7 +4187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8566,7 +11705,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9194,7 +12333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -733,16 +733,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -815,7 +815,7 @@
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
+          <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment btn)</t>
+          <t>Invoicing/Finance view (Finance tab)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -977,16 +977,12 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
-        </is>
-      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1001,12 +997,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1014,14 +1010,14 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+          <t>ORG-terminal gated: prod none, staging has one</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1034,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
+          <t>WO-level History (History tab)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1046,36 +1042,32 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>STAGING-LESS</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
-        </is>
-      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
+          <t>Order Parts area (Parts tab)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1093,26 +1085,22 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
-        </is>
-      </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
+          <t>WO Notes (Notes tab)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1135,17 +1123,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
+          <t>Timesheets (tab)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1168,93 +1156,101 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr"/>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment btn)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr"/>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
+          <t>Change Asset on WO</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1264,34 +1260,34 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
+          <t>WO Delete</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1301,7 +1297,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1314,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
+          <t>Send to Portal</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1326,36 +1322,36 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>STAGING-LESS</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
+          <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
+          <t>Create/Edit WO Lines (New Line)</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1373,26 +1369,22 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
-        </is>
-      </c>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
+          <t>Review Work Orders (Reviewed)</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1415,17 +1407,17 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
+          <t>See Financial Data (Rate/Margin)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1448,17 +1440,17 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
+          <t>Invoicing/Finance view (Finance tab)</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1481,17 +1473,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment btn)</t>
+          <t>Take Payment (New Payment)</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1514,12 +1506,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1529,7 +1521,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>NOT VERIFIED</t>
+          <t>N/V</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1544,29 +1536,29 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+          <t>ORG-terminal gated: prod none, staging has one</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1574,31 +1566,27 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
-        </is>
-      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Senior Service Advisor (+SA Technician,+SA No Reports)</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
+          <t>Order Parts area (Parts tab)</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1606,36 +1594,32 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>STAGING-LESS</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
-        </is>
-      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>SA Limited View</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
+          <t>WO Notes (Notes tab)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1653,26 +1637,22 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
-        </is>
-      </c>
+      <c r="G26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>SA Limited View</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
+          <t>Timesheets (tab)</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1695,158 +1675,170 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>SA Limited View</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>SA Limited View</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr"/>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>SA Limited View</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment btn)</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr"/>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>SA Limited View</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
           <t>Service Advisor</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>SA Limited View</t>
-        </is>
-      </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1854,31 +1846,31 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+          <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
           <t>Service Advisor</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>SA Limited View</t>
-        </is>
-      </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
+          <t>Create/Edit WO Lines (New Line)</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -1886,36 +1878,32 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>STAGING-LESS</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
-        </is>
-      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
+          <t>Review Work Orders (Reviewed)</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1933,26 +1921,22 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
-        </is>
-      </c>
+      <c r="G34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
+          <t>See Financial Data (Rate/Margin)</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1975,17 +1959,17 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
+          <t>Invoicing/Finance view (Finance tab)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -2008,22 +1992,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2031,9 +2015,9 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
@@ -2041,22 +2025,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment btn)</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -2064,69 +2048,69 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr"/>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>ORG-terminal gated: prod none, staging has one</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
-        </is>
-      </c>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -2134,31 +2118,27 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
-        </is>
-      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
+          <t>WO Notes (Notes tab)</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -2166,36 +2146,32 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>STAGING-LESS</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
-        </is>
-      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
+          <t>Timesheets (tab)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -2203,145 +2179,153 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>STAGING-LESS</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
-        </is>
-      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr"/>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr"/>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr"/>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment btn)</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>NOT VERIFIED</t>
+          <t>N/V*</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -2349,64 +2333,68 @@
           <t>NOT VERIFIED</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E47" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
+          <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -2414,31 +2402,27 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
-        </is>
-      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
+          <t>Review Work Orders (Reviewed)</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -2446,36 +2430,32 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>STAGING-LESS</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
-        </is>
-      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
+          <t>See Financial Data (Rate/Margin)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -2493,26 +2473,22 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
-        </is>
-      </c>
+      <c r="G50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
+          <t>Invoicing/Finance view (Finance tab)</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -2535,22 +2511,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -2558,9 +2534,9 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr"/>
@@ -2568,22 +2544,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2591,32 +2567,36 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr"/>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>ORG-terminal gated: prod none, staging has one</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment btn)</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2624,9 +2604,9 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
@@ -2634,22 +2614,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2657,36 +2637,32 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
-        </is>
-      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2694,31 +2670,27 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
-        </is>
-      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
+          <t>Timesheets (tab)</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2726,177 +2698,185 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>STAGING-LESS</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
-        </is>
-      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>STAGING-LESS</t>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
+          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>STAGING-LESS</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr"/>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr"/>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr"/>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment btn)</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2904,69 +2884,69 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr"/>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
-        </is>
-      </c>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D64" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2974,31 +2954,27 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
-        </is>
-      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
+          <t>See Financial Data (Rate/Margin)</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -3006,46 +2982,42 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>STAGING-LESS</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
-        </is>
-      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Invoicing/Finance view (Finance tab)</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -3053,26 +3025,22 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
-        </is>
-      </c>
+      <c r="G66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
+          <t>Take Payment (New Payment)</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -3080,14 +3048,14 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
@@ -3095,55 +3063,59 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr"/>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>ORG-terminal gated: prod none, staging has one</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -3151,9 +3123,9 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr"/>
@@ -3161,27 +3133,27 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment btn)</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -3194,59 +3166,55 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E71" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
-        </is>
-      </c>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -3254,171 +3222,175 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
-        </is>
-      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
+          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>STAGING-LESS</t>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr"/>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr"/>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
+          <t>Send to Portal</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -3426,37 +3398,41 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr"/>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment btn)</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -3464,9 +3440,9 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr"/>
@@ -3474,22 +3450,22 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -3497,68 +3473,60 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
-        </is>
-      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D80" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
-        </is>
-      </c>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
+          <t>Invoicing/Finance view (Finance tab)</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -3576,26 +3544,22 @@
           <t>STAGING-LESS</t>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
-        </is>
-      </c>
+      <c r="G81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
+          <t>Take Payment (New Payment)</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
@@ -3603,84 +3567,84 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>prod portal is org-customer-portal-config gated (Truck Hill has it broadly)</t>
-        </is>
-      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr"/>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>ORG-terminal gated: prod none, staging has one</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr"/>
@@ -3688,32 +3652,32 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
-        </is>
-      </c>
-      <c r="D85" s="8" t="inlineStr">
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr"/>
@@ -3721,32 +3685,32 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment btn)</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E86" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr"/>
@@ -3754,49 +3718,45 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D87" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E87" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>ORG-CONFIG gated: prod Truck Hill has NO terminal; staging Heavy Duty HAS one</t>
-        </is>
-      </c>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -3806,12 +3766,12 @@
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -3821,44 +3781,2713 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>prod line menu showed only Move (state-dep); staging showed Return</t>
+          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Invoicing/Finance view (Finance tab)</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>ORG-terminal gated: prod none, staging has one</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E106" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Invoicing/Finance view (Finance tab)</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>ORG-terminal gated: prod none, staging has one</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E118" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E119" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E120" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Invoicing/Finance view (Finance tab)</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="E128" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>ORG-terminal gated: prod none, staging has one</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E130" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E132" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E133" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E134" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E135" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (+Reporting)</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E136" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E138" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E139" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>Invoicing/Finance view (Finance tab)</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D142" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>ORG-terminal gated: prod none, staging has one</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D148" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E148" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E149" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D150" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E150" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D151" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E151" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
           <t>Time Clock User</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B152" s="5" t="inlineStr">
         <is>
           <t>Time Clock User</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E152" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E153" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E154" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E155" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>Invoicing/Finance view (Finance tab)</t>
+        </is>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G156" s="5" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D157" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E157" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="E158" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>ORG-terminal gated: prod none, staging has one</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D159" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E159" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E160" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D161" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F161" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D162" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F162" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>Part Return (line Return action)</t>
+        </is>
+      </c>
+      <c r="D163" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E163" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E164" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D165" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E165" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>capture inconsistent across roles - needs targeted re-observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
         <is>
           <t>WO Delete</t>
         </is>
       </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent (deletable only w/o invoice) - confounded this pass</t>
+      <c r="D166" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E166" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
         </is>
       </c>
     </row>
@@ -3917,7 +6546,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>

--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -733,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G166"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
+          <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
     </row>
@@ -1206,26 +1206,22 @@
           <t>Change Customer on WO</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1243,26 +1239,22 @@
           <t>Change Asset on WO</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1277,7 +1269,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
+          <t>Approve line</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -1297,44 +1289,44 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Service Manager</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+          <t>Decline line</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>prod portal org-customer-portal gated</t>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1343,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
+          <t>Send to Portal</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1369,7 +1361,11 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1384,7 +1380,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
+          <t>Create/Edit WO Lines (New Line)</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1417,7 +1413,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
+          <t>Review Work Orders (Reviewed)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1450,7 +1446,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Invoicing/Finance view (Finance tab)</t>
+          <t>See Financial Data (Rate/Margin)</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1483,12 +1479,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment)</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Invoicing/Finance view (Finance tab)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1496,9 +1492,9 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
@@ -1516,12 +1512,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>N/V</t>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1529,16 +1525,12 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>ORG-terminal gated: prod none, staging has one</t>
-        </is>
-      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1553,12 +1545,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>WO-level History (History tab)</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1566,12 +1558,16 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>ORG-terminal gated: prod none, staging has one</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1586,7 +1582,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Order Parts area (Parts tab)</t>
+          <t>WO-level History (History tab)</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1619,7 +1615,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>WO Notes (Notes tab)</t>
+          <t>Order Parts area (Parts tab)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1652,7 +1648,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Timesheets (tab)</t>
+          <t>WO Notes (Notes tab)</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1685,29 +1681,25 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
-        </is>
-      </c>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1722,27 +1714,27 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Change Customer on WO</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
+          <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
     </row>
@@ -1759,29 +1751,25 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Change Asset on WO</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1796,99 +1784,99 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
-        </is>
-      </c>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+          <t>Approve line</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>prod portal org-customer-portal gated</t>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Service Advisor</t>
+          <t>Service Manager</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr"/>
+          <t>Decline line</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1903,7 +1891,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
+          <t>Send to Portal</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1921,7 +1909,11 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -1936,7 +1928,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
+          <t>Create/Edit WO Lines (New Line)</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1969,7 +1961,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Invoicing/Finance view (Finance tab)</t>
+          <t>Review Work Orders (Reviewed)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -2002,12 +1994,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment)</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2015,9 +2007,9 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
@@ -2035,12 +2027,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>N/V</t>
+          <t>Invoicing/Finance view (Finance tab)</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -2048,16 +2040,12 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>ORG-terminal gated: prod none, staging has one</t>
-        </is>
-      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -2072,12 +2060,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>WO-level History (History tab)</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -2085,9 +2073,9 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
@@ -2105,12 +2093,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Order Parts area (Parts tab)</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -2118,12 +2106,16 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr"/>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>ORG-terminal gated: prod none, staging has one</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -2138,7 +2130,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>WO Notes (Notes tab)</t>
+          <t>WO-level History (History tab)</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -2171,7 +2163,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Timesheets (tab)</t>
+          <t>Order Parts area (Parts tab)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -2204,29 +2196,25 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
-        </is>
-      </c>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -2241,29 +2229,25 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Change Customer on WO</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -2278,27 +2262,27 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Change Asset on WO</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
+          <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
     </row>
@@ -2315,44 +2299,40 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
-        </is>
-      </c>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
           <t>Service Advisor</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>SA Limited View</t>
-        </is>
-      </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
+          <t>Change Asset on WO</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -2370,77 +2350,81 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>prod portal org-customer-portal gated</t>
-        </is>
-      </c>
+      <c r="G47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
           <t>Service Advisor</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>SA Limited View</t>
-        </is>
-      </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr"/>
+          <t>Approve line</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
+          <t>Senior Service Advisor (+SA Tech,+SA NoRep)</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
           <t>Service Advisor</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>SA Limited View</t>
-        </is>
-      </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr"/>
+          <t>Decline line</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -2455,7 +2439,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
+          <t>Send to Portal</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -2473,7 +2457,11 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -2488,7 +2476,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Invoicing/Finance view (Finance tab)</t>
+          <t>Create/Edit WO Lines (New Line)</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -2521,7 +2509,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment)</t>
+          <t>Review Work Orders (Reviewed)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -2554,12 +2542,12 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2567,16 +2555,12 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>ORG-terminal gated: prod none, staging has one</t>
-        </is>
-      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -2591,7 +2575,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>WO-level History (History tab)</t>
+          <t>Invoicing/Finance view (Finance tab)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2624,7 +2608,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Order Parts area (Parts tab)</t>
+          <t>Take Payment (New Payment)</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2657,12 +2641,12 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>WO Notes (Notes tab)</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2670,12 +2654,16 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr"/>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>ORG-terminal gated: prod none, staging has one</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -2690,7 +2678,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Timesheets (tab)</t>
+          <t>WO-level History (History tab)</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2723,29 +2711,25 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
-        </is>
-      </c>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -2760,29 +2744,25 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Change Customer on WO</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E59" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -2797,29 +2777,25 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Change Asset on WO</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -2837,41 +2813,41 @@
           <t>WO Delete</t>
         </is>
       </c>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>NOT VERIFIED</t>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
+          <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
+          <t>Change Customer on WO</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2889,26 +2865,22 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>prod portal org-customer-portal gated</t>
-        </is>
-      </c>
+      <c r="G62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
+          <t>Change Asset on WO</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2931,68 +2903,76 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr"/>
+          <t>Approve line</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Foreman</t>
+          <t>SA Limited View</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr"/>
+          <t>Decline line</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -3007,7 +2987,7 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Invoicing/Finance view (Finance tab)</t>
+          <t>Send to Portal</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -3025,7 +3005,11 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr"/>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -3040,12 +3024,12 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment)</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -3053,9 +3037,9 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
@@ -3073,29 +3057,25 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>N/V</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>ORG-terminal gated: prod none, staging has one</t>
-        </is>
-      </c>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -3110,7 +3090,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>WO-level History (History tab)</t>
+          <t>See Financial Data (Rate/Margin)</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -3143,7 +3123,7 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Order Parts area (Parts tab)</t>
+          <t>Invoicing/Finance view (Finance tab)</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -3176,12 +3156,12 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>WO Notes (Notes tab)</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -3189,9 +3169,9 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr"/>
@@ -3209,25 +3189,29 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Timesheets (tab)</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr"/>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>ORG-terminal gated: prod none, staging has one</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -3242,29 +3226,25 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D73" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E73" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
-        </is>
-      </c>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -3279,29 +3259,25 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Change Customer on WO</t>
-        </is>
-      </c>
-      <c r="D74" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -3316,29 +3292,25 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Change Asset on WO</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E75" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -3353,44 +3325,40 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
-        </is>
-      </c>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
+          <t>WO Delete</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -3410,24 +3378,24 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>prod portal org-customer-portal gated</t>
+          <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
+          <t>Change Customer on WO</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -3450,27 +3418,27 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -3483,68 +3451,76 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr"/>
+          <t>Approve line</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>Foreman</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Invoicing/Finance view (Finance tab)</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Decline line</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>STAGING-LESS</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr"/>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -3559,25 +3535,29 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment)</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E82" s="10" t="inlineStr">
-        <is>
-          <t>N/V</t>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr"/>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -3592,29 +3572,25 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="inlineStr">
-        <is>
-          <t>N/V</t>
-        </is>
-      </c>
-      <c r="E83" s="10" t="inlineStr">
-        <is>
-          <t>N/V</t>
-        </is>
-      </c>
-      <c r="F83" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>ORG-terminal gated: prod none, staging has one</t>
-        </is>
-      </c>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -3629,12 +3605,12 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>WO-level History (History tab)</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -3642,9 +3618,9 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="F84" s="7" t="inlineStr">
-        <is>
-          <t>STAGING-LESS</t>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr"/>
@@ -3662,12 +3638,12 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Order Parts area (Parts tab)</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -3675,9 +3651,9 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr">
-        <is>
-          <t>STAGING-LESS</t>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr"/>
@@ -3695,7 +3671,7 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>WO Notes (Notes tab)</t>
+          <t>Invoicing/Finance view (Finance tab)</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -3703,14 +3679,14 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr"/>
@@ -3728,22 +3704,22 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Timesheets (tab)</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>STAGING-LESS</t>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr"/>
@@ -3761,17 +3737,17 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
+          <t>Send to Terminal</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>N/V*</t>
+          <t>N/V</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>N/V*</t>
+          <t>N/V</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -3781,7 +3757,7 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
+          <t>ORG-terminal gated: prod none, staging has one</t>
         </is>
       </c>
     </row>
@@ -3798,29 +3774,25 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Change Customer on WO</t>
-        </is>
-      </c>
-      <c r="D89" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E89" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -3835,29 +3807,25 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Change Asset on WO</t>
-        </is>
-      </c>
-      <c r="D90" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E90" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -3872,44 +3840,40 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
-        </is>
-      </c>
-      <c r="D91" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E91" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
-        </is>
-      </c>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
+          <t>Timesheets (tab)</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -3917,36 +3881,32 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>prod portal org-customer-portal gated</t>
-        </is>
-      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
+          <t>WO Delete</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -3954,47 +3914,51 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr"/>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>observed on estimate WO (deletable state)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
-        </is>
-      </c>
-      <c r="D94" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr"/>
@@ -4002,17 +3966,17 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
+          <t>Change Asset on WO</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -4020,14 +3984,14 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr"/>
@@ -4035,68 +3999,76 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Invoicing/Finance view (Finance tab)</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr"/>
+          <t>Approve line</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Parts Manager</t>
+          <t>Technician</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment)</t>
-        </is>
-      </c>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr"/>
+          <t>Decline line</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -4111,12 +4083,12 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D98" s="10" t="inlineStr">
-        <is>
-          <t>N/V</t>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -4124,14 +4096,14 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>ORG-terminal gated: prod none, staging has one</t>
+          <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4120,7 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>WO-level History (History tab)</t>
+          <t>Create/Edit WO Lines (New Line)</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -4181,12 +4153,12 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Order Parts area (Parts tab)</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -4194,9 +4166,9 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr"/>
@@ -4214,7 +4186,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>WO Notes (Notes tab)</t>
+          <t>See Financial Data (Rate/Margin)</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -4247,7 +4219,7 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Timesheets (tab)</t>
+          <t>Invoicing/Finance view (Finance tab)</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -4255,14 +4227,14 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>STAGING-LESS</t>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr"/>
@@ -4280,29 +4252,25 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D103" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E103" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
-        </is>
-      </c>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -4317,17 +4285,17 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Change Customer on WO</t>
+          <t>Send to Terminal</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E104" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
@@ -4337,7 +4305,7 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
+          <t>ORG-terminal gated: prod none, staging has one</t>
         </is>
       </c>
     </row>
@@ -4354,29 +4322,25 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Change Asset on WO</t>
-        </is>
-      </c>
-      <c r="D105" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E105" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -4391,44 +4355,40 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
-        </is>
-      </c>
-      <c r="D106" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E106" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F106" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
-        </is>
-      </c>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
+          <t>WO Notes (Notes tab)</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -4436,36 +4396,32 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E107" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>STAGING-LESS</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>prod portal org-customer-portal gated</t>
-        </is>
-      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
+          <t>Timesheets (tab)</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -4488,17 +4444,17 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
+          <t>WO Delete</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
@@ -4516,27 +4472,31 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G109" s="5" t="inlineStr"/>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>observed on estimate WO (deletable state)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -4544,9 +4504,9 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F110" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr"/>
@@ -4554,22 +4514,22 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Invoicing/Finance view (Finance tab)</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -4577,9 +4537,9 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="F111" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr"/>
@@ -4587,60 +4547,64 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment)</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F112" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
-        </is>
-      </c>
-      <c r="G112" s="5" t="inlineStr"/>
+          <t>Approve line</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E112" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Parts Technician</t>
+          <t>Parts Manager</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
+          <t>Decline line</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>N/V</t>
-        </is>
-      </c>
-      <c r="E113" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
@@ -4650,7 +4614,7 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>ORG-terminal gated: prod none, staging has one</t>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4631,7 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>WO-level History (History tab)</t>
+          <t>Send to Portal</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
@@ -4685,7 +4649,11 @@
           <t>STAGING-LESS</t>
         </is>
       </c>
-      <c r="G114" s="5" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -4700,7 +4668,7 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Order Parts area (Parts tab)</t>
+          <t>Create/Edit WO Lines (New Line)</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -4708,14 +4676,14 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F115" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr"/>
@@ -4733,17 +4701,17 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>WO Notes (Notes tab)</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
@@ -4766,7 +4734,7 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Timesheets (tab)</t>
+          <t>See Financial Data (Rate/Margin)</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
@@ -4799,29 +4767,25 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D118" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E118" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F118" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
-        </is>
-      </c>
+          <t>Invoicing/Finance view (Finance tab)</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -4836,29 +4800,25 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Change Customer on WO</t>
-        </is>
-      </c>
-      <c r="D119" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E119" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F119" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -4873,17 +4833,17 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Change Asset on WO</t>
+          <t>Send to Terminal</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E120" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
@@ -4893,7 +4853,7 @@
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
+          <t>ORG-terminal gated: prod none, staging has one</t>
         </is>
       </c>
     </row>
@@ -4910,54 +4870,50 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
-        </is>
-      </c>
-      <c r="D121" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E121" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
-        </is>
-      </c>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
-        </is>
-      </c>
-      <c r="D122" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E122" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
@@ -4965,36 +4921,32 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>prod portal org-customer-portal gated</t>
-        </is>
-      </c>
+      <c r="G122" s="5" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
-        </is>
-      </c>
-      <c r="D123" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E123" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
@@ -5007,27 +4959,27 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
-        </is>
-      </c>
-      <c r="D124" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E124" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
@@ -5040,17 +4992,17 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
+          <t>WO Delete</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
@@ -5058,32 +5010,36 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F125" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="inlineStr"/>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>observed on estimate WO (deletable state)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Invoicing/Finance view (Finance tab)</t>
+          <t>Change Customer on WO</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
@@ -5106,17 +5062,17 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment)</t>
+          <t>Change Asset on WO</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
@@ -5139,27 +5095,27 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
+          <t>Approve line</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>N/V</t>
+          <t>N/V*</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>N/V</t>
+          <t>N/V*</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
@@ -5169,42 +5125,46 @@
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>ORG-terminal gated: prod none, staging has one</t>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative (+Reporting)</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Parts Technician</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>WO-level History (History tab)</t>
-        </is>
-      </c>
-      <c r="D129" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E129" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F129" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G129" s="5" t="inlineStr"/>
+          <t>Decline line</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E129" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -5219,7 +5179,7 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Order Parts area (Parts tab)</t>
+          <t>Send to Portal</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
@@ -5237,7 +5197,11 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G130" s="5" t="inlineStr"/>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -5252,7 +5216,7 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>WO Notes (Notes tab)</t>
+          <t>Create/Edit WO Lines (New Line)</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
@@ -5260,14 +5224,14 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F131" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
+      <c r="E131" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr"/>
@@ -5285,7 +5249,7 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Timesheets (tab)</t>
+          <t>Review Work Orders (Reviewed)</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
@@ -5318,29 +5282,25 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D133" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E133" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F133" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
-        </is>
-      </c>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -5355,29 +5315,25 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>Change Customer on WO</t>
-        </is>
-      </c>
-      <c r="D134" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E134" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F134" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>Invoicing/Finance view (Finance tab)</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E134" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -5392,29 +5348,25 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>Change Asset on WO</t>
-        </is>
-      </c>
-      <c r="D135" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E135" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F135" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -5429,17 +5381,17 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
+          <t>Send to Terminal</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>N/V*</t>
+          <t>N/V</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>N/V*</t>
+          <t>N/V</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
@@ -5449,29 +5401,29 @@
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
+          <t>ORG-terminal gated: prod none, staging has one</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative (+Reporting)</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
-        </is>
-      </c>
-      <c r="D137" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -5479,31 +5431,27 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="F137" s="7" t="inlineStr">
-        <is>
-          <t>STAGING-LESS</t>
-        </is>
-      </c>
-      <c r="G137" s="5" t="inlineStr">
-        <is>
-          <t>prod portal org-customer-portal gated</t>
-        </is>
-      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative (+Reporting)</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
+          <t>Order Parts area (Parts tab)</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
@@ -5526,17 +5474,17 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative (+Reporting)</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
+          <t>WO Notes (Notes tab)</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
@@ -5544,14 +5492,14 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="E139" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F139" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr"/>
@@ -5559,27 +5507,27 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative (+Reporting)</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
@@ -5592,27 +5540,27 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative (+Reporting)</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>Invoicing/Finance view (Finance tab)</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
@@ -5620,22 +5568,26 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G141" s="5" t="inlineStr"/>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>observed on estimate WO (deletable state)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative (+Reporting)</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment)</t>
+          <t>Change Customer on WO</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
@@ -5643,14 +5595,14 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F142" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
+      <c r="E142" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr"/>
@@ -5658,22 +5610,22 @@
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative (+Reporting)</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D143" s="10" t="inlineStr">
-        <is>
-          <t>N/V</t>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -5681,82 +5633,86 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G143" s="5" t="inlineStr">
-        <is>
-          <t>ORG-terminal gated: prod none, staging has one</t>
-        </is>
-      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative (+Reporting)</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>WO-level History (History tab)</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E144" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Approve line</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E144" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>STAGING-LESS</t>
-        </is>
-      </c>
-      <c r="G144" s="5" t="inlineStr"/>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative (+Reporting)</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Office User</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Order Parts area (Parts tab)</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E145" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Decline line</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>STAGING-LESS</t>
-        </is>
-      </c>
-      <c r="G145" s="5" t="inlineStr"/>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -5771,7 +5727,7 @@
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>WO Notes (Notes tab)</t>
+          <t>Send to Portal</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
@@ -5779,17 +5735,21 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F146" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G146" s="5" t="inlineStr"/>
+      <c r="E146" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
@@ -5804,17 +5764,17 @@
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>Timesheets (tab)</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E147" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
@@ -5837,29 +5797,25 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D148" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E148" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F148" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G148" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
-        </is>
-      </c>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D148" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -5874,29 +5830,25 @@
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>Change Customer on WO</t>
-        </is>
-      </c>
-      <c r="D149" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E149" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F149" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -5911,29 +5863,25 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>Change Asset on WO</t>
-        </is>
-      </c>
-      <c r="D150" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E150" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F150" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G150" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>Invoicing/Finance view (Finance tab)</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
@@ -5948,49 +5896,45 @@
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>WO Delete</t>
-        </is>
-      </c>
-      <c r="D151" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E151" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F151" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G151" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
-        </is>
-      </c>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D151" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G151" s="5" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>Send to Portal</t>
-        </is>
-      </c>
-      <c r="D152" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
@@ -5998,36 +5942,36 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="F152" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>prod portal org-customer-portal gated</t>
+          <t>ORG-terminal gated: prod none, staging has one</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>Create/Edit WO Lines (New Line)</t>
-        </is>
-      </c>
-      <c r="D153" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -6035,9 +5979,9 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="F153" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr"/>
@@ -6045,22 +5989,22 @@
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>Review Work Orders (Reviewed)</t>
-        </is>
-      </c>
-      <c r="D154" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
@@ -6068,9 +6012,9 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="F154" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr"/>
@@ -6078,27 +6022,27 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>See Financial Data (Rate/Margin)</t>
-        </is>
-      </c>
-      <c r="D155" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E155" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr">
@@ -6111,27 +6055,27 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>Invoicing/Finance view (Finance tab)</t>
-        </is>
-      </c>
-      <c r="D156" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E156" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
@@ -6144,92 +6088,92 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>Take Payment (New Payment)</t>
-        </is>
-      </c>
-      <c r="D157" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E157" s="10" t="inlineStr">
-        <is>
-          <t>N/V</t>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G157" s="5" t="inlineStr"/>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>observed on estimate WO (deletable state)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D158" s="10" t="inlineStr">
-        <is>
-          <t>N/V</t>
-        </is>
-      </c>
-      <c r="E158" s="10" t="inlineStr">
-        <is>
-          <t>N/V</t>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E158" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G158" s="5" t="inlineStr">
-        <is>
-          <t>ORG-terminal gated: prod none, staging has one</t>
-        </is>
-      </c>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>WO-level History (History tab)</t>
-        </is>
-      </c>
-      <c r="D159" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -6237,9 +6181,9 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="F159" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr"/>
@@ -6247,68 +6191,76 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>Order Parts area (Parts tab)</t>
-        </is>
-      </c>
-      <c r="D160" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E160" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F160" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G160" s="5" t="inlineStr"/>
+          <t>Approve line</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E160" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Time Clock User</t>
+          <t>Office User</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>WO Notes (Notes tab)</t>
-        </is>
-      </c>
-      <c r="D161" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E161" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F161" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
-        </is>
-      </c>
-      <c r="G161" s="5" t="inlineStr"/>
+          <t>Decline line</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E161" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
@@ -6323,7 +6275,7 @@
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>Timesheets (tab)</t>
+          <t>Send to Portal</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
@@ -6331,17 +6283,21 @@
           <t>hidden</t>
         </is>
       </c>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F162" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE</t>
-        </is>
-      </c>
-      <c r="G162" s="5" t="inlineStr"/>
+      <c r="E162" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>prod portal org-customer-portal gated</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
@@ -6356,29 +6312,25 @@
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Part Return (line Return action)</t>
-        </is>
-      </c>
-      <c r="D163" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E163" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F163" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G163" s="5" t="inlineStr">
-        <is>
-          <t>prod line menu was WO-state limited (Move only) - needs seeding to compare</t>
-        </is>
-      </c>
+          <t>Create/Edit WO Lines (New Line)</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E163" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -6393,29 +6345,25 @@
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>Change Customer on WO</t>
-        </is>
-      </c>
-      <c r="D164" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E164" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F164" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G164" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>Review Work Orders (Reviewed)</t>
+        </is>
+      </c>
+      <c r="D164" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E164" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
@@ -6430,29 +6378,25 @@
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>Change Asset on WO</t>
-        </is>
-      </c>
-      <c r="D165" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="E165" s="10" t="inlineStr">
-        <is>
-          <t>N/V*</t>
-        </is>
-      </c>
-      <c r="F165" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G165" s="5" t="inlineStr">
-        <is>
-          <t>capture inconsistent across roles - needs targeted re-observation</t>
-        </is>
-      </c>
+          <t>See Financial Data (Rate/Margin)</t>
+        </is>
+      </c>
+      <c r="D165" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E165" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
@@ -6467,27 +6411,402 @@
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
+          <t>Invoicing/Finance view (Finance tab)</t>
+        </is>
+      </c>
+      <c r="D166" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E166" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G166" s="5" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>Take Payment (New Payment)</t>
+        </is>
+      </c>
+      <c r="D167" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E167" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D168" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="E168" s="10" t="inlineStr">
+        <is>
+          <t>N/V</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>ORG-terminal gated: prod none, staging has one</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>WO-level History (History tab)</t>
+        </is>
+      </c>
+      <c r="D169" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E169" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts area (Parts tab)</t>
+        </is>
+      </c>
+      <c r="D170" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E170" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D171" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F171" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>Timesheets (tab)</t>
+        </is>
+      </c>
+      <c r="D172" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F172" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="G172" s="5" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
           <t>WO Delete</t>
         </is>
       </c>
-      <c r="D166" s="10" t="inlineStr">
+      <c r="D173" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E173" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>observed on estimate WO (deletable state)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>Change Customer on WO</t>
+        </is>
+      </c>
+      <c r="D174" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E174" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G174" s="5" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>Change Asset on WO</t>
+        </is>
+      </c>
+      <c r="D175" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E175" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>Approve line</t>
+        </is>
+      </c>
+      <c r="D176" s="10" t="inlineStr">
         <is>
           <t>N/V*</t>
         </is>
       </c>
-      <c r="E166" s="10" t="inlineStr">
+      <c r="E176" s="10" t="inlineStr">
         <is>
           <t>N/V*</t>
         </is>
       </c>
-      <c r="F166" s="7" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G166" s="5" t="inlineStr">
-        <is>
-          <t>WO-STATE dependent + staging Delete control not located even on deletable WO - needs targeted seeding</t>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>Decline line</t>
+        </is>
+      </c>
+      <c r="D177" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="E177" s="10" t="inlineStr">
+        <is>
+          <t>N/V*</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="inlineStr">
+        <is>
+          <t>estimate WO line already approved (line-state) - needs a pending-line WO both envs</t>
         </is>
       </c>
     </row>

--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Live Compare DUAL" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Staging Live Grid" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Production Live Grid" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Parts-Module Dual LIVE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +42,10 @@
       <name val="Consolas"/>
     </font>
     <font>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="009C0006"/>
     </font>
   </fonts>
@@ -108,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,6 +137,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -15964,4 +15972,1352 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="60" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>PARTS-MODULE deep-flow — LIVE dual observation 2026-07-15. Both envs driven live to /parts/orders per role; controls (New PO = Order Parts; Receive = accept delivery) observed on-screen with full-page screenshots. Staging via switch-user impersonation (7) + throwaway role-swap+switch-user (4, throwaway restored). Production via test-staff role-swap+self-login (14 roles, test staff restored to Office User). Every row is DUAL LIVE-OBSERVED (Rules 10 &amp; 12) — no inference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Staging Role</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Prod role compared</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Capability</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>PROD observed</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Staging observed</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Direction / verdict</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Per-spec?</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Prod screenshot</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Staging screenshot / Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/parts_orders.png  prod merge: Service Advisor (+ SA Technician, SA No Reports) | Story: Order Parts controls the ability to create a purchase order. FE-gated. (merge components SA Technician, SA No Reports also SHOWN — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/parts_orders.png  prod merge: Service Advisor (+ SA Technician, SA No Reports) | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button. (merge components SA Technician, SA No Reports also SHOWN — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/parts_orders.png  confirmed mapping: staging Service Advisor &lt;- prod SA Limited View | Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/parts_orders.png  confirmed mapping: staging Service Advisor &lt;- prod SA Limited View | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/parts_orders.png  prod: Parts nav hidden but /parts/orders reachable directly | Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/parts_orders.png  prod: Parts nav hidden but /parts/orders reachable directly | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/parts_orders.png  both envs: /parts/orders page viewable, but no New PO / no Receive | Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/parts_orders.png  both envs: /parts/orders page viewable, but no New PO / no Receive | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/parts_orders.png  prod merge: Sales Representative (+ Reporting) | Story: Order Parts controls the ability to create a purchase order. FE-gated. (merge components Reporting also hidden — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/parts_orders.png  prod merge: Sales Representative (+ Reporting) | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button. (merge components Reporting also hidden — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Staging Live Grid" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Production Live Grid" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Parts-Module Dual LIVE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="New-WO Create Dual LIVE" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17320,4 +17321,1979 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="55" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>NEW-WO CREATE flow — LIVE dual observation 2026-07-15. Both envs driven live: open Work Orders list, click "New", observe the New Work Order dialog (Add Customer / Add Asset). Staging via switch-user (7) + throwaway role-swap+switch-user (4, restored). Production via test-staff role-swap+self-login (14, restored to Office User). Every row DUAL LIVE-OBSERVED (Rules 10 &amp; 12) — no inference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Staging Role</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Prod role compared</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Capability</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>PROD observed</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Staging observed</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Direction / verdict</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Per-spec?</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Prod screenshot</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Staging screenshot / Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog. (merge SA Technician, SA No Reports also SHOWN — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog. (merge SA Technician, SA No Reports also SHOWN — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported. (merge SA Technician, SA No Reports also SHOWN — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE (staging grants more)</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>see note</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE (staging grants more)</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>see note</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE (staging grants more)</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>see note</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog. (merge Reporting also hidden — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog. (merge Reporting also hidden — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported. (merge Reporting also hidden — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Production Live Grid" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Parts-Module Dual LIVE" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="New-WO Create Dual LIVE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Remaining-Caps Staging LIVE" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -50,7 +51,7 @@
       <color rgb="009C0006"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +88,16 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -114,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -141,6 +152,22 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -19296,4 +19323,3349 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>STAGING-side LIVE observations of the coordinator remaining caps (existing data, no seeding). PROD EXPIRED this run -&gt; prod cells NOT VERIFIED. Rebuild dual once fresh prod cookies supplied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Staging Role</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Prod Role (compare)</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Capability</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>STAGING Observed (live)</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>PROD Observed</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Staging Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>admin quick-login (self)</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Admin/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Start/Complete/Pick)</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>admin quick-login (self)</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Admin/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Delete Work Order in WO menu)</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>admin quick-login (self)</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Admin/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>admin quick-login (self)</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Admin/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>admin quick-login (self)</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Admin/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>admin quick-login (self)</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Admin/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor (merge)</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Senior_Service_Advisor/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor (merge)</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Complete; Start hidden)</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Senior_Service_Advisor/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor (merge)</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Delete Work Order in WO menu)</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Senior_Service_Advisor/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor (merge)</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Senior_Service_Advisor/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor (merge)</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Senior_Service_Advisor/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor (merge)</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Senior_Service_Advisor/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Parts_Manager/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Parts_Manager/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>hidden (WO menu = Audit Log only)</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Parts_Manager/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Parts_Manager/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>hidden (finance menu = Issue Credit only)</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Parts_Manager/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Parts_Manager/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Service_Advisor/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Service_Advisor/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>hidden (WO menu = Audit Log + Timesheets, no Delete)</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Service_Advisor/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Service_Advisor/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>hidden (finance menu = Issue Credit only)</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Service_Advisor/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Service_Advisor/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative (merge)</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Return only)</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Sales_Representative/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative (merge)</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>partial (Start only)</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Sales_Representative/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative (merge)</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="inlineStr">
+        <is>
+          <t>hidden (no WO menu)</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Sales_Representative/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative (merge)</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Sales_Representative/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative (merge)</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Sales_Representative/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative (merge)</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Sales_Representative/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>tech quick-login (shared org, tech view)</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Technician/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Complete/Pick; Approve/Start hidden)</t>
+        </is>
+      </c>
+      <c r="E58" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>tech quick-login (shared org, tech view)</t>
+        </is>
+      </c>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Technician/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>hidden (no WO menu)</t>
+        </is>
+      </c>
+      <c r="E59" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>tech quick-login (shared org, tech view)</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Technician/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>hidden (no Finance tab)</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>tech quick-login (shared org, tech view)</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Technician/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D61" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E61" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>tech quick-login (shared org, tech view)</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Technician/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod side)</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>tech quick-login (shared org, tech view)</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/staging/Technician/wo_lines.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
+        </is>
+      </c>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H66" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
+        </is>
+      </c>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (both sides)</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H68" s="14" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I68" s="14" t="inlineStr">
+        <is>
+          <t>(not rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>CAPS NOT OBSERVABLE ON STAGING THIS RUN (both sides NOT VERIFIED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>(all roles)</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>(all)</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>Assign Vendor / Fix Part#</t>
+        </is>
+      </c>
+      <c r="D71" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired</t>
+        </is>
+      </c>
+      <c r="F71" s="16" t="inlineStr">
+        <is>
+          <t>PO-detail page (/parts/orders/{id}) did not render its content via direct URL (shows nav shell + 'Go to Work Orders' only) — needs navigation from the WO Parts tab; NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G71" s="16" t="inlineStr"/>
+      <c r="H71" s="16" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I71" s="16" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>(all roles)</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>(all)</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>Bulk Receive</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E72" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired</t>
+        </is>
+      </c>
+      <c r="F72" s="16" t="inlineStr">
+        <is>
+          <t>/parts/deliveries rendered nav shell only, no bulk-receive control surfaced via direct URL; NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G72" s="16" t="inlineStr"/>
+      <c r="H72" s="16" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I72" s="16" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>(all roles)</t>
+        </is>
+      </c>
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>(all)</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>Core OK/Not-OK</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E73" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired</t>
+        </is>
+      </c>
+      <c r="F73" s="16" t="inlineStr">
+        <is>
+          <t>Reference picked-parts WO has no cored line; no existing WO with a cored picked part (P550848) located; NOT VERIFIED (needs a cored picked line seeded)</t>
+        </is>
+      </c>
+      <c r="G73" s="16" t="inlineStr"/>
+      <c r="H73" s="16" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I73" s="16" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>(all roles)</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>(all)</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>See AP/AR detail</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E74" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — prod session expired</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>AP/AR route not reliably isolatable (/accounting,/bookkeeping,/reports/aging all returned generic shell); NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G74" s="16" t="inlineStr"/>
+      <c r="H74" s="16" t="inlineStr">
+        <is>
+          <t>NOT-VERIFIED</t>
+        </is>
+      </c>
+      <c r="I74" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -15,7 +15,8 @@
     <sheet name="Production Live Grid" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Parts-Module Dual LIVE" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="New-WO Create Dual LIVE" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Remaining-Caps Staging LIVE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Remaining-Caps Dual LIVE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Prod Remaining-Caps (all 14)" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -51,7 +52,7 @@
       <color rgb="009C0006"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +99,11 @@
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -168,6 +174,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -763,6 +772,736 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Prod Legacy Role</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Core OK/Not-OK</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>New Payment</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Issue Credit</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Finance method</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>finance panel loaded</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Finance tab present but /api/work-orders/invoices/estimate HTTP 400 -&gt; "No location" (role-swap session artifact)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Finance tab present but /api/work-orders/invoices/estimate HTTP 400 -&gt; "No location" (role-swap session artifact)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor - No Reports</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>finance panel loaded</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor Technician</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>no Finance tab on invoiced WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor - Limited View</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>finance panel loaded</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>no Finance tab on invoiced WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Start/Complete)</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>no Finance tab on invoiced WO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Start/Complete)</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Finance tab present but /api/work-orders/invoices/estimate HTTP 400 -&gt; "No location" (role-swap session artifact)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Start/Complete)</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Finance tab present but /api/work-orders/invoices/estimate HTTP 400 -&gt; "No location" (role-swap session artifact)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (WO detail did not render)</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (WO detail did not render)</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (WO detail did not render)</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>invoiced WO did not render ("No location")</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (WO detail did not render)</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (WO detail did not render)</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (WO detail did not render)</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>invoiced WO did not render ("No location")</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Finance tab present but /api/work-orders/invoices/estimate HTTP 400 -&gt; "No location" (role-swap session artifact)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (WO detail did not render)</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (WO detail did not render)</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (WO detail did not render)</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>invoiced WO did not render ("No location")</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -19331,24 +20070,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>STAGING-side LIVE observations of the coordinator remaining caps (existing data, no seeding). PROD EXPIRED this run -&gt; prod cells NOT VERIFIED. Rebuild dual once fresh prod cookies supplied.</t>
+          <t>REAL DUAL verdicts for the remaining FE-gated caps — BOTH sides live-observed 2026-07-15b. Prod re-observed via renewable self-login + test-staff role-swap (restored to Office User). Part Return prod = NOT VERIFIED (control not surfacable via headless probe). Finance NOT VERIFIED where /api/work-orders/invoices/estimate HTTP 400 crashed the panel. Staging Service Manager/Foreman/Office User/Parts Technician = NOT VERIFIED (no role-holder + staff/change HTTP 500).</t>
         </is>
       </c>
     </row>
@@ -19360,7 +20099,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>Prod Role (compare)</t>
+          <t>Prod Role(s) mapped</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
@@ -19370,17 +20109,17 @@
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
+          <t>PROD Observed (live)</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
           <t>STAGING Observed (live)</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
-        <is>
-          <t>PROD Observed</t>
-        </is>
-      </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>Verdict</t>
+          <t>Direction / Verdict</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
@@ -19395,7 +20134,7 @@
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>Staging Evidence</t>
+          <t>Evidence</t>
         </is>
       </c>
     </row>
@@ -19415,34 +20154,34 @@
           <t>Part Return</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F3" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>admin quick-login (self)</t>
+          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Admin/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
         </is>
       </c>
     </row>
@@ -19464,32 +20203,32 @@
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
           <t>SHOWN (Approve/Start/Complete/Pick)</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
-          <t>admin quick-login (self)</t>
+          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
         </is>
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Admin/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
         </is>
       </c>
     </row>
@@ -19511,32 +20250,32 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
           <t>SHOWN (Delete Work Order in WO menu)</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>admin quick-login (self)</t>
+          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Admin/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
         </is>
       </c>
     </row>
@@ -19561,29 +20300,29 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>admin quick-login (self)</t>
+          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Admin/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
         </is>
       </c>
     </row>
@@ -19608,29 +20347,29 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>admin quick-login (self)</t>
+          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Admin/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
         </is>
       </c>
     </row>
@@ -19655,29 +20394,29 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>admin quick-login (self)</t>
+          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Admin/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
         </is>
       </c>
     </row>
@@ -19699,32 +20438,32 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
         </is>
       </c>
     </row>
@@ -19744,34 +20483,34 @@
           <t>Set Line Status</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>PROD live / STAGING NV</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
         </is>
       </c>
     </row>
@@ -19791,34 +20530,34 @@
           <t>WO Delete (Delete Work Order)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>PROD live / STAGING NV</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
         </is>
       </c>
     </row>
@@ -19840,32 +20579,32 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
         </is>
       </c>
     </row>
@@ -19887,32 +20626,32 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
         </is>
       </c>
     </row>
@@ -19934,32 +20673,32 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
         </is>
       </c>
     </row>
@@ -19971,7 +20710,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Service Advisor (merge)</t>
+          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
@@ -19979,34 +20718,34 @@
           <t>Part Return</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Senior_Service_Advisor/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20757,7 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Service Advisor (merge)</t>
+          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -20028,32 +20767,32 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
           <t>SHOWN (Approve/Complete; Start hidden)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Senior_Service_Advisor/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
         </is>
       </c>
     </row>
@@ -20065,7 +20804,7 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Service Advisor (merge)</t>
+          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -20075,32 +20814,32 @@
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
+          <t>SHOWN  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
           <t>SHOWN (Delete Work Order in WO menu)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Senior_Service_Advisor/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
         </is>
       </c>
     </row>
@@ -20112,7 +20851,7 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Service Advisor (merge)</t>
+          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -20120,34 +20859,34 @@
           <t>Invoicing create (New Payment)</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Senior_Service_Advisor/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
         </is>
       </c>
     </row>
@@ -20159,7 +20898,7 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Service Advisor (merge)</t>
+          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
@@ -20167,34 +20906,34 @@
           <t>Invoice Reverse</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Senior_Service_Advisor/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
         </is>
       </c>
     </row>
@@ -20206,7 +20945,7 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Service Advisor (merge)</t>
+          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -20214,34 +20953,34 @@
           <t>Invoice Issue Credit</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Senior_Service_Advisor/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
         </is>
       </c>
     </row>
@@ -20261,34 +21000,34 @@
           <t>Part Return</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Parts_Manager/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
         </is>
       </c>
     </row>
@@ -20310,32 +21049,32 @@
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
+          <t>SHOWN (Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
           <t>SHOWN (Approve/Start/Complete)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Parts_Manager/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
         </is>
       </c>
     </row>
@@ -20355,34 +21094,34 @@
           <t>WO Delete (Delete Work Order)</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>hidden (WO menu = Audit Log only)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>STAGING-LESS (prod-more)</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Parts_Manager/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
         </is>
       </c>
     </row>
@@ -20402,34 +21141,34 @@
           <t>Invoicing create (New Payment)</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Parts_Manager/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
         </is>
       </c>
     </row>
@@ -20449,34 +21188,34 @@
           <t>Invoice Reverse</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>hidden (finance menu = Issue Credit only)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Parts_Manager/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
         </is>
       </c>
     </row>
@@ -20496,34 +21235,34 @@
           <t>Invoice Issue Credit</t>
         </is>
       </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Parts_Manager/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
         </is>
       </c>
     </row>
@@ -20535,7 +21274,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>SA Limited View</t>
+          <t>Service Advisor - Limited View</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
@@ -20543,34 +21282,34 @@
           <t>Part Return</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Service_Advisor/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
         </is>
       </c>
     </row>
@@ -20582,7 +21321,7 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>SA Limited View</t>
+          <t>Service Advisor - Limited View</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
@@ -20592,32 +21331,32 @@
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
           <t>SHOWN (Approve/Start/Complete)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Service_Advisor/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
         </is>
       </c>
     </row>
@@ -20629,7 +21368,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>SA Limited View</t>
+          <t>Service Advisor - Limited View</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -20637,34 +21376,34 @@
           <t>WO Delete (Delete Work Order)</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>hidden (WO menu = Audit Log + Timesheets, no Delete)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>STAGING-LESS (prod-more)</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Service_Advisor/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
         </is>
       </c>
     </row>
@@ -20676,7 +21415,7 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>SA Limited View</t>
+          <t>Service Advisor - Limited View</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
@@ -20689,29 +21428,29 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Service_Advisor/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
         </is>
       </c>
     </row>
@@ -20723,7 +21462,7 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>SA Limited View</t>
+          <t>Service Advisor - Limited View</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
@@ -20731,34 +21470,34 @@
           <t>Invoice Reverse</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>hidden (finance menu = Issue Credit only)</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>STAGING-LESS (prod-more)</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Service_Advisor/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
         </is>
       </c>
     </row>
@@ -20770,7 +21509,7 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>SA Limited View</t>
+          <t>Service Advisor - Limited View</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -20783,29 +21522,29 @@
           <t>SHOWN</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Service_Advisor/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
         </is>
       </c>
     </row>
@@ -20827,32 +21566,32 @@
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
         </is>
       </c>
     </row>
@@ -20872,34 +21611,34 @@
           <t>Set Line Status</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>PROD live / STAGING NV</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
         </is>
       </c>
     </row>
@@ -20919,34 +21658,34 @@
           <t>WO Delete (Delete Work Order)</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>PROD live / STAGING NV</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
         </is>
       </c>
     </row>
@@ -20966,34 +21705,34 @@
           <t>Invoicing create (New Payment)</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>PROD live / STAGING NV</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
         </is>
       </c>
     </row>
@@ -21013,34 +21752,34 @@
           <t>Invoice Reverse</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>PROD live / STAGING NV</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
         </is>
       </c>
     </row>
@@ -21060,34 +21799,34 @@
           <t>Invoice Issue Credit</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>PROD live / STAGING NV</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
         </is>
       </c>
     </row>
@@ -21109,32 +21848,32 @@
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
         </is>
       </c>
     </row>
@@ -21154,34 +21893,34 @@
           <t>Set Line Status</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>PROD live / STAGING NV</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
         </is>
       </c>
     </row>
@@ -21201,34 +21940,34 @@
           <t>WO Delete (Delete Work Order)</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>PROD live / STAGING NV</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
         </is>
       </c>
     </row>
@@ -21250,32 +21989,32 @@
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
         </is>
       </c>
     </row>
@@ -21297,32 +22036,32 @@
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
         </is>
       </c>
     </row>
@@ -21344,32 +22083,32 @@
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
         </is>
       </c>
     </row>
@@ -21391,32 +22130,32 @@
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E45" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
         </is>
       </c>
     </row>
@@ -21436,34 +22175,34 @@
           <t>Set Line Status</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="inlineStr">
         <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E46" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>PROD live / STAGING NV</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
         </is>
       </c>
     </row>
@@ -21483,34 +22222,34 @@
           <t>WO Delete (Delete Work Order)</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
         <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E47" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F47" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>PROD live / STAGING NV</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
         </is>
       </c>
     </row>
@@ -21532,32 +22271,32 @@
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
         </is>
       </c>
     </row>
@@ -21579,32 +22318,32 @@
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E49" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
         </is>
       </c>
     </row>
@@ -21626,32 +22365,32 @@
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
         </is>
       </c>
-      <c r="E50" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>role-swap (staff/change)</t>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
         </is>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
         </is>
       </c>
     </row>
@@ -21663,7 +22402,7 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Sales Representative (merge)</t>
+          <t>Sales Representative (merge: + Reporting)</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
@@ -21671,34 +22410,34 @@
           <t>Part Return</t>
         </is>
       </c>
-      <c r="D51" s="15" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)  [merge: + Reporting]</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
         <is>
           <t>SHOWN (Return only)</t>
         </is>
       </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Sales_Representative/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
         </is>
       </c>
     </row>
@@ -21710,7 +22449,7 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Sales Representative (merge)</t>
+          <t>Sales Representative (merge: + Reporting)</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -21720,32 +22459,32 @@
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED (WO detail did not render)  [merge: + Reporting]</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
           <t>partial (Start only)</t>
         </is>
       </c>
-      <c r="E52" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Sales_Representative/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
         </is>
       </c>
     </row>
@@ -21757,7 +22496,7 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Sales Representative (merge)</t>
+          <t>Sales Representative (merge: + Reporting)</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -21765,34 +22504,34 @@
           <t>WO Delete (Delete Work Order)</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (WO detail did not render)  [merge: + Reporting]</t>
+        </is>
+      </c>
+      <c r="E53" s="17" t="inlineStr">
         <is>
           <t>hidden (no WO menu)</t>
         </is>
       </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F53" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Sales_Representative/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
         </is>
       </c>
     </row>
@@ -21804,7 +22543,7 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Sales Representative (merge)</t>
+          <t>Sales Representative (merge: + Reporting)</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
@@ -21812,34 +22551,34 @@
           <t>Invoicing create (New Payment)</t>
         </is>
       </c>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F54" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED  [merge: + Reporting]</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Sales_Representative/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
         </is>
       </c>
     </row>
@@ -21851,7 +22590,7 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Sales Representative (merge)</t>
+          <t>Sales Representative (merge: + Reporting)</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
@@ -21859,34 +22598,34 @@
           <t>Invoice Reverse</t>
         </is>
       </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED  [merge: + Reporting]</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Sales_Representative/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
         </is>
       </c>
     </row>
@@ -21898,7 +22637,7 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Sales Representative (merge)</t>
+          <t>Sales Representative (merge: + Reporting)</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -21906,34 +22645,34 @@
           <t>Invoice Issue Credit</t>
         </is>
       </c>
-      <c r="D56" s="17" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E56" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F56" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED  [merge: + Reporting]</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Sales_Representative/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
         </is>
       </c>
     </row>
@@ -21953,34 +22692,34 @@
           <t>Part Return</t>
         </is>
       </c>
-      <c r="D57" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E57" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F57" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>tech quick-login (shared org, tech view)</t>
+          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
         </is>
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>STAGING live / PROD NV</t>
         </is>
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Technician/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
         </is>
       </c>
     </row>
@@ -22002,32 +22741,32 @@
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
+          <t>SHOWN (Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
           <t>SHOWN (Complete/Pick; Approve/Start hidden)</t>
         </is>
       </c>
-      <c r="E58" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F58" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>tech quick-login (shared org, tech view)</t>
+          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
         </is>
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Technician/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
         </is>
       </c>
     </row>
@@ -22047,34 +22786,34 @@
           <t>WO Delete (Delete Work Order)</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E59" s="17" t="inlineStr">
         <is>
           <t>hidden (no WO menu)</t>
         </is>
       </c>
-      <c r="E59" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F59" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>STAGING-LESS (prod-more)</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>tech quick-login (shared org, tech view)</t>
+          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
         </is>
       </c>
       <c r="H59" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Technician/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
         </is>
       </c>
     </row>
@@ -22096,32 +22835,32 @@
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
           <t>hidden (no Finance tab)</t>
         </is>
       </c>
-      <c r="E60" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F60" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+      <c r="F60" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>tech quick-login (shared org, tech view)</t>
+          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
         </is>
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Technician/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
         </is>
       </c>
     </row>
@@ -22143,32 +22882,32 @@
       </c>
       <c r="D61" s="17" t="inlineStr">
         <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E61" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F61" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E61" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F61" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>tech quick-login (shared org, tech view)</t>
+          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
         </is>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Technician/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
         </is>
       </c>
     </row>
@@ -22190,32 +22929,32 @@
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E62" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F62" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (prod side)</t>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F62" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>tech quick-login (shared org, tech view)</t>
+          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
         </is>
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>STAGING OBSERVED-LIVE / PROD NOT-VERIFIED</t>
+          <t>DUAL OBSERVED-LIVE</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>live-ui-2026-07-15/staging/Technician/wo_lines.png</t>
+          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
         </is>
       </c>
     </row>
@@ -22237,32 +22976,32 @@
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
         </is>
       </c>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F63" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I63" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
         </is>
       </c>
     </row>
@@ -22284,32 +23023,32 @@
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED (WO detail did not render)</t>
+        </is>
+      </c>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
         </is>
       </c>
-      <c r="E64" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F64" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
         </is>
       </c>
     </row>
@@ -22331,32 +23070,32 @@
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED (WO detail did not render)</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
         </is>
       </c>
-      <c r="E65" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F65" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H65" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
         </is>
       </c>
     </row>
@@ -22378,32 +23117,32 @@
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
         </is>
       </c>
-      <c r="E66" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F66" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
         </is>
       </c>
     </row>
@@ -22425,32 +23164,32 @@
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
         </is>
       </c>
-      <c r="E67" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F67" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
+          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
         </is>
       </c>
     </row>
@@ -22472,198 +23211,34 @@
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
           <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
         </is>
       </c>
-      <c r="E68" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired 2026-07-15</t>
-        </is>
-      </c>
-      <c r="F68" s="14" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (both sides)</t>
+      <c r="F68" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>switch-user impersonation</t>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
         </is>
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>NOT-VERIFIED</t>
+          <t>BOTH NV</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>(not rendered)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69"/>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>CAPS NOT OBSERVABLE ON STAGING THIS RUN (both sides NOT VERIFIED)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="16" t="inlineStr">
-        <is>
-          <t>(all roles)</t>
-        </is>
-      </c>
-      <c r="B71" s="16" t="inlineStr">
-        <is>
-          <t>(all)</t>
-        </is>
-      </c>
-      <c r="C71" s="16" t="inlineStr">
-        <is>
-          <t>Assign Vendor / Fix Part#</t>
-        </is>
-      </c>
-      <c r="D71" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E71" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired</t>
-        </is>
-      </c>
-      <c r="F71" s="16" t="inlineStr">
-        <is>
-          <t>PO-detail page (/parts/orders/{id}) did not render its content via direct URL (shows nav shell + 'Go to Work Orders' only) — needs navigation from the WO Parts tab; NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G71" s="16" t="inlineStr"/>
-      <c r="H71" s="16" t="inlineStr">
-        <is>
-          <t>NOT-VERIFIED</t>
-        </is>
-      </c>
-      <c r="I71" s="16" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="16" t="inlineStr">
-        <is>
-          <t>(all roles)</t>
-        </is>
-      </c>
-      <c r="B72" s="16" t="inlineStr">
-        <is>
-          <t>(all)</t>
-        </is>
-      </c>
-      <c r="C72" s="16" t="inlineStr">
-        <is>
-          <t>Bulk Receive</t>
-        </is>
-      </c>
-      <c r="D72" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E72" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired</t>
-        </is>
-      </c>
-      <c r="F72" s="16" t="inlineStr">
-        <is>
-          <t>/parts/deliveries rendered nav shell only, no bulk-receive control surfaced via direct URL; NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G72" s="16" t="inlineStr"/>
-      <c r="H72" s="16" t="inlineStr">
-        <is>
-          <t>NOT-VERIFIED</t>
-        </is>
-      </c>
-      <c r="I72" s="16" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="16" t="inlineStr">
-        <is>
-          <t>(all roles)</t>
-        </is>
-      </c>
-      <c r="B73" s="16" t="inlineStr">
-        <is>
-          <t>(all)</t>
-        </is>
-      </c>
-      <c r="C73" s="16" t="inlineStr">
-        <is>
-          <t>Core OK/Not-OK</t>
-        </is>
-      </c>
-      <c r="D73" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E73" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired</t>
-        </is>
-      </c>
-      <c r="F73" s="16" t="inlineStr">
-        <is>
-          <t>Reference picked-parts WO has no cored line; no existing WO with a cored picked part (P550848) located; NOT VERIFIED (needs a cored picked line seeded)</t>
-        </is>
-      </c>
-      <c r="G73" s="16" t="inlineStr"/>
-      <c r="H73" s="16" t="inlineStr">
-        <is>
-          <t>NOT-VERIFIED</t>
-        </is>
-      </c>
-      <c r="I73" s="16" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="16" t="inlineStr">
-        <is>
-          <t>(all roles)</t>
-        </is>
-      </c>
-      <c r="B74" s="16" t="inlineStr">
-        <is>
-          <t>(all)</t>
-        </is>
-      </c>
-      <c r="C74" s="16" t="inlineStr">
-        <is>
-          <t>See AP/AR detail</t>
-        </is>
-      </c>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E74" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — prod session expired</t>
-        </is>
-      </c>
-      <c r="F74" s="16" t="inlineStr">
-        <is>
-          <t>AP/AR route not reliably isolatable (/accounting,/bookkeeping,/reports/aging all returned generic shell); NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G74" s="16" t="inlineStr"/>
-      <c r="H74" s="16" t="inlineStr">
-        <is>
-          <t>NOT-VERIFIED</t>
-        </is>
-      </c>
-      <c r="I74" s="16" t="inlineStr"/>
+          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -8,15 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="READ ME - Coverage &amp; Honesty" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Full Dual Matrix" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Send to Terminal LIVE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Live Compare DUAL" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Staging Live Grid" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Production Live Grid" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Parts-Module Dual LIVE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="New-WO Create Dual LIVE" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Remaining-Caps Dual LIVE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Prod Remaining-Caps (all 14)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Pass-9 LIVE (2026-07-16)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Full Dual Matrix" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Send to Terminal LIVE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Live Compare DUAL" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Staging Live Grid" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Production Live Grid" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Parts-Module Dual LIVE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="New-WO Create Dual LIVE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Remaining-Caps Dual LIVE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Prod Remaining-Caps (all 14)" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +51,10 @@
     <font>
       <b val="1"/>
       <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="11">
@@ -131,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -179,6 +184,12 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -778,6 +789,3187 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>REAL DUAL verdicts for the remaining FE-gated caps — BOTH sides live-observed 2026-07-15b. Prod re-observed via renewable self-login + test-staff role-swap (restored to Office User). Part Return prod = NOT VERIFIED (control not surfacable via headless probe). Finance NOT VERIFIED where /api/work-orders/invoices/estimate HTTP 400 crashed the panel. Staging Service Manager/Foreman/Office User/Parts Technician = NOT VERIFIED (no role-holder + staff/change HTTP 500).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Staging Role</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Prod Role(s) mapped</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Capability</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>PROD Observed (live)</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>STAGING Observed (live)</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Direction / Verdict</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Start/Complete/Pick)</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Delete Work Order in WO menu)</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>PROD live / STAGING NV</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>PROD live / STAGING NV</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Complete; Start hidden)</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Delete Work Order in WO menu)</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>hidden (WO menu = Audit Log only)</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>STAGING-LESS (prod-more)</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>hidden (finance menu = Issue Credit only)</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor - Limited View</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor - Limited View</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor - Limited View</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>hidden (WO menu = Audit Log + Timesheets, no Delete)</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>STAGING-LESS (prod-more)</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor - Limited View</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor - Limited View</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>hidden (finance menu = Issue Credit only)</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>STAGING-LESS (prod-more)</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Service Advisor - Limited View</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline/Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>PROD live / STAGING NV</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>PROD live / STAGING NV</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>PROD live / STAGING NV</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>PROD live / STAGING NV</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>PROD live / STAGING NV</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>PROD live / STAGING NV</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>PROD live / STAGING NV</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>PROD live / STAGING NV</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>PROD live / STAGING NV</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative (merge: + Reporting)</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)  [merge: + Reporting]</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Return only)</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative (merge: + Reporting)</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (WO detail did not render)  [merge: + Reporting]</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>partial (Start only)</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative (merge: + Reporting)</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (WO detail did not render)  [merge: + Reporting]</t>
+        </is>
+      </c>
+      <c r="E53" s="17" t="inlineStr">
+        <is>
+          <t>hidden (no WO menu)</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative (merge: + Reporting)</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED  [merge: + Reporting]</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative (merge: + Reporting)</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED  [merge: + Reporting]</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative (merge: + Reporting)</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED  [merge: + Reporting]</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>STAGING live / PROD NV</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Start/Complete)</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN (Complete/Pick; Approve/Start hidden)</t>
+        </is>
+      </c>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
+        </is>
+      </c>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>hidden (no WO menu)</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>STAGING-LESS (prod-more)</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>hidden (no Finance tab)</t>
+        </is>
+      </c>
+      <c r="F60" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D61" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E61" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F61" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F62" s="15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>DUAL OBSERVED-LIVE</t>
+        </is>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (WO detail did not render)</t>
+        </is>
+      </c>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>WO Delete (Delete Work Order)</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (WO detail did not render)</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
+        </is>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>Invoicing create (New Payment)</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H66" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>Invoice Issue Credit</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
+        </is>
+      </c>
+      <c r="F68" s="16" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
+        </is>
+      </c>
+      <c r="H68" s="14" t="inlineStr">
+        <is>
+          <t>BOTH NV</t>
+        </is>
+      </c>
+      <c r="I68" s="14" t="inlineStr">
+        <is>
+          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1503,6 +4695,771 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>PASS-9 (2026-07-16) — self-service unblocks. OBSERVED-LIVE only; NOT VERIFIED never inferred (Rules 10/12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Staging role</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Capability</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Prod (LIVE)</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Staging (LIVE)</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Dual verdict</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Confidence / method</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>New Payment</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE (prod SA-LV self-login; stg switch-user)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Invoice Reverse</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>STAGING-LESS (release risk)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Issue Credit</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>New Payment / Finance</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>HIDDEN (no Finance tab)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Issue Credit</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>New Payment / Finance</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>403 DENY (Pass-8)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Issue Credit</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>403 DENY (Pass-8)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>New Payment/Reverse/Credit</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>SHOWN/SHOWN/SHOWN</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>prod estimate-400 crash; invoice-view=200</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>New Payment/Reverse/Credit</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>SHOWN/hidden/SHOWN</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>prod estimate-400 crash</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>New Payment/Reverse/Credit</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>SHOWN/hidden/SHOWN</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>prod estimate-400 crash</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE (seeded WO S-25619)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (Approve/Decline)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>no status buttons</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Set Line Status</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Start/Complete only (Pass-8)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE (stg); prod partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>WO Delete</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Service Manager/Parts Manager/Parts Technician</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>Prod finance (New Payment/Reverse/Credit)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>prod estimate-400 -&gt; /no-location on S1-518/543/517; needs dev fix or per-role prod login</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>Service Mgr/Foreman/Office/Parts Tech</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>Core OK/Not-OK</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>needs picked cored part on a line (deep seed / attended session)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Service Mgr/Foreman/Office/Parts Tech</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>needs a picked part on a line</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>(all)</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>Assign Vendor / Fix Part# / Bulk Receive / See AP-AR</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>PO-detail/deliveries/AP-AR in-app nav not driven this pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7590,7 +11547,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7909,7 +11866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15427,7 +19384,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16055,7 +20012,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16741,7 +20698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18089,7 +22046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20062,3185 +24019,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>REAL DUAL verdicts for the remaining FE-gated caps — BOTH sides live-observed 2026-07-15b. Prod re-observed via renewable self-login + test-staff role-swap (restored to Office User). Part Return prod = NOT VERIFIED (control not surfacable via headless probe). Finance NOT VERIFIED where /api/work-orders/invoices/estimate HTTP 400 crashed the panel. Staging Service Manager/Foreman/Office User/Parts Technician = NOT VERIFIED (no role-holder + staff/change HTTP 500).</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>Staging Role</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>Prod Role(s) mapped</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>Capability</t>
-        </is>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>PROD Observed (live)</t>
-        </is>
-      </c>
-      <c r="E2" s="13" t="inlineStr">
-        <is>
-          <t>STAGING Observed (live)</t>
-        </is>
-      </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>Direction / Verdict</t>
-        </is>
-      </c>
-      <c r="G2" s="13" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="I2" s="13" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>Part Return</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F3" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G3" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
-        </is>
-      </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I3" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>Set Line Status</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Approve/Decline/Start/Complete)</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Approve/Start/Complete/Pick)</t>
-        </is>
-      </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
-        </is>
-      </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>WO Delete (Delete Work Order)</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Delete Work Order in WO menu)</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>Invoicing create (New Payment)</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Reverse</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Issue Credit</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: admin quick-login (self)</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Administrator/  +  staging/Admin/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Part Return</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Set Line Status</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Approve/Decline/Start/Complete)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>PROD live / STAGING NV</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>WO Delete (Delete Work Order)</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>PROD live / STAGING NV</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Invoicing create (New Payment)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Reverse</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Issue Credit</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder in staff list + staff/change returned HTTP 500 today (shared-env drift) — could not impersonate</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Manager/  +  staging/Service_Manager/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Senior Service Advisor</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>Part Return</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>Senior Service Advisor</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>Set Line Status</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Approve/Decline/Start/Complete)  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Approve/Complete; Start hidden)</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Senior Service Advisor</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>WO Delete (Delete Work Order)</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Delete Work Order in WO menu)</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>Senior Service Advisor</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>Invoicing create (New Payment)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>Senior Service Advisor</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Reverse</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
-        </is>
-      </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>Senior Service Advisor</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor (merge: + Service Advisor Technician + Service Advisor - No Reports)</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Issue Credit</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED  [merge: + Service Advisor Technician + Service Advisor - No Reports]</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Advisor/  +  staging/Senior_Service_Advisor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>Part Return</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>Set Line Status</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Start/Complete)</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Approve/Start/Complete)</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>WO Delete (Delete Work Order)</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>hidden (WO menu = Audit Log only)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>STAGING-LESS (prod-more)</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>Invoicing create (New Payment)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Reverse</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>hidden (finance menu = Issue Credit only)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Issue Credit</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Parts_Manager/  +  staging/Parts_Manager/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor - Limited View</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>Part Return</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor - Limited View</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>Set Line Status</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Approve/Decline/Start/Complete)</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Approve/Start/Complete)</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H28" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor - Limited View</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>WO Delete (Delete Work Order)</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>hidden (WO menu = Audit Log + Timesheets, no Delete)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>STAGING-LESS (prod-more)</t>
-        </is>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H29" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor - Limited View</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>Invoicing create (New Payment)</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H30" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I30" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor - Limited View</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Reverse</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>hidden (finance menu = Issue Credit only)</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr">
-        <is>
-          <t>STAGING-LESS (prod-more)</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I31" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>Service Advisor - Limited View</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Issue Credit</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I32" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Service_Advisor__Limited_View/  +  staging/Service_Advisor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>Part Return</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I33" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="inlineStr">
-        <is>
-          <t>Set Line Status</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Approve/Decline/Start/Complete)</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H34" s="14" t="inlineStr">
-        <is>
-          <t>PROD live / STAGING NV</t>
-        </is>
-      </c>
-      <c r="I34" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>WO Delete (Delete Work Order)</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>PROD live / STAGING NV</t>
-        </is>
-      </c>
-      <c r="I35" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>Invoicing create (New Payment)</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>HIDDEN</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>PROD live / STAGING NV</t>
-        </is>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Reverse</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>HIDDEN</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>PROD live / STAGING NV</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Issue Credit</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>HIDDEN</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>PROD live / STAGING NV</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Foreman/  +  staging/Foreman/</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>Part Return</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I39" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>Set Line Status</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>HIDDEN</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>PROD live / STAGING NV</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>WO Delete (Delete Work Order)</t>
-        </is>
-      </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>PROD live / STAGING NV</t>
-        </is>
-      </c>
-      <c r="I41" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr">
-        <is>
-          <t>Invoicing create (New Payment)</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H42" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I42" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Reverse</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="B44" s="14" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Issue Credit</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H44" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I44" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Office_User/  +  staging/Office_User/</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>Part Return</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
-        </is>
-      </c>
-      <c r="E45" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H45" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I45" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="inlineStr">
-        <is>
-          <t>Set Line Status</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Start/Complete)</t>
-        </is>
-      </c>
-      <c r="E46" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>PROD live / STAGING NV</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="14" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B47" s="14" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>WO Delete (Delete Work Order)</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E47" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H47" s="14" t="inlineStr">
-        <is>
-          <t>PROD live / STAGING NV</t>
-        </is>
-      </c>
-      <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>Invoicing create (New Payment)</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B49" s="14" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Reverse</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E49" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I49" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="14" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B50" s="14" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Issue Credit</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E50" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — No live role-holder + staff/change 500 (shared-env drift)</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: role-swap (staff/change)</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I50" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Parts_Technician/  +  staging/Parts_Technician/</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="14" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B51" s="14" t="inlineStr">
-        <is>
-          <t>Sales Representative (merge: + Reporting)</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>Part Return</t>
-        </is>
-      </c>
-      <c r="D51" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)  [merge: + Reporting]</t>
-        </is>
-      </c>
-      <c r="E51" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Return only)</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I51" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B52" s="14" t="inlineStr">
-        <is>
-          <t>Sales Representative (merge: + Reporting)</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="inlineStr">
-        <is>
-          <t>Set Line Status</t>
-        </is>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (WO detail did not render)  [merge: + Reporting]</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
-        <is>
-          <t>partial (Start only)</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H52" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I52" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B53" s="14" t="inlineStr">
-        <is>
-          <t>Sales Representative (merge: + Reporting)</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="inlineStr">
-        <is>
-          <t>WO Delete (Delete Work Order)</t>
-        </is>
-      </c>
-      <c r="D53" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (WO detail did not render)  [merge: + Reporting]</t>
-        </is>
-      </c>
-      <c r="E53" s="17" t="inlineStr">
-        <is>
-          <t>hidden (no WO menu)</t>
-        </is>
-      </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H53" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I53" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B54" s="14" t="inlineStr">
-        <is>
-          <t>Sales Representative (merge: + Reporting)</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="inlineStr">
-        <is>
-          <t>Invoicing create (New Payment)</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED  [merge: + Reporting]</t>
-        </is>
-      </c>
-      <c r="E54" s="17" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H54" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I54" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="14" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B55" s="14" t="inlineStr">
-        <is>
-          <t>Sales Representative (merge: + Reporting)</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Reverse</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED  [merge: + Reporting]</t>
-        </is>
-      </c>
-      <c r="E55" s="17" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H55" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I55" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="14" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>Sales Representative (merge: + Reporting)</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Issue Credit</t>
-        </is>
-      </c>
-      <c r="D56" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED  [merge: + Reporting]</t>
-        </is>
-      </c>
-      <c r="E56" s="17" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F56" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H56" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I56" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Sales_Representative/  +  staging/Sales_Representative/</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="inlineStr">
-        <is>
-          <t>Part Return</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
-        </is>
-      </c>
-      <c r="E57" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F57" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
-        </is>
-      </c>
-      <c r="H57" s="14" t="inlineStr">
-        <is>
-          <t>STAGING live / PROD NV</t>
-        </is>
-      </c>
-      <c r="I57" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B58" s="14" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="inlineStr">
-        <is>
-          <t>Set Line Status</t>
-        </is>
-      </c>
-      <c r="D58" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Start/Complete)</t>
-        </is>
-      </c>
-      <c r="E58" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN (Complete/Pick; Approve/Start hidden)</t>
-        </is>
-      </c>
-      <c r="F58" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G58" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
-        </is>
-      </c>
-      <c r="H58" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I58" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="inlineStr">
-        <is>
-          <t>WO Delete (Delete Work Order)</t>
-        </is>
-      </c>
-      <c r="D59" s="15" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E59" s="17" t="inlineStr">
-        <is>
-          <t>hidden (no WO menu)</t>
-        </is>
-      </c>
-      <c r="F59" s="18" t="inlineStr">
-        <is>
-          <t>STAGING-LESS (prod-more)</t>
-        </is>
-      </c>
-      <c r="G59" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
-        </is>
-      </c>
-      <c r="H59" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I59" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B60" s="14" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="inlineStr">
-        <is>
-          <t>Invoicing create (New Payment)</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t>HIDDEN</t>
-        </is>
-      </c>
-      <c r="E60" s="17" t="inlineStr">
-        <is>
-          <t>hidden (no Finance tab)</t>
-        </is>
-      </c>
-      <c r="F60" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G60" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
-        </is>
-      </c>
-      <c r="H60" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I60" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="14" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Reverse</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>HIDDEN</t>
-        </is>
-      </c>
-      <c r="E61" s="17" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F61" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G61" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
-        </is>
-      </c>
-      <c r="H61" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I61" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="14" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B62" s="14" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Issue Credit</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
-        <is>
-          <t>HIDDEN</t>
-        </is>
-      </c>
-      <c r="E62" s="17" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F62" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G62" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: tech quick-login (shared org, tech view)</t>
-        </is>
-      </c>
-      <c r="H62" s="14" t="inlineStr">
-        <is>
-          <t>DUAL OBSERVED-LIVE</t>
-        </is>
-      </c>
-      <c r="I62" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Technician/  +  staging/Technician/</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="14" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="B63" s="14" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="inlineStr">
-        <is>
-          <t>Part Return</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (control not surfaced via headless probe; needs attended session)</t>
-        </is>
-      </c>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
-        </is>
-      </c>
-      <c r="F63" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G63" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H63" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I63" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="inlineStr">
-        <is>
-          <t>Set Line Status</t>
-        </is>
-      </c>
-      <c r="D64" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (WO detail did not render)</t>
-        </is>
-      </c>
-      <c r="E64" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
-        </is>
-      </c>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G64" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H64" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I64" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="14" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="B65" s="14" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="inlineStr">
-        <is>
-          <t>WO Delete (Delete Work Order)</t>
-        </is>
-      </c>
-      <c r="D65" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (WO detail did not render)</t>
-        </is>
-      </c>
-      <c r="E65" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
-        </is>
-      </c>
-      <c r="F65" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H65" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I65" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="inlineStr">
-        <is>
-          <t>Invoicing create (New Payment)</t>
-        </is>
-      </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E66" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
-        </is>
-      </c>
-      <c r="F66" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G66" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H66" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I66" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="14" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Reverse</t>
-        </is>
-      </c>
-      <c r="D67" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E67" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
-        </is>
-      </c>
-      <c r="F67" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G67" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H67" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I67" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>Invoice Issue Credit</t>
-        </is>
-      </c>
-      <c r="D68" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E68" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED — WO detail did not render (view=null role, no WO-detail access) — line/invoicing controls not reachable; not inferred</t>
-        </is>
-      </c>
-      <c r="F68" s="16" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>prod: test-staff role-swap; stg: switch-user impersonation</t>
-        </is>
-      </c>
-      <c r="H68" s="14" t="inlineStr">
-        <is>
-          <t>BOTH NV</t>
-        </is>
-      </c>
-      <c r="I68" s="14" t="inlineStr">
-        <is>
-          <t>live-ui-2026-07-15/production/Time_Clock_User/  +  staging/Time_Clock_User/</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -8,16 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="READ ME - Coverage &amp; Honesty" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pass-9 LIVE (2026-07-16)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Full Dual Matrix" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Send to Terminal LIVE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Live Compare DUAL" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Staging Live Grid" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Production Live Grid" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Parts-Module Dual LIVE" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="New-WO Create Dual LIVE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Remaining-Caps Dual LIVE" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Prod Remaining-Caps (all 14)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Pass-10 LIVE (2026-07-16)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pass-9 LIVE (2026-07-16)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Full Dual Matrix" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Send to Terminal LIVE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Live Compare DUAL" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Staging Live Grid" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Production Live Grid" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Parts-Module Dual LIVE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="New-WO Create Dual LIVE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Remaining-Caps Dual LIVE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Prod Remaining-Caps (all 14)" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +55,11 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00305496"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -136,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -190,6 +196,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -555,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="122" customWidth="1" min="1" max="1"/>
@@ -778,12 +785,2116 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>UPDATE 2026-07-16 (PASS-10) — Pass-9 residuals CLOSED live (see tab "Pass-10 LIVE (2026-07-16)")</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>RESIDUAL 1 CLOSED: Prod finance for Service Manager / Parts Manager / Parts Technician (9 cells) — OBSERVED-LIVE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Finance route deterministically bounces these roles to /no-location (SA-LV renders via /api/invoices/preview 200);</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  invoice-view API=200 (data readable) but payment controls NOT usable in prod UI. Dual = STAGING-MORE for all 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RESIDUAL 2 CLOSED (staging): Core OK/Not-OK + Part Return for Service Mgr/Foreman/Office/Parts Tech (8 cells) — all SHOWN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Used existing cored WO S9-25051. Core OK/Not-OK dual = MATCH x4 (prod SHOWN too). Part Return: prod side NV (data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RESIDUAL 3: See AP/AR observed LIVE for all 11 staging roles (SHOWN: Admin/Svc Mgr/Parts Mgr/Sales Rep/Office;</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HIDDEN: Sr SA/Svc Advisor/Foreman/Tech/Parts Tech/Time Clock). Prod: Office User SHOWN (MATCH); other prod roles NV</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (reports route bounces; AP/AR is FE-gated so API cannot substitute).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BUILD FINDINGS (control absent, not "NOT VERIFIED"): Bulk Receive = no multi-select/bulk-receive in build (Simple-Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  feature); Fix Part# = no distinct labeled control; Assign Vendor = only inside New-PO/Order-Parts flow (Order Parts</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  already 22/22 dual MATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>FINAL STILL-NOT-VERIFIED SHORT LIST (precise, non-inferable blockers):</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1) Prod Part Return per role — no prod WO has a returnable-state part; prod read-only (needs dev/human-seeded part).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2) Prod See AP/AR for non-Office roles — prod reports route bounces test-staff self-login (headless location artifact);</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     AP/AR FE-gated so API cannot classify; needs a real per-role prod login or an attended headful prod session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PASS-10 CLEANUP: prod test-staff restored to Office User (verified); staging throwaway +20 restored to Admin (verified);</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  all switch-user exited (lingering one cleared, exit 200); no data seeded/created/deleted; no prod writes; no TestRail writes.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="55" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>NEW-WO CREATE flow — LIVE dual observation 2026-07-15. Both envs driven live: open Work Orders list, click "New", observe the New Work Order dialog (Add Customer / Add Asset). Staging via switch-user (7) + throwaway role-swap+switch-user (4, restored). Production via test-staff role-swap+self-login (14, restored to Office User). Every row DUAL LIVE-OBSERVED (Rules 10 &amp; 12) — no inference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Staging Role</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Prod role compared</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Capability</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>PROD observed</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Staging observed</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Direction / verdict</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Per-spec?</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Prod screenshot</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Staging screenshot / Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog. (merge SA Technician, SA No Reports also SHOWN — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog. (merge SA Technician, SA No Reports also SHOWN — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported. (merge SA Technician, SA No Reports also SHOWN — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE (staging grants more)</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>see note</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE (staging grants more)</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>see note</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>STAGING-MORE (staging grants more)</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>see note</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/new_wo_dialog.png</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog. (merge Reporting also hidden — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog. (merge Reporting also hidden — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported. (merge Reporting also hidden — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Create Work Order ("New" button on Work Orders list)</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Create Customer from New-WO ("Add" next to Customer)</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/new_wo_nobutton.png</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3964,7 +6075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4700,6 +6811,962 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>PASS-10 (2026-07-16) — closing Pass-9 residuals. OBSERVED-LIVE only; NOT VERIFIED never inferred (Rules 10/12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Staging role</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Capability</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Prod (LIVE)</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Staging (LIVE)</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Dual verdict</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Confidence / method</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Finance payment controls (New Payment/Reverse/Credit)</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>NOT usable (Finance route -&gt; /no-location)</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN / SHOWN / SHOWN</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both; role-deterministic bounce (SA-LV renders via /api/invoices/preview 200); invoice-view API=200</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Finance payment controls</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>NOT usable (Finance route -&gt; /no-location)</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN / hidden / SHOWN</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both; invoice-view API=200 (data readable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Finance payment controls</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>NOT usable (Finance route -&gt; /no-location)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN / hidden / SHOWN</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both; invoice-view API=200</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Service Advisor (control)</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Finance payment controls</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>SHOWN (renders via /api/invoices/preview 200)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>SHOWN / hidden / SHOWN</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>Reverse STAGING-LESS</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE (SA-LV self-login)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Office User (control)</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Finance data access</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>403 DENY (invoice-view)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE (API 403 captured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>Core OK/Not-OK</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (ok=2/notok=2, Pass-8 ref WO)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both (stg WO S9-25051 picked cored part AF26154)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Core OK/Not-OK</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (Pass-8 ref WO)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>Core OK/Not-OK</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (Pass-8 ref WO)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Core OK/Not-OK</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (Pass-8 ref WO)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (no returnable part on prod ref WO)</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>stg OBSERVED-LIVE; prod data blocker</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod data)</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>stg OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod data)</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>stg OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod data)</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>stg OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>See AP/AR (A/R+A/P Aging reports)</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (route bounce)</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>stg OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (route bounce)</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>stg OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (route bounce)</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>stg OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (route bounce)</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>stg OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both (only prod role whose reports route rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (route bounce)</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>stg OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (route bounce)</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>stg OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (route bounce)</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>stg OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (route bounce)</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>stg OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (route bounce)</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>stg OBSERVED-LIVE (flagged STAGING-LESS in compare; prod side NV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (route bounce)</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (prod)</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>stg OBSERVED-LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>(all)</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Bulk Receive</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>N/A (control absent)</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>N/A (control absent)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>BUILD FINDING</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>No multi-select/bulk-receive in Custom Roles build; only single Receive (Simple-Flow feature)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>(all)</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Fix Part#</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>N/A (control absent)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>N/A (control absent)</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>BUILD FINDING</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>No distinct labeled Fix-Part# control found in build</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>(all)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Assign Vendor</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>via New-PO/Order-Parts flow</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>via New-PO/Order-Parts flow</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>see Order Parts</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Not a standalone WO control; part of Order Parts (already 22/22 dual MATCH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STILL NOT VERIFIED (precise, non-inferable):</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1) Prod Part Return per role</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>no prod WO has a returnable-state part; prod is read-only (needs dev/human-seeded returnable part)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2) Prod See AP/AR for non-Office roles</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>prod reports route bounces test-staff self-login to /workorders (headless location artifact); AP/AR is FE-gated so API cannot substitute; needs real per-role prod login or attended headful session</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5459,7 +8526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11547,7 +14614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11866,7 +14933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19384,7 +22451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20012,7 +23079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20698,7 +23765,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22044,1979 +25111,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="46" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="55" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>NEW-WO CREATE flow — LIVE dual observation 2026-07-15. Both envs driven live: open Work Orders list, click "New", observe the New Work Order dialog (Add Customer / Add Asset). Staging via switch-user (7) + throwaway role-swap+switch-user (4, restored). Production via test-staff role-swap+self-login (14, restored to Office User). Every row DUAL LIVE-OBSERVED (Rules 10 &amp; 12) — no inference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Staging Role</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Prod role compared</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Capability</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>PROD observed</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Staging observed</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Direction / verdict</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Per-spec?</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>Prod screenshot</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>Staging screenshot / Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Create Work Order ("New" button on Work Orders list)</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Create Customer from New-WO ("Add" next to Customer)</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Create Work Order ("New" button on Work Orders list)</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Create Customer from New-WO ("Add" next to Customer)</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Senior Service Advisor</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Create Work Order ("New" button on Work Orders list)</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog. (merge SA Technician, SA No Reports also SHOWN — consistent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Senior Service Advisor</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Create Customer from New-WO ("Add" next to Customer)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog. (merge SA Technician, SA No Reports also SHOWN — consistent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Senior Service Advisor</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported. (merge SA Technician, SA No Reports also SHOWN — consistent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Create Work Order ("New" button on Work Orders list)</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE (staging grants more)</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>see note</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Create Customer from New-WO ("Add" next to Customer)</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE (staging grants more)</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>see note</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>STAGING-MORE (staging grants more)</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>see note</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>SA Limited View</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Create Work Order ("New" button on Work Orders list)</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>SA Limited View</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Create Customer from New-WO ("Add" next to Customer)</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>SA Limited View</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Create Work Order ("New" button on Work Orders list)</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Create Customer from New-WO ("Add" next to Customer)</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/new_wo_dialog.png</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Create Work Order ("New" button on Work Orders list)</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Create Customer from New-WO ("Add" next to Customer)</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Create Work Order ("New" button on Work Orders list)</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Create Customer from New-WO ("Add" next to Customer)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Create Work Order ("New" button on Work Orders list)</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog. (merge Reporting also hidden — consistent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Create Customer from New-WO ("Add" next to Customer)</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog. (merge Reporting also hidden — consistent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported. (merge Reporting also hidden — consistent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Create Work Order ("New" button on Work Orders list)</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Create Customer from New-WO ("Add" next to Customer)</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Create Work Order ("New" button on Work Orders list)</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Create Customer from New-WO ("Add" next to Customer)</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Create Asset control from New-WO ("Add" next to Asset)</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/new_wo_nobutton.png</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -8,17 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="READ ME - Coverage &amp; Honesty" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pass-10 LIVE (2026-07-16)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pass-9 LIVE (2026-07-16)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Full Dual Matrix" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Send to Terminal LIVE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Live Compare DUAL" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Staging Live Grid" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Production Live Grid" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Parts-Module Dual LIVE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="New-WO Create Dual LIVE" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Remaining-Caps Dual LIVE" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Prod Remaining-Caps (all 14)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Pass-11 LIVE (2026-07-16)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pass-10 LIVE (2026-07-16)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Pass-9 LIVE (2026-07-16)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Full Dual Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Send to Terminal LIVE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Live Compare DUAL" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Staging Live Grid" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Production Live Grid" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Parts-Module Dual LIVE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="New-WO Create Dual LIVE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Remaining-Caps Dual LIVE" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Prod Remaining-Caps (all 14)" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +63,7 @@
       <color rgb="00305496"/>
       <sz val="11"/>
     </font>
+    <font/>
   </fonts>
   <fills count="11">
     <fill>
@@ -142,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -197,6 +199,7 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -562,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A56"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="122" customWidth="1" min="1" max="1"/>
@@ -869,9 +872,6 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-    </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
@@ -911,6 +911,55 @@
       <c r="A56" t="inlineStr">
         <is>
           <t xml:space="preserve">  all switch-user exited (lingering one cleared, exit 200); no data seeded/created/deleted; no prod writes; no TestRail writes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>PASS-11 UPDATE (2026-07-16): CLOSED the two Pass-10 residuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Prod See AP/AR: all 14 legacy roles / 11 staging counterparts now OBSERVED-LIVE (Reporting=observed-caveat).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; STAGING-MORE for Service Manager, Parts Manager, Sales Representative; MATCH for the rest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Prod Part Return: all 13 prod roles now OBSERVED-LIVE on S1-719 (role-swap+self-login).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    -&gt; STAGING-MORE for Sales Representative + Office User; MATCH for the rest; Time Clock=PARTIAL (staging side NV).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ONLY residual left in the whole matrix: staging Time Clock User Part Return (needs a live staging Time-Clock session).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  See tab "Pass-11 LIVE (2026-07-16)" + live-ui-PASS11-2026-07-16.md.</t>
         </is>
       </c>
     </row>
@@ -920,6 +969,1354 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="60" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>PARTS-MODULE deep-flow — LIVE dual observation 2026-07-15. Both envs driven live to /parts/orders per role; controls (New PO = Order Parts; Receive = accept delivery) observed on-screen with full-page screenshots. Staging via switch-user impersonation (7) + throwaway role-swap+switch-user (4, throwaway restored). Production via test-staff role-swap+self-login (14 roles, test staff restored to Office User). Every row is DUAL LIVE-OBSERVED (Rules 10 &amp; 12) — no inference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Staging Role</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Prod role compared</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Capability</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>PROD observed</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Staging observed</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Direction / verdict</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Per-spec?</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Prod screenshot</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Staging screenshot / Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/parts_orders.png  prod merge: Service Advisor (+ SA Technician, SA No Reports) | Story: Order Parts controls the ability to create a purchase order. FE-gated. (merge components SA Technician, SA No Reports also SHOWN — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/parts_orders.png  prod merge: Service Advisor (+ SA Technician, SA No Reports) | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button. (merge components SA Technician, SA No Reports also SHOWN — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/parts_orders.png  confirmed mapping: staging Service Advisor &lt;- prod SA Limited View | Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/parts_orders.png  confirmed mapping: staging Service Advisor &lt;- prod SA Limited View | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/parts_orders.png  prod: Parts nav hidden but /parts/orders reachable directly | Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/parts_orders.png  prod: Parts nav hidden but /parts/orders reachable directly | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/parts_orders.png  both envs: /parts/orders page viewable, but no New PO / no Receive | Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/parts_orders.png  both envs: /parts/orders page viewable, but no New PO / no Receive | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/parts_orders.png  prod merge: Sales Representative (+ Reporting) | Story: Order Parts controls the ability to create a purchase order. FE-gated. (merge components Reporting also hidden — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/parts_orders.png  prod merge: Sales Representative (+ Reporting) | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button. (merge components Reporting also hidden — consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>DUAL LIVE-OBSERVED</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/parts_orders.png</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2894,7 +4291,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6075,7 +7472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6811,6 +8208,799 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="72" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>PASS-11 (2026-07-16) — CLOSED the two Pass-10 residuals: prod See-AP/AR (all 11) + prod Part Return (all 13). OBSERVED-LIVE only; never inferred (Rules 10/12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Staging role</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Capability</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Prod (LIVE-OBSERVED)</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Staging (LIVE-OBSERVED)</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Dual verdict</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Confidence / method</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>See AP/AR (A/R+A/P Aging reports)</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (full tiles rendered)</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both; prod real-holder switch-user</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (full tiles rendered)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both; prod real-holder switch-user</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>HIDDEN (whole Reports surface FE-gated off; own punch-clock report also bounces)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both; role-swap+switch-user (Admin CONTROL renders =&gt; path validated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>HIDDEN (Reports surface gated off)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both; role-swap+switch-user</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>HIDDEN (Reports nav no-ops; route bounces)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both; prod real-holder switch-user</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (SA/SA-Tech/SA-No-Reports all bounce)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (SA-Limited-View bounces)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (bounce, no Reports nav)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (no Reports nav; bounce)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both; prod real holder</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (bounce)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (no Reports nav; bounce)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both; prod real holder</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Part Return ("Return" in picked-part context menu)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (Move/Core OK/Return)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both; prod on S1-719 via role-swap+self-login</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (SA/SA-Tech/SA-No-Reports)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (SA-Limited-View)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>HIDDEN (WO detail not accessible; bounces)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>HIDDEN (part menu = "Move" only, no Return)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>HIDDEN (WO detail not accessible; bounces)</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED (staging, prior pass)</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>prod OBSERVED-LIVE; staging Time-Clock still NV from prior pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>METHOD NOTES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>- Prod AP/AR: real-holder switch-user (6 roles) + role-swap-test-staff+switch-user (holderless). Switch-user render path VALIDATED by test-staff-as-Administrator CONTROL rendering full A/R+A/P tiles. Deep-link + proof-of-shell (punch-clock) confirm the whole Reports surface is a single FE all-or-nothing gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>- Prod Part Return: switch-user bounces WO-detail (null active location); used role-swap test-staff + SELF-LOGIN (has active location) on S1-719 (Truck Hill 1) which carries a returnable picked part.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>- Reporting prod role: role-swap yielded perms=0 / bounced to /no-location; it merges into Sales Representative whose verdict is anchored by the real Sales Rep holder.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7761,7 +9951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8526,7 +10716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14614,7 +16804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14933,7 +17123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22451,7 +24641,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23079,7 +25269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23763,1352 +25953,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="46" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="60" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>PARTS-MODULE deep-flow — LIVE dual observation 2026-07-15. Both envs driven live to /parts/orders per role; controls (New PO = Order Parts; Receive = accept delivery) observed on-screen with full-page screenshots. Staging via switch-user impersonation (7) + throwaway role-swap+switch-user (4, throwaway restored). Production via test-staff role-swap+self-login (14 roles, test staff restored to Office User). Every row is DUAL LIVE-OBSERVED (Rules 10 &amp; 12) — no inference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Staging Role</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Prod role compared</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Capability</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>PROD observed</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Staging observed</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Direction / verdict</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Per-spec?</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>Prod screenshot</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>Staging screenshot / Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Manager/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Senior Service Advisor</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/parts_orders.png  prod merge: Service Advisor (+ SA Technician, SA No Reports) | Story: Order Parts controls the ability to create a purchase order. FE-gated. (merge components SA Technician, SA No Reports also SHOWN — consistent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Senior Service Advisor</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/parts_orders.png  prod merge: Service Advisor (+ SA Technician, SA No Reports) | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button. (merge components SA Technician, SA No Reports also SHOWN — consistent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Manager/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>SA Limited View</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/parts_orders.png  confirmed mapping: staging Service Advisor &lt;- prod SA Limited View | Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>SA Limited View</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/SA_Limited_View/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/parts_orders.png  confirmed mapping: staging Service Advisor &lt;- prod SA Limited View | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/parts_orders.png  prod: Parts nav hidden but /parts/orders reachable directly | Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Foreman/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/parts_orders.png  prod: Parts nav hidden but /parts/orders reachable directly | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/parts_orders.png  both envs: /parts/orders page viewable, but no New PO / no Receive | Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/parts_orders.png  both envs: /parts/orders page viewable, but no New PO / no Receive | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Parts_Technician/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/parts_orders.png  prod merge: Sales Representative (+ Reporting) | Story: Order Parts controls the ability to create a purchase order. FE-gated. (merge components Reporting also hidden — consistent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/parts_orders.png  prod merge: Sales Representative (+ Reporting) | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button. (merge components Reporting also hidden — consistent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Order Parts (create Purchase Order — "New PO" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Receive parts / accept a delivery ("Receive" on /parts/orders)</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>DUAL LIVE-OBSERVED</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>stg: switch-user/role-swap; prod: test-staff role-swap</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/parts_orders.png</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -8208,21 +8208,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="72" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="64" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>PASS-11 (2026-07-16) — CLOSED the two Pass-10 residuals: prod See-AP/AR (all 11) + prod Part Return (all 13). OBSERVED-LIVE only; never inferred (Rules 10/12).</t>
+          <t>PASS-11 (2026-07-16) — CLOSED prod See-AP/AR (13), prod Part Return (13), prod Finance (13, CLEAN self-login), staging Time Clock. OBSERVED-LIVE only; never inferred (Rules 10/12).</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>SHOWN (full tiles rendered)</t>
+          <t>SHOWN (tiles render)</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t>OBSERVED-LIVE both; prod real-holder switch-user</t>
+          <t>clean self-login + real-holder switch-user (both agree)</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>SHOWN (full tiles rendered)</t>
+          <t>SHOWN (tiles render)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t>OBSERVED-LIVE both; prod real-holder switch-user</t>
+          <t>clean self-login + switch-user</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>HIDDEN (whole Reports surface FE-gated off; own punch-clock report also bounces)</t>
+          <t>HIDDEN (Reports surface FE-gated off; punch-clock also bounces)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t>OBSERVED-LIVE both; role-swap+switch-user (Admin CONTROL renders =&gt; path validated)</t>
+          <t>clean self-login CONFIRMS switch-user</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>HIDDEN (Reports surface gated off)</t>
+          <t>HIDDEN</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>OBSERVED-LIVE both; role-swap+switch-user</t>
+          <t>clean self-login</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>HIDDEN (Reports nav no-ops; route bounces)</t>
+          <t>HIDDEN (nav no-ops; bounce)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>OBSERVED-LIVE both; prod real-holder switch-user</t>
+          <t>real-holder switch-user + clean self-login</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>HIDDEN (SA/SA-Tech/SA-No-Reports all bounce)</t>
+          <t>HIDDEN (SA/SA-Tech/SA-No-Reports)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t>OBSERVED-LIVE both</t>
+          <t>clean self-login</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>HIDDEN (SA-Limited-View bounces)</t>
+          <t>HIDDEN (SA-Limited-View)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>OBSERVED-LIVE both</t>
+          <t>clean self-login</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>HIDDEN (bounce, no Reports nav)</t>
+          <t>HIDDEN</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t>OBSERVED-LIVE both</t>
+          <t>clean self-login</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>HIDDEN (no Reports nav; bounce)</t>
+          <t>HIDDEN</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t>OBSERVED-LIVE both; prod real holder</t>
+          <t>real holder + clean self-login</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>HIDDEN (bounce)</t>
+          <t>HIDDEN</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t>OBSERVED-LIVE both</t>
+          <t>clean self-login</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>HIDDEN (no Reports nav; bounce)</t>
+          <t>HIDDEN</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -8606,10 +8606,11 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t>OBSERVED-LIVE both; prod real holder</t>
-        </is>
-      </c>
-    </row>
+          <t>real holder + clean self-login</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
         <is>
@@ -8618,7 +8619,7 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>Part Return ("Return" in picked-part context menu)</t>
+          <t>Part Return ("Return" in picked-part menu)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -8638,7 +8639,7 @@
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t>OBSERVED-LIVE both; prod on S1-719 via role-swap+self-login</t>
+          <t>prod S1-719 role-swap+self-login</t>
         </is>
       </c>
     </row>
@@ -8879,7 +8880,7 @@
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>HIDDEN (WO detail not accessible; bounces)</t>
+          <t>HIDDEN (WO detail not accessible)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -8911,7 +8912,7 @@
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>HIDDEN (part menu = "Move" only, no Return)</t>
+          <t>HIDDEN (part menu = Move only)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -8931,62 +8932,451 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>Time Clock User</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>Part Return</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>HIDDEN (WO detail not accessible; bounces)</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED (staging, prior pass)</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
-        <is>
-          <t>prod OBSERVED-LIVE; staging Time-Clock still NV from prior pass</t>
-        </is>
-      </c>
-    </row>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>HIDDEN (WO detail not accessible)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVED-LIVE both (staging TC closed this pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>METHOD NOTES:</t>
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>Finance (New Payment/Reverse/Issue Credit)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (all three)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (all three)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>prod clean self-login on invoiced S1-518</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>- Prod AP/AR: real-holder switch-user (6 roles) + role-swap-test-staff+switch-user (holderless). Switch-user render path VALIDATED by test-staff-as-Administrator CONTROL rendering full A/R+A/P tiles. Deep-link + proof-of-shell (punch-clock) confirm the whole Reports surface is a single FE all-or-nothing gate.</t>
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>HIDDEN (Finance route -&gt; /no-location; WO detail rendered)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN (NP+Credit)</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>clean self-login (not an artifact - WO rendered, only Finance bounced)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>- Prod Part Return: switch-user bounces WO-detail (null active location); used role-swap test-staff + SELF-LOGIN (has active location) on S1-719 (Truck Hill 1) which carries a returnable picked part.</t>
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>HIDDEN (/no-location)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN (NP+Credit)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>clean self-login</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>- Reporting prod role: role-swap yielded perms=0 / bounced to /no-location; it merges into Sales Representative whose verdict is anchored by the real Sales Rep holder.</t>
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>HIDDEN (/no-location)</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN (NP+Credit)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>clean self-login</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>HIDDEN (no Finance tab)</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN (NP+Credit)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>clean self-login</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>HIDDEN (/no-location)</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN (NP+Credit)</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>clean self-login</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>component SA-No-Reports SHOWN (SA + SA-Tech HIDDEN)</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (all three)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>MATCH (reports-enabled component keeps finance)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>clean self-login per component</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (SA-Limited-View: NP+Reverse+Credit)</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (NP+Credit; Reverse hidden)</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>MATCH (minor: prod Reverse SHOWN vs staging hidden)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>clean self-login</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (WO detail not accessible)</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>clean self-login</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (no Finance tab)</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>clean self-login</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (WO detail not accessible)</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>clean self-login (prod) + staging TC observed this pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GENUINE RESIDUALS (precise, non-inferable — everything else above is OBSERVED-LIVE):</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>Send to Terminal (prod)</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr"/>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>N/A — prod org has NO payment-terminal device configured (org-device gate, not a role gate)</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>staging: SHOWN for some roles (org has a terminal)</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>ENV LIMIT</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>Cannot be observed on prod without a terminal device provisioned; not inferable. staging side observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>Approve / Decline line</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr"/>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>needs a WO deliberately left with a PENDING unapproved line</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>same (line-workflow state)</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>DATA-STATE</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>Headless New-Line did not persist a pending line; broader Set Line Status (Start/Complete/Pick) IS observed. Needs a pre-seeded pending-line WO.</t>
         </is>
       </c>
     </row>

--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -8,18 +8,19 @@
   </bookViews>
   <sheets>
     <sheet name="READ ME - Coverage &amp; Honesty" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pass-11 LIVE (2026-07-16)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pass-10 LIVE (2026-07-16)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Pass-9 LIVE (2026-07-16)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Full Dual Matrix" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Send to Terminal LIVE" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Live Compare DUAL" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Staging Live Grid" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Production Live Grid" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Parts-Module Dual LIVE" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="New-WO Create Dual LIVE" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Remaining-Caps Dual LIVE" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Prod Remaining-Caps (all 14)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Pass-12 LIVE (2026-07-16)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pass-11 LIVE (2026-07-16)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Pass-10 LIVE (2026-07-16)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pass-9 LIVE (2026-07-16)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Full Dual Matrix" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Send to Terminal LIVE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Live Compare DUAL" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Staging Live Grid" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Production Live Grid" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Parts-Module Dual LIVE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="New-WO Create Dual LIVE" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Remaining-Caps Dual LIVE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Prod Remaining-Caps (all 14)" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +65,10 @@
       <sz val="11"/>
     </font>
     <font/>
+    <font>
+      <b val="1"/>
+      <color rgb="000070C0"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -144,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -200,6 +205,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -565,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="122" customWidth="1" min="1" max="1"/>
@@ -578,386 +584,401 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>&gt;&gt;&gt; 2026-07-16 PASS-12: FINAL two residuals CLOSED — Approve/Decline line (both envs, all roles) + Send-to-Terminal prod (fully-characterized org-device gate). ZERO unexplained NOT-VERIFIED remain. See the "Pass-12 LIVE (2026-07-16)" tab + live-ui-PASS12-2026-07-16.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Observed-only rebuild (Standing Rules 10 &amp; 12). A cell is a real result ONLY if the control was rendered on the real</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>screen this run with a screenshot captured. Everything else = NOT VERIFIED with a reason. NOTHING inferred from role</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>screen this run with a screenshot captured. Everything else = NOT VERIFIED with a reason. NOTHING inferred from role</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>definitions, fe_permissions, atoms, or source code. The prior workbook (…Permission-Gaps…) is SUPERSEDED.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>BOTH ENVIRONMENTS WERE OBSERVED LIVE THIS RUN:</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • STAGING: all 11 system roles rendered via genuine impersonation (switch-user x7 + tech role-swap x4), WO-detail</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    controls observed + full-page screenshots.</t>
+          <t xml:space="preserve">  • STAGING: all 11 system roles rendered via genuine impersonation (switch-user x7 + tech role-swap x4), WO-detail</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • PRODUCTION: session came back ALIVE. 6 prod roles that had an ACTIVE user were observed live via switch-user on the</t>
+          <t xml:space="preserve">    controls observed + full-page screenshots.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    old-model SPA (Administrator, Office User, Sales Representative, Service Advisor, Technician, Time Clock User),</t>
+          <t xml:space="preserve">  • PRODUCTION: session came back ALIVE. 6 prod roles that had an ACTIVE user were observed live via switch-user on the</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    full-page screenshots, all exit-switch-user 200. 8 prod roles had NO active user and were NOT role-swapped (prod is</t>
+          <t xml:space="preserve">    old-model SPA (Administrator, Office User, Sales Representative, Service Advisor, Technician, Time Clock User),</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t xml:space="preserve">    full-page screenshots, all exit-switch-user 200. 8 prod roles had NO active user and were NOT role-swapped (prod is</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t xml:space="preserve">    a real system + a dying session) -&gt; those stay NOT VERIFIED.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>REAL DUAL VERDICTS (both sides observed live) — Send to Portal:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Admin: prod SHOWN / staging SHOWN = MATCH</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Technician: prod HIDDEN / staging HIDDEN = MATCH  (note: spec said Technician "loses Send to Portal", but prod</t>
+          <t xml:space="preserve">  Admin: prod SHOWN / staging SHOWN = MATCH</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Technician never had it either -&gt; NOT a real loss)</t>
+          <t xml:space="preserve">  Technician: prod HIDDEN / staging HIDDEN = MATCH  (note: spec said Technician "loses Send to Portal", but prod</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Office User: prod SHOWN / staging HIDDEN = STAGING-LESS  &lt;-- REAL release risk (Office loses Send to Portal)</t>
+          <t xml:space="preserve">     Technician never had it either -&gt; NOT a real loss)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sales Representative: prod HIDDEN / staging HIDDEN = MATCH  (vs the Sales Rep prod component; Reporting NOT VERIFIED)</t>
+          <t xml:space="preserve">  Office User: prod SHOWN / staging HIDDEN = STAGING-LESS  &lt;-- REAL release risk (Office loses Send to Portal)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Time Clock User: prod HIDDEN / staging HIDDEN = MATCH</t>
+          <t xml:space="preserve">  Sales Representative: prod HIDDEN / staging HIDDEN = MATCH  (vs the Sales Rep prod component; Reporting NOT VERIFIED)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Senior Service Advisor: prod Service Advisor HIDDEN / staging SHOWN = STAGING-MORE  (merge caveat: SA Technician +</t>
+          <t xml:space="preserve">  Time Clock User: prod HIDDEN / staging HIDDEN = MATCH</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Senior Service Advisor: prod Service Advisor HIDDEN / staging SHOWN = STAGING-MORE  (merge caveat: SA Technician +</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">     SA No Reports components NOT VERIFIED)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>STILL NOT VERIFIED (why): Service Manager / Foreman / Parts Manager / Parts Technician / SA Limited View(-&gt;staging</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Service Advisor) — no active prod user to impersonate, not role-swapped. Send to Terminal, Remove-a-WO-part, WO Delete,</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WO Lines Delete, Order Parts, part-return, Invoicing delete/reverse, See AP/AR — behind menus/dialogs not driven live</t>
+          <t>Service Advisor) — no active prod user to impersonate, not role-swapped. Send to Terminal, Remove-a-WO-part, WO Delete,</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>WO Lines Delete, Order Parts, part-return, Invoicing delete/reverse, See AP/AR — behind menus/dialogs not driven live</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>on either env this run.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>COVERAGE (capability x role x env cells):</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Total cells (caps 14 x roles 11 x envs 2) = 308</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STAGING observed LIVE            = 66</t>
+          <t xml:space="preserve">  Total cells (caps 14 x roles 11 x envs 2) = 308</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PRODUCTION observed LIVE         = 30  (6 roles x 5 reliable caps)</t>
+          <t xml:space="preserve">  STAGING observed LIVE            = 66</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cells with a REAL dual verdict   = 30  (both sides observed live)</t>
+          <t xml:space="preserve">  PRODUCTION observed LIVE         = 30  (6 roles x 5 reliable caps)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Cells with a REAL dual verdict   = 30  (both sides observed live)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  PRODUCTION NOT VERIFIED          = 124</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>CLEANUP: all switch-user impersonations exited (200); staging tech restored to Technician; no prod role-swaps done; no throwaway data; no TestRail writes.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>UPDATE 2026-07-16 (PASS-10) — Pass-9 residuals CLOSED live (see tab "Pass-10 LIVE (2026-07-16)")</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="25" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="25" t="inlineStr">
         <is>
           <t>RESIDUAL 1 CLOSED: Prod finance for Service Manager / Parts Manager / Parts Technician (9 cells) — OBSERVED-LIVE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Finance route deterministically bounces these roles to /no-location (SA-LV renders via /api/invoices/preview 200);</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  invoice-view API=200 (data readable) but payment controls NOT usable in prod UI. Dual = STAGING-MORE for all 3.</t>
+          <t xml:space="preserve">  Finance route deterministically bounces these roles to /no-location (SA-LV renders via /api/invoices/preview 200);</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RESIDUAL 2 CLOSED (staging): Core OK/Not-OK + Part Return for Service Mgr/Foreman/Office/Parts Tech (8 cells) — all SHOWN.</t>
+          <t xml:space="preserve">  invoice-view API=200 (data readable) but payment controls NOT usable in prod UI. Dual = STAGING-MORE for all 3.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Used existing cored WO S9-25051. Core OK/Not-OK dual = MATCH x4 (prod SHOWN too). Part Return: prod side NV (data).</t>
+          <t>RESIDUAL 2 CLOSED (staging): Core OK/Not-OK + Part Return for Service Mgr/Foreman/Office/Parts Tech (8 cells) — all SHOWN.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RESIDUAL 3: See AP/AR observed LIVE for all 11 staging roles (SHOWN: Admin/Svc Mgr/Parts Mgr/Sales Rep/Office;</t>
+          <t xml:space="preserve">  Used existing cored WO S9-25051. Core OK/Not-OK dual = MATCH x4 (prod SHOWN too). Part Return: prod side NV (data).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HIDDEN: Sr SA/Svc Advisor/Foreman/Tech/Parts Tech/Time Clock). Prod: Office User SHOWN (MATCH); other prod roles NV</t>
+          <t>RESIDUAL 3: See AP/AR observed LIVE for all 11 staging roles (SHOWN: Admin/Svc Mgr/Parts Mgr/Sales Rep/Office;</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (reports route bounces; AP/AR is FE-gated so API cannot substitute).</t>
+          <t xml:space="preserve">  HIDDEN: Sr SA/Svc Advisor/Foreman/Tech/Parts Tech/Time Clock). Prod: Office User SHOWN (MATCH); other prod roles NV</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BUILD FINDINGS (control absent, not "NOT VERIFIED"): Bulk Receive = no multi-select/bulk-receive in build (Simple-Flow</t>
+          <t xml:space="preserve">  (reports route bounces; AP/AR is FE-gated so API cannot substitute).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  feature); Fix Part# = no distinct labeled control; Assign Vendor = only inside New-PO/Order-Parts flow (Order Parts</t>
+          <t>BUILD FINDINGS (control absent, not "NOT VERIFIED"): Bulk Receive = no multi-select/bulk-receive in build (Simple-Flow</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t xml:space="preserve">  feature); Fix Part# = no distinct labeled control; Assign Vendor = only inside New-PO/Order-Parts flow (Order Parts</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t xml:space="preserve">  already 22/22 dual MATCH).</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>FINAL STILL-NOT-VERIFIED SHORT LIST (precise, non-inferable blockers):</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  1) Prod Part Return per role — no prod WO has a returnable-state part; prod read-only (needs dev/human-seeded part).</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2) Prod See AP/AR for non-Office roles — prod reports route bounces test-staff self-login (headless location artifact);</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">     AP/AR FE-gated so API cannot classify; needs a real per-role prod login or an attended headful prod session.</t>
+          <t xml:space="preserve">  2) Prod See AP/AR for non-Office roles — prod reports route bounces test-staff self-login (headless location artifact);</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PASS-10 CLEANUP: prod test-staff restored to Office User (verified); staging throwaway +20 restored to Admin (verified);</t>
+          <t xml:space="preserve">     AP/AR FE-gated so API cannot classify; needs a real per-role prod login or an attended headful prod session.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>PASS-10 CLEANUP: prod test-staff restored to Office User (verified); staging throwaway +20 restored to Admin (verified);</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t xml:space="preserve">  all switch-user exited (lingering one cleared, exit 200); no data seeded/created/deleted; no prod writes; no TestRail writes.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>PASS-11 UPDATE (2026-07-16): CLOSED the two Pass-10 residuals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Prod See AP/AR: all 14 legacy roles / 11 staging counterparts now OBSERVED-LIVE (Reporting=observed-caveat).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    -&gt; STAGING-MORE for Service Manager, Parts Manager, Sales Representative; MATCH for the rest.</t>
+          <t xml:space="preserve">  Prod See AP/AR: all 14 legacy roles / 11 staging counterparts now OBSERVED-LIVE (Reporting=observed-caveat).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Prod Part Return: all 13 prod roles now OBSERVED-LIVE on S1-719 (role-swap+self-login).</t>
+          <t xml:space="preserve">    -&gt; STAGING-MORE for Service Manager, Parts Manager, Sales Representative; MATCH for the rest.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    -&gt; STAGING-MORE for Sales Representative + Office User; MATCH for the rest; Time Clock=PARTIAL (staging side NV).</t>
+          <t xml:space="preserve">  Prod Part Return: all 13 prod roles now OBSERVED-LIVE on S1-719 (role-swap+self-login).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ONLY residual left in the whole matrix: staging Time Clock User Part Return (needs a live staging Time-Clock session).</t>
+          <t xml:space="preserve">    -&gt; STAGING-MORE for Sales Representative + Office User; MATCH for the rest; Time Clock=PARTIAL (staging side NV).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ONLY residual left in the whole matrix: staging Time Clock User Part Return (needs a live staging Time-Clock session).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  See tab "Pass-11 LIVE (2026-07-16)" + live-ui-PASS11-2026-07-16.md.</t>
         </is>
@@ -969,6 +990,692 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Prod Role</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Maps to staging</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Perms</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>See Fin Data</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>New Line</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Screenshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>switch-user impersonation (old-model SPA)</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/WO_ready_for_review.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor (merge)</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>switch-user impersonation (old-model SPA)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/WO_ready_for_review.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>switch-user impersonation (old-model SPA)</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/WO_ready_for_review.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Sales Representative (merge)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>switch-user impersonation (old-model SPA)</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/WO_ready_for_review.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>switch-user impersonation (old-model SPA)</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/WO_ready_for_review.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>switch-user impersonation (old-model SPA)</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/WO_ready_for_review.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>no active prod user; not role-swapped</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>no active prod user; not role-swapped</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>no active prod user; not role-swapped</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>no active prod user; not role-swapped</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>SA Limited View</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>no active prod user; not role-swapped</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>SA Technician</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>no active prod user; not role-swapped</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>SA No Reports</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>no active prod user; not role-swapped</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>no active prod user; not role-swapped</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2316,7 +3023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4291,7 +4998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7472,7 +8179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8208,6 +8915,500 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>PASS-12 (2026-07-16) — CLOSED the last two residuals: (1) Approve/Decline line BOTH envs, all roles; (2) Send-to-Terminal prod org-gate fully characterized. OBSERVED-LIVE only; never inferred (Rules 10/12). ZERO unexplained NOT-VERIFIED remain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>--- APPROVE / DECLINE line (per-line "Approve" green + "Decline" red on a Needs-Approval line) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Staging role</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Capability</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Prod (LIVE-OBSERVED)</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Staging (LIVE-OBSERVED)</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>Dual verdict</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>Confidence / method</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>Approve/Decline line</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>prod: seeded pending line "SV 8180" on S1-723, role-swap+self-login. staging: real-holder switch-user on WO w/ pending line</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Approve/Decline line</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>prod role-swap+self-login; staging role-swap+switch-user (2026-07-15 healthy, change 201)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Approve/Decline line</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN (prod SA/SA-Tech/SA-No-Reports/SA-Limited all SHOWN)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>prod role-swap+self-login; staging real-holder switch-user</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Service Advisor</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Approve/Decline line</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>prod + staging real-holder switch-user</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>Approve/Decline line</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>prod role-swap+self-login; staging role-swap+switch-user (2026-07-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Approve/Decline line</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (line renders, no Approve/Decline)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (line renders, no Approve/Decline)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>prod role-swap+self-login; staging real-holder switch-user on S10-25071</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>Parts Manager</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Approve/Decline line</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>HIDDEN (line renders, no Approve/Decline)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>SHOWN</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>STAGING-MORE</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>prod role-swap+self-login (HIDDEN) vs staging real-holder switch-user (SHOWN) — migration difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Approve/Decline line</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>prod role-swap+self-login; staging role-swap+switch-user (2026-07-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>Approve/Decline line</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (line renders, no action buttons)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>prod role-swap+self-login; staging role-swap+switch-user (2026-07-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Approve/Decline line</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (WO detail not accessible — bounce)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (only Start shown)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>prod role-swap+self-login; staging real-holder switch-user</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Time Clock User</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Approve/Decline line</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (WO detail not accessible — bounce)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>HIDDEN (WO viewable, no action buttons)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>prod role-swap+self-login; staging real-holder switch-user on S71-24170</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>--- SEND TO TERMINAL (payment dialog, invoiced WO) — ORG-DEVICE GATE, fully characterized ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>CONCLUSION</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>Send-to-Terminal is ORG-DEVICE gated, NOT role/migration gated.</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr"/>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>ORG-CONFIG</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Definitive, evidence-backed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>(all invoicing roles)</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>ABSENT for every prod role — prod org has NO terminal device AND no UI path to add one</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>SHOWN for invoicing roles (Admin/Parts Mgr/Senior SA...) — staging org HAS a terminal device</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>ORG-CONFIG (not a role/permission diff)</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>prod admin Settings full nav + Payment Methods page screenshots show NO Terminals/Card-Readers/Devices section; New Payment Method creates NAMED methods only; all terminal APIs (/api/terminals, /api/payment-terminals, /api/card-readers, /api/stripe/terminals) = 404; admin holds no terminal fe_permission. Provisioning a terminal requires external payment-processor/hardware registration (not a UI action). Migrating roles does NOT change Send-to-Terminal access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FINAL STATUS: All role-permission capability cells for the priority + broad set are OBSERVED-LIVE across both envs. The only non-role cell is Send-to-Terminal, now a FULLY-CHARACTERIZED org-device-config verdict (not an unexplained NOT-VERIFIED).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8610,7 +9811,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
         <is>
@@ -8963,7 +10163,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
         <is>
@@ -9316,7 +10515,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -9385,7 +10583,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10341,7 +11539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11106,7 +12304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17194,7 +18392,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17513,7 +18711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25031,7 +26229,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25657,690 +26855,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Prod Role</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Maps to staging</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Perms</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Send to Portal</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>See Fin Data</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>New Line</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Screenshot</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>switch-user impersonation (old-model SPA)</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Administrator/WO_ready_for_review.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Service Advisor</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Senior Service Advisor (merge)</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>switch-user impersonation (old-model SPA)</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Service_Advisor/WO_ready_for_review.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Office User</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>switch-user impersonation (old-model SPA)</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Office_User/WO_ready_for_review.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Sales Representative (merge)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>switch-user impersonation (old-model SPA)</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Sales_Representative/WO_ready_for_review.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Technician</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>SHOWN</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>switch-user impersonation (old-model SPA)</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Technician/WO_ready_for_review.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Time Clock User</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>switch-user impersonation (old-model SPA)</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/production/Time_Clock_User/WO_ready_for_review.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Service Manager</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>no active prod user; not role-swapped</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>no active prod user; not role-swapped</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Parts Manager</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>no active prod user; not role-swapped</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>no active prod user; not role-swapped</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>SA Limited View</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>no active prod user; not role-swapped</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>SA Technician</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>no active prod user; not role-swapped</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>SA No Reports</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>no active prod user; not role-swapped</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Reporting</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>no active prod user; not role-swapped</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Parts-Module Dual LIVE" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="New-WO Create Dual LIVE" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Approve-Decline LIVE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Spec-Standing Conformance" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +64,10 @@
     <font>
       <b val="1"/>
       <color rgb="000070C0"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="11">
@@ -144,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -205,6 +210,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -572,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="124" customWidth="1" min="1" max="1"/>
@@ -585,9 +594,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -616,9 +622,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-    </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
@@ -626,9 +629,6 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -671,9 +671,6 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-    </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -751,9 +748,6 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-    </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
@@ -782,9 +776,6 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-    </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
@@ -813,9 +804,6 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-    </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
@@ -844,9 +832,6 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-    </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
@@ -858,6 +843,702 @@
       <c r="A45" t="inlineStr">
         <is>
           <t>prod test-staff restored to Office User + Truck Hill 1; no throwaway data left; no TestRail writes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>TWO NEW ANNOTATION COLUMNS (added 2026-07-16) — 'Per Spec (v2)?' and 'Per Standing Instructions?'</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Added to the RIGHT of the verdict column on every role x capability x verdict tab (Full Dual Matrix, Pass-11, Pass-12,</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Approve-Decline LIVE, Send to Terminal LIVE, Parts-Module Dual LIVE, New-WO Create Dual LIVE). They evaluate the STAGING</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>(new-model) permission for each row — they DO NOT change any observed verdict; columns are ADDED only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>'Per Spec (v2)?' vocabulary (source: CustomRolesandPermissions_2.doc / current-spec-2026-07-15.md, Sasha Grosman, SV-7388):</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * 'Per spec — expected reduction' : STAGING-LESS row and the spec does NOT grant that role the capability (loss is intended).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * 'Per spec — expected grant'     : STAGING-MORE row and the spec DOES grant that role the capability (grant is intended).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * 'Per spec (matches)'            : MATCH row that agrees with the spec grant/withhold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * 'DEVIATION'                     : staging state is the OPPOSITE of what the spec prescribes (spec grants but staging hides,</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                      or staging grants but spec withholds). DEVIATION (gating model) = build gates the capability</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                      differently than the spec role-gate (Send to Terminal: build uses org-device presence, not Customer Portal ON).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * 'Spec silent — not addressed'   : the spec has no rule for this capability (Issue Credit; Decline/Set Line Status; remove-a-WO-part atom). NOT inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * 'Spec inconsistent/ambiguous'   : the spec contradicts itself for this role/capability (Send to Portal §3/§4 Full-View vs Open Q6 'can approve a WOL';</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                      Core OK/Not-OK §1b/03-Jul WOL-C&amp;E vs Key-Decision/07-Jul WO-View). Flagged, never resolved by inference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * 'Org-device config gate'        : Send to Terminal — the staging-vs-prod difference is org-config (terminal device present), not a role/migration delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Every value cites the spec gate/section it was judged against. Where the spec is silent or inconsistent, conformance is NOT inferred (stated explicitly).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>'Per Standing Instructions?' vocabulary (source: CLAUDE.md 'Sasha's spec updates' + 'Key findings' enforcement model + standing rules):</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * 'Consistent with standing rule: &lt;which&gt;'  — staging matches the documented permission-design rule (rule cited).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * 'Conflicts with standing rule: &lt;which&gt; (&lt;why&gt;)' — staging contradicts a documented rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * 'No standing rule addresses this'         — no documented rule covers the capability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Key rules used: Order Parts requires See Financial Data; AR/AP aging reports FOLLOW the Reports permission (all-or-nothing), NOT Manage AP/AR;</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WO View = create/edit ANY note / WO Delete = delete any note; WO Lines Create&amp;Edit covers Core OK/Not-OK + line story; return-a-WO-part has NO gate;</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  enforcement model = BE enforces only resource View/Edit, while Delete / WO sub-perms / cross-toggles / view_mode are FRONT-END display gates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>HEADLINE CONFORMANCE RESULT (297 role x capability rows annotated across 7 tabs):</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Per-spec (expected/matches): 276   |   DEVIATION: 7   |   Spec silent: 11   |   Spec inconsistent/ambiguous: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  =&gt; The migration is LARGELY SPEC-ACCURATE: every STAGING-LESS loss and nearly every STAGING-MORE grant maps to an intended spec gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  The only flags: (1) Send to Terminal for Foreman/Office User/Parts Technician = DEVIATION (gating model): build shows it via org-device</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      gate although the spec role-gate requires Customer Portal ON (which those 3 roles have OFF). Org-config, not a role over-grant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (2) See AP/AR for Senior Service Advisor = DEVIATION: spec grants it (Manage AP/AR ON + Reports ON) but BOTH envs hide it (a MATCH row) —</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      staging does not implement the spec grant for SSA. (3) Send to Portal for Office User/Parts Tech (STAGING-LESS) + Sales Rep (MATCH) =</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Spec inconsistent/ambiguous (bare Full-View reading vs Open Q6 'can approve a WOL'). See the 'Spec-Standing Conformance' tab.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>SPEC (v2) + STANDING-INSTRUCTION CONFORMANCE — summary of the two annotation columns (2026-07-16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Evaluates each STAGING (new-model) role x capability verdict against (1) the v2 spec intent and (2) the documented permission-design standing rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Observed verdicts are UNCHANGED — these two columns are additive. See each dual-verdict tab for the per-row wording + cited gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>TALLY (297 annotated rows across 7 tabs):</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Per spec — expected / matches</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>276</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>STAGING grant/withhold agrees with the spec gate (intended).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DEVIATION</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>STAGING is opposite of what the spec prescribes (incl. gating-model divergence).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Spec silent — not addressed</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Spec has no rule (Decline/Set Line Status; Issue Credit; remove-a-WO-part atom).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Spec inconsistent / ambiguous</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Spec contradicts itself (Send to Portal Full-View vs Open Q6 approve-a-WOL).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>KEY SIGNAL: every STAGING-LESS loss and nearly every STAGING-MORE grant is a SPEC-ACCURATE gate change. The migration is largely faithful.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>Release-relevant DEVIATIONS / flags to review (the only non-per-spec rows):</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Capability</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Why (spec judgement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Full Dual Matrix</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Foreman has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Full Dual Matrix</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Parts Technician has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Full Dual Matrix</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Office User has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Pass-11 LIVE (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Senior Service Advisor</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>See AP/AR</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION — spec grants to Senior Service Advisor (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)) but staging hides it (both envs hidden).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Send to Terminal LIVE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Foreman has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Send to Terminal LIVE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Office User has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Send to Terminal LIVE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Parts Technician has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>SPEC-INCONSISTENT / AMBIGUOUS rows (flagged, not resolved — never inferred):</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Capability</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LESS</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Spec inconsistent/ambiguous — §3/§4 grant Send to Portal to ANY Full-View role (incl. Parts Technician), so a bare-Full-View reading would make this staging state NOT per spec; BUT Open Q6 conditions it on 'can approve a WOL', which Parts Technician lacks (no WOL Create&amp;Edit) -&gt; then per spec. Flagged, not resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>LESS</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Spec inconsistent/ambiguous — §3/§4 grant Send to Portal to ANY Full-View role (incl. Office User), so a bare-Full-View reading would make this staging state NOT per spec; BUT Open Q6 conditions it on 'can approve a WOL', which Office User lacks (no WOL Create&amp;Edit) -&gt; then per spec. Flagged, not resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Spec inconsistent/ambiguous — §3/§4 Full-View would grant; Open Q6 'can approve a WOL' would withhold (Sales Rep lacks WOL Create&amp;Edit). Both envs hidden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>SPEC-SILENT capabilities in this deliverable (conformance NOT inferred): Decline line / Set Line Status (11 rows); Issue Credit (bundled in the 'Finance' cap); remove-a-WO-part as a discrete atom (spec only covers return=no gate, move=WOL C&amp;E, remove-lines=WOL Delete).</t>
         </is>
       </c>
     </row>
@@ -872,7 +1553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -881,6 +1562,8 @@
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="90" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -928,6 +1611,16 @@
           <t>Confidence / method</t>
         </is>
       </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Per Spec (v2)?</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Per Standing Instructions?</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
@@ -960,6 +1653,16 @@
           <t>prod: seeded pending line "SV 8180" on S1-723, role-swap+self-login. staging: real-holder switch-user on WO w/ pending line</t>
         </is>
       </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
@@ -992,6 +1695,16 @@
           <t>prod role-swap+self-login; staging role-swap+switch-user (2026-07-15 healthy, change 201)</t>
         </is>
       </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="inlineStr">
@@ -1024,6 +1737,16 @@
           <t>prod role-swap+self-login; staging real-holder switch-user</t>
         </is>
       </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
@@ -1056,6 +1779,16 @@
           <t>prod + staging real-holder switch-user</t>
         </is>
       </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
@@ -1088,6 +1821,16 @@
           <t>prod role-swap+self-login; staging role-swap+switch-user (2026-07-15)</t>
         </is>
       </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
@@ -1120,6 +1863,16 @@
           <t>prod role-swap+self-login; staging real-holder switch-user on S10-25071</t>
         </is>
       </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
@@ -1152,6 +1905,16 @@
           <t>prod role-swap+self-login (HIDDEN) vs staging real-holder switch-user (SHOWN) — migration difference</t>
         </is>
       </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Parts Manager holds the gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
@@ -1184,6 +1947,16 @@
           <t>prod role-swap+self-login; staging role-swap+switch-user (2026-07-15)</t>
         </is>
       </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="inlineStr">
@@ -1216,6 +1989,16 @@
           <t>prod role-swap+self-login; staging role-swap+switch-user (2026-07-15)</t>
         </is>
       </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Office User (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
@@ -1248,6 +2031,16 @@
           <t>prod role-swap+self-login; staging real-holder switch-user</t>
         </is>
       </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="21" t="inlineStr">
@@ -1280,6 +2073,16 @@
           <t>prod role-swap+self-login; staging real-holder switch-user on S71-24170</t>
         </is>
       </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1352,6 +2155,13 @@
       <c r="A21" t="inlineStr">
         <is>
           <t>FINAL STATUS: All role-permission capability cells for the priority + broad set are OBSERVED-LIVE across both envs. The only non-role cell is Send-to-Terminal, now a FULLY-CHARACTERIZED org-device-config verdict (not an unexplained NOT-VERIFIED).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>LEGEND — 'Per Spec (v2)?': Per spec-expected/matches | DEVIATION (spec grants/withholds opposite of staging) | Spec silent (not addressed) | Spec inconsistent/ambiguous | Org-device config gate (out of role model). 'Per Standing Instructions?': Consistent / Conflicts / No rule — cites the specific standing rule. Existing observed verdicts UNCHANGED; columns are ADDED.</t>
         </is>
       </c>
     </row>
@@ -1366,7 +2176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1375,6 +2185,8 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="64" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1415,6 +2227,16 @@
           <t>Confidence / method</t>
         </is>
       </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Per Spec (v2)?</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Per Standing Instructions?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
@@ -1447,6 +2269,16 @@
           <t>clean self-login + real-holder switch-user (both agree)</t>
         </is>
       </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: AP/AR tabs/fields = Manage AP/AR (requires SFD ON); AR/AP AGING reports FOLLOW the Reports permission (all-or-nothing), decoupled 3 Jul 2026 — NOT Manage AP/AR.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
@@ -1479,6 +2311,16 @@
           <t>clean self-login + switch-user</t>
         </is>
       </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Office User (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: AP/AR tabs/fields = Manage AP/AR (requires SFD ON); AR/AP AGING reports FOLLOW the Reports permission (all-or-nothing), decoupled 3 Jul 2026 — NOT Manage AP/AR.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="23" t="inlineStr">
@@ -1511,6 +2353,16 @@
           <t>clean self-login CONFIRMS switch-user</t>
         </is>
       </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Service Manager holds the gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: AP/AR tabs/fields = Manage AP/AR (requires SFD ON); AR/AP AGING reports FOLLOW the Reports permission (all-or-nothing), decoupled 3 Jul 2026 — NOT Manage AP/AR.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
@@ -1543,6 +2395,16 @@
           <t>clean self-login</t>
         </is>
       </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Parts Manager holds the gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: AP/AR tabs/fields = Manage AP/AR (requires SFD ON); AR/AP AGING reports FOLLOW the Reports permission (all-or-nothing), decoupled 3 Jul 2026 — NOT Manage AP/AR.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
@@ -1575,6 +2437,16 @@
           <t>real-holder switch-user + clean self-login</t>
         </is>
       </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Sales Representative holds the gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: AP/AR tabs/fields = Manage AP/AR (requires SFD ON); AR/AP AGING reports FOLLOW the Reports permission (all-or-nothing), decoupled 3 Jul 2026 — NOT Manage AP/AR.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
@@ -1607,6 +2479,16 @@
           <t>clean self-login</t>
         </is>
       </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION — spec grants to Senior Service Advisor (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)) but staging hides it (both envs hidden).</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: AP/AR tabs/fields = Manage AP/AR (requires SFD ON); AR/AP AGING reports FOLLOW the Reports permission (all-or-nothing), decoupled 3 Jul 2026 — NOT Manage AP/AR.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
@@ -1639,6 +2521,16 @@
           <t>clean self-login</t>
         </is>
       </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Service Advisor (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: AP/AR tabs/fields = Manage AP/AR (requires SFD ON); AR/AP AGING reports FOLLOW the Reports permission (all-or-nothing), decoupled 3 Jul 2026 — NOT Manage AP/AR.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="21" t="inlineStr">
@@ -1671,6 +2563,16 @@
           <t>clean self-login</t>
         </is>
       </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Foreman (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: AP/AR tabs/fields = Manage AP/AR (requires SFD ON); AR/AP AGING reports FOLLOW the Reports permission (all-or-nothing), decoupled 3 Jul 2026 — NOT Manage AP/AR.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
@@ -1703,6 +2605,16 @@
           <t>real holder + clean self-login</t>
         </is>
       </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: AP/AR tabs/fields = Manage AP/AR (requires SFD ON); AR/AP AGING reports FOLLOW the Reports permission (all-or-nothing), decoupled 3 Jul 2026 — NOT Manage AP/AR.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="inlineStr">
@@ -1735,6 +2647,16 @@
           <t>clean self-login</t>
         </is>
       </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: AP/AR tabs/fields = Manage AP/AR (requires SFD ON); AR/AP AGING reports FOLLOW the Reports permission (all-or-nothing), decoupled 3 Jul 2026 — NOT Manage AP/AR.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
@@ -1767,6 +2689,16 @@
           <t>real holder + clean self-login</t>
         </is>
       </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: AP/AR tabs/fields = Manage AP/AR (requires SFD ON); AR/AP AGING reports FOLLOW the Reports permission (all-or-nothing), decoupled 3 Jul 2026 — NOT Manage AP/AR.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
@@ -1799,6 +2731,16 @@
           <t>prod S1-719 role-swap+self-login</t>
         </is>
       </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: NO permission gate — return a WO part is available to everyone (29 Jun; §1a)).</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: returning a part from a WO has NO permission gate — everyone (29 Jun 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="21" t="inlineStr">
@@ -1831,6 +2773,16 @@
           <t>OBSERVED-LIVE both</t>
         </is>
       </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: NO permission gate — return a WO part is available to everyone (29 Jun; §1a)).</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: returning a part from a WO has NO permission gate — everyone (29 Jun 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="21" t="inlineStr">
@@ -1863,6 +2815,16 @@
           <t>OBSERVED-LIVE both</t>
         </is>
       </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: NO permission gate — return a WO part is available to everyone (29 Jun; §1a)).</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: returning a part from a WO has NO permission gate — everyone (29 Jun 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="inlineStr">
@@ -1895,6 +2857,16 @@
           <t>OBSERVED-LIVE both</t>
         </is>
       </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: NO permission gate — return a WO part is available to everyone (29 Jun; §1a)).</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: returning a part from a WO has NO permission gate — everyone (29 Jun 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
@@ -1927,6 +2899,16 @@
           <t>OBSERVED-LIVE both</t>
         </is>
       </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: NO permission gate — return a WO part is available to everyone (29 Jun; §1a)).</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: returning a part from a WO has NO permission gate — everyone (29 Jun 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="inlineStr">
@@ -1959,6 +2941,16 @@
           <t>OBSERVED-LIVE both</t>
         </is>
       </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Technician (gate: NO permission gate — return a WO part is available to everyone (29 Jun; §1a)).</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: returning a part from a WO has NO permission gate — everyone (29 Jun 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
@@ -1991,6 +2983,16 @@
           <t>OBSERVED-LIVE both</t>
         </is>
       </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Manager (gate: NO permission gate — return a WO part is available to everyone (29 Jun; §1a)).</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: returning a part from a WO has NO permission gate — everyone (29 Jun 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
@@ -2023,6 +3025,16 @@
           <t>OBSERVED-LIVE both</t>
         </is>
       </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Technician (gate: NO permission gate — return a WO part is available to everyone (29 Jun; §1a)).</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: returning a part from a WO has NO permission gate — everyone (29 Jun 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="23" t="inlineStr">
@@ -2055,6 +3067,16 @@
           <t>OBSERVED-LIVE both</t>
         </is>
       </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Sales Representative holds the gate: NO permission gate — return a WO part is available to everyone (29 Jun; §1a)).</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: returning a part from a WO has NO permission gate — everyone (29 Jun 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="23" t="inlineStr">
@@ -2087,6 +3109,16 @@
           <t>OBSERVED-LIVE both</t>
         </is>
       </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Office User holds the gate: NO permission gate — return a WO part is available to everyone (29 Jun; §1a)).</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: returning a part from a WO has NO permission gate — everyone (29 Jun 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="23" t="inlineStr">
@@ -2119,6 +3151,16 @@
           <t>OBSERVED-LIVE both (staging TC closed this pass)</t>
         </is>
       </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Time Clock User holds the gate: NO permission gate — return a WO part is available to everyone (29 Jun; §1a)).</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: returning a part from a WO has NO permission gate — everyone (29 Jun 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
@@ -2151,6 +3193,16 @@
           <t>prod clean self-login on invoiced S1-518</t>
         </is>
       </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: New Payment = Invoicing Create&amp;Edit; Reverse Invoice = WO Delete (moved off Invoicing Delete, 28 Jun); no standing rule addresses Issue Credit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
@@ -2183,6 +3235,16 @@
           <t>clean self-login (not an artifact - WO rendered, only Finance bounced)</t>
         </is>
       </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Service Manager holds the gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: New Payment = Invoicing Create&amp;Edit; Reverse Invoice = WO Delete (moved off Invoicing Delete, 28 Jun); no standing rule addresses Issue Credit.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="23" t="inlineStr">
@@ -2215,6 +3277,16 @@
           <t>clean self-login</t>
         </is>
       </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Parts Manager holds the gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: New Payment = Invoicing Create&amp;Edit; Reverse Invoice = WO Delete (moved off Invoicing Delete, 28 Jun); no standing rule addresses Issue Credit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
@@ -2247,6 +3319,16 @@
           <t>clean self-login</t>
         </is>
       </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Parts Technician holds the gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: New Payment = Invoicing Create&amp;Edit; Reverse Invoice = WO Delete (moved off Invoicing Delete, 28 Jun); no standing rule addresses Issue Credit.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
@@ -2279,6 +3361,16 @@
           <t>clean self-login</t>
         </is>
       </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Foreman holds the gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: New Payment = Invoicing Create&amp;Edit; Reverse Invoice = WO Delete (moved off Invoicing Delete, 28 Jun); no standing rule addresses Issue Credit.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="23" t="inlineStr">
@@ -2311,6 +3403,16 @@
           <t>clean self-login</t>
         </is>
       </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Office User holds the gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: New Payment = Invoicing Create&amp;Edit; Reverse Invoice = WO Delete (moved off Invoicing Delete, 28 Jun); no standing rule addresses Issue Credit.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
@@ -2343,6 +3445,16 @@
           <t>clean self-login per component</t>
         </is>
       </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: New Payment = Invoicing Create&amp;Edit; Reverse Invoice = WO Delete (moved off Invoicing Delete, 28 Jun); no standing rule addresses Issue Credit.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="21" t="inlineStr">
@@ -2375,6 +3487,16 @@
           <t>clean self-login</t>
         </is>
       </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: New Payment = Invoicing Create&amp;Edit; Reverse Invoice = WO Delete (moved off Invoicing Delete, 28 Jun); no standing rule addresses Issue Credit.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="21" t="inlineStr">
@@ -2407,6 +3529,16 @@
           <t>clean self-login</t>
         </is>
       </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: New Payment = Invoicing Create&amp;Edit; Reverse Invoice = WO Delete (moved off Invoicing Delete, 28 Jun); no standing rule addresses Issue Credit.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="21" t="inlineStr">
@@ -2439,6 +3571,16 @@
           <t>clean self-login</t>
         </is>
       </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: New Payment = Invoicing Create&amp;Edit; Reverse Invoice = WO Delete (moved off Invoicing Delete, 28 Jun); no standing rule addresses Issue Credit.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="21" t="inlineStr">
@@ -2471,6 +3613,16 @@
           <t>clean self-login (prod) + staging TC observed this pass</t>
         </is>
       </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: New Payment = Invoicing Create&amp;Edit; Reverse Invoice = WO Delete (moved off Invoicing Delete, 28 Jun); no standing rule addresses Issue Credit.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2532,6 +3684,13 @@
       <c r="F42" s="24" t="inlineStr">
         <is>
           <t>Headless New-Line did not persist a pending line; broader Set Line Status (Start/Complete/Pick) IS observed. Needs a pre-seeded pending-line WO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>LEGEND — 'Per Spec (v2)?': Per spec-expected/matches | DEVIATION (spec grants/withholds opposite of staging) | Spec silent (not addressed) | Spec inconsistent/ambiguous | Org-device config gate (out of role model). 'Per Standing Instructions?': Consistent / Conflicts / No rule — cites the specific standing rule. Existing observed verdicts UNCHANGED; columns are ADDED.</t>
         </is>
       </c>
     </row>
@@ -2546,7 +3705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2556,6 +3715,8 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2594,6 +3755,16 @@
           <t>Caveat</t>
         </is>
       </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Per Spec (v2)?</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Per Standing Instructions?</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -2631,6 +3802,16 @@
           <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: View Mode = Full View (spec §3/§4); Open Q6 also: 'anyone who can approve a WOL').</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7 / §6): Send to Portal = Full View; enforcement model = FE display gate (view_mode). Standing rules cite bare Full View; build also requires WOL-approve (Open Q6).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -2664,6 +3845,16 @@
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Work Order Lines -&gt; Create &amp; Edit (spec §1b/§13)).</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: add a new line = WO Lines Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -2697,6 +3888,16 @@
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: WO sub-setting 'Review WOs' (spec §B WO Sub-Settings)).</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: 'Review WOs' is a WO sub-setting = FE display gate; no other standing rule addresses it.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2730,6 +3931,16 @@
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: See Financial Data toggle (spec §5a)).</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: See Financial Data is the app-wide toggle gating Part Sales/Invoicing/Order Parts/Manage AP/AR (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2763,6 +3974,16 @@
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Invoicing -&gt; View; SFD gates Invoicing (spec §1i/§5a)).</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Invoicing View gates the Finance tab; SFD gates Invoicing (enforcement: resource View).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2796,6 +4017,16 @@
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Invoicing -&gt; Create &amp; Edit (spec §1i, Open Q4)).</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: payments = Invoicing Create&amp;Edit; the Office-cannot-create-invoices hard-coded rule does NOT block Office from taking payment.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2833,6 +4064,16 @@
           <t>ORG-terminal gated: prod none, staging has one</t>
         </is>
       </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (role-gate met) + Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.  Admin meets the spec role-gate; the observed staging-vs-prod difference is ORG-CONFIG, not role/migration.</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2866,6 +4107,16 @@
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Work Orders -&gt; Create &amp; Edit (spec §11, 07 Jul; WO-level audit log)).</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: History logs split WO-level (WO Create&amp;Edit) vs line-level (WOL Create&amp;Edit); WO-level = WO Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2899,6 +4150,16 @@
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2932,6 +4193,16 @@
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Work Orders -&gt; View (create/edit any note) (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: WO View = create/edit ANY note; WO Delete = delete any note (every role with WO View can see/add notes).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2965,6 +4236,16 @@
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Timesheets -&gt; View (spec §1j); clock-in/out + My Timesheets always on).</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: clock in/out + 'My Timesheets' always available regardless of Timesheets perm; the tab tracks Timesheets View (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -3002,6 +4283,16 @@
           <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Work Orders -&gt; Delete (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: enforcement model — Delete is a FE display gate (BE enforces only View/Edit); WO Delete also gates Reverse Invoice.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -3035,6 +4326,16 @@
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -3068,6 +4369,16 @@
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -3105,6 +4416,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Admin via live-ui-2026-07-16/staging/approve-decline-realholder.json. Prod: Administrator.</t>
         </is>
       </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: WO Lines -&gt; Create &amp; Edit + Full View (Open Q6)).</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: approve a line = WOL Create&amp;Edit + Full View (FE gate); View Mode is UX not security, but approve is FE-gated by Full View.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -3142,6 +4463,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Admin via live-ui-2026-07-16/staging/approve-decline-realholder.json. Prod: Administrator.</t>
         </is>
       </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>No standing rule addresses Decline/Set Line Status as a discrete action (grouped with approve under WOL Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -3179,6 +4510,16 @@
           <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: View Mode = Full View (spec §3/§4); Open Q6 also: 'anyone who can approve a WOL').</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7 / §6): Send to Portal = Full View; enforcement model = FE display gate (view_mode). Standing rules cite bare Full View; build also requires WOL-approve (Open Q6).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -3212,6 +4553,16 @@
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: Work Order Lines -&gt; Create &amp; Edit (spec §1b/§13)).</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: add a new line = WO Lines Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -3245,6 +4596,16 @@
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: WO sub-setting 'Review WOs' (spec §B WO Sub-Settings)).</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: 'Review WOs' is a WO sub-setting = FE display gate; no other standing rule addresses it.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -3278,6 +4639,16 @@
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: See Financial Data toggle (spec §5a)).</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: See Financial Data is the app-wide toggle gating Part Sales/Invoicing/Order Parts/Manage AP/AR (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -3311,6 +4682,16 @@
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: Invoicing -&gt; View; SFD gates Invoicing (spec §1i/§5a)).</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Invoicing View gates the Finance tab; SFD gates Invoicing (enforcement: resource View).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -3344,6 +4725,16 @@
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Service Manager holds the gate: Invoicing -&gt; Create &amp; Edit (spec §1i, Open Q4)).</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: payments = Invoicing Create&amp;Edit; the Office-cannot-create-invoices hard-coded rule does NOT block Office from taking payment.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -3381,6 +4772,16 @@
           <t>Send-to-Terminal is ORG-DEVICE gated, NOT role/permission gated (Pass-12): prod org has no terminal -&gt; hidden for all; staging org HAS a terminal -&gt; shows for any role that can open New Payment. Not a migration/role difference.</t>
         </is>
       </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (role-gate met) + Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.  Service Manager meets the spec role-gate; the observed staging-vs-prod difference is ORG-CONFIG, not role/migration.</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -3414,6 +4815,16 @@
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: Work Orders -&gt; Create &amp; Edit (spec §11, 07 Jul; WO-level audit log)).</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: History logs split WO-level (WO Create&amp;Edit) vs line-level (WOL Create&amp;Edit); WO-level = WO Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -3447,6 +4858,16 @@
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -3480,6 +4901,16 @@
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: Work Orders -&gt; View (create/edit any note) (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: WO View = create/edit ANY note; WO Delete = delete any note (every role with WO View can see/add notes).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -3513,6 +4944,16 @@
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: Timesheets -&gt; View (spec §1j); clock-in/out + My Timesheets always on).</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: clock in/out + 'My Timesheets' always available regardless of Timesheets perm; the tab tracks Timesheets View (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3550,6 +4991,16 @@
           <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Service Manager holds the gate: Work Orders -&gt; Delete (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: enforcement model — Delete is a FE display gate (BE enforces only View/Edit); WO Delete also gates Reverse Invoice.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3583,6 +5034,16 @@
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Service Manager holds the gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3616,6 +5077,16 @@
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Service Manager holds the gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3653,6 +5124,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Service Manager via approve-decline-REALHOLDER-ALL.json. Prod: Service Manager.</t>
         </is>
       </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: WO Lines -&gt; Create &amp; Edit + Full View (Open Q6)).</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: approve a line = WOL Create&amp;Edit + Full View (FE gate); View Mode is UX not security, but approve is FE-gated by Full View.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3690,6 +5171,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Service Manager via approve-decline-REALHOLDER-ALL.json. Prod: Service Manager.</t>
         </is>
       </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>No standing rule addresses Decline/Set Line Status as a discrete action (grouped with approve under WOL Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3727,6 +5218,16 @@
           <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: View Mode = Full View (spec §3/§4); Open Q6 also: 'anyone who can approve a WOL').</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7 / §6): Send to Portal = Full View; enforcement model = FE display gate (view_mode). Standing rules cite bare Full View; build also requires WOL-approve (Open Q6).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3760,6 +5261,16 @@
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Work Order Lines -&gt; Create &amp; Edit (spec §1b/§13)).</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: add a new line = WO Lines Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3793,6 +5304,16 @@
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: WO sub-setting 'Review WOs' (spec §B WO Sub-Settings)).</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: 'Review WOs' is a WO sub-setting = FE display gate; no other standing rule addresses it.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3826,6 +5347,16 @@
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: See Financial Data toggle (spec §5a)).</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: See Financial Data is the app-wide toggle gating Part Sales/Invoicing/Order Parts/Manage AP/AR (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3859,6 +5390,16 @@
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Invoicing -&gt; View; SFD gates Invoicing (spec §1i/§5a)).</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Invoicing View gates the Finance tab; SFD gates Invoicing (enforcement: resource View).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3892,6 +5433,16 @@
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Senior Service Advisor holds the gate: Invoicing -&gt; Create &amp; Edit (spec §1i, Open Q4)).</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: payments = Invoicing Create&amp;Edit; the Office-cannot-create-invoices hard-coded rule does NOT block Office from taking payment.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3929,6 +5480,16 @@
           <t>Send-to-Terminal is ORG-DEVICE gated, NOT role/permission gated (Pass-12): prod org has no terminal -&gt; hidden for all; staging org HAS a terminal -&gt; shows for any role that can open New Payment. Not a migration/role difference.</t>
         </is>
       </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (role-gate met) + Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.  Senior Service Advisor meets the spec role-gate; the observed staging-vs-prod difference is ORG-CONFIG, not role/migration.</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3962,6 +5523,16 @@
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Work Orders -&gt; Create &amp; Edit (spec §11, 07 Jul; WO-level audit log)).</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: History logs split WO-level (WO Create&amp;Edit) vs line-level (WOL Create&amp;Edit); WO-level = WO Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3995,6 +5566,16 @@
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -4028,6 +5609,16 @@
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Work Orders -&gt; View (create/edit any note) (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: WO View = create/edit ANY note; WO Delete = delete any note (every role with WO View can see/add notes).</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4061,6 +5652,16 @@
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Timesheets -&gt; View (spec §1j); clock-in/out + My Timesheets always on).</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: clock in/out + 'My Timesheets' always available regardless of Timesheets perm; the tab tracks Timesheets View (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4098,6 +5699,16 @@
           <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Work Orders -&gt; Delete (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: enforcement model — Delete is a FE display gate (BE enforces only View/Edit); WO Delete also gates Reverse Invoice.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4131,6 +5742,16 @@
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4164,6 +5785,16 @@
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4201,6 +5832,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Senior Service Advisor via approve-decline-REALHOLDER-ALL.json (perms 31). Prod: Service Advisor + SA Technician + SA No Reports (all SHOWN).</t>
         </is>
       </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: WO Lines -&gt; Create &amp; Edit + Full View (Open Q6)).</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: approve a line = WOL Create&amp;Edit + Full View (FE gate); View Mode is UX not security, but approve is FE-gated by Full View.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4238,6 +5879,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Senior Service Advisor via approve-decline-REALHOLDER-ALL.json (perms 31). Prod: Service Advisor + SA Technician + SA No Reports (all SHOWN).</t>
         </is>
       </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>No standing rule addresses Decline/Set Line Status as a discrete action (grouped with approve under WOL Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -4275,6 +5926,16 @@
           <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: View Mode = Full View (spec §3/§4); Open Q6 also: 'anyone who can approve a WOL').</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7 / §6): Send to Portal = Full View; enforcement model = FE display gate (view_mode). Standing rules cite bare Full View; build also requires WOL-approve (Open Q6).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -4308,6 +5969,16 @@
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Work Order Lines -&gt; Create &amp; Edit (spec §1b/§13)).</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: add a new line = WO Lines Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -4341,6 +6012,16 @@
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: WO sub-setting 'Review WOs' (spec §B WO Sub-Settings)).</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: 'Review WOs' is a WO sub-setting = FE display gate; no other standing rule addresses it.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -4374,6 +6055,16 @@
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: See Financial Data toggle (spec §5a)).</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: See Financial Data is the app-wide toggle gating Part Sales/Invoicing/Order Parts/Manage AP/AR (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -4407,6 +6098,16 @@
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Invoicing -&gt; View; SFD gates Invoicing (spec §1i/§5a)).</t>
+        </is>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Invoicing View gates the Finance tab; SFD gates Invoicing (enforcement: resource View).</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -4440,6 +6141,16 @@
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Invoicing -&gt; Create &amp; Edit (spec §1i, Open Q4)).</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: payments = Invoicing Create&amp;Edit; the Office-cannot-create-invoices hard-coded rule does NOT block Office from taking payment.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -4477,6 +6188,16 @@
           <t>ORG-terminal gated: prod none, staging has one</t>
         </is>
       </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (role-gate met) + Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.  Service Advisor meets the spec role-gate; the observed staging-vs-prod difference is ORG-CONFIG, not role/migration.</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -4510,6 +6231,16 @@
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Work Orders -&gt; Create &amp; Edit (spec §11, 07 Jul; WO-level audit log)).</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: History logs split WO-level (WO Create&amp;Edit) vs line-level (WOL Create&amp;Edit); WO-level = WO Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -4543,6 +6274,16 @@
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -4576,6 +6317,16 @@
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Work Orders -&gt; View (create/edit any note) (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: WO View = create/edit ANY note; WO Delete = delete any note (every role with WO View can see/add notes).</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -4609,6 +6360,16 @@
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Timesheets -&gt; View (spec §1j); clock-in/out + My Timesheets always on).</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: clock in/out + 'My Timesheets' always available regardless of Timesheets perm; the tab tracks Timesheets View (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -4646,6 +6407,16 @@
           <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Service Advisor; gate: Work Orders -&gt; Delete (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: enforcement model — Delete is a FE display gate (BE enforces only View/Edit); WO Delete also gates Reverse Invoice.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -4679,6 +6450,16 @@
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -4712,6 +6493,16 @@
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr"/>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -4749,6 +6540,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Service Advisor via approve-decline-REALHOLDER-ALL.json (perms 25). Prod: SA Limited View.</t>
         </is>
       </c>
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: WO Lines -&gt; Create &amp; Edit + Full View (Open Q6)).</t>
+        </is>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: approve a line = WOL Create&amp;Edit + Full View (FE gate); View Mode is UX not security, but approve is FE-gated by Full View.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -4786,6 +6587,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Service Advisor via approve-decline-REALHOLDER-ALL.json (perms 25). Prod: SA Limited View.</t>
         </is>
       </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+        </is>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>No standing rule addresses Decline/Set Line Status as a discrete action (grouped with approve under WOL Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -4823,6 +6634,16 @@
           <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
+      <c r="H66" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: View Mode = Full View (spec §3/§4); Open Q6 also: 'anyone who can approve a WOL').</t>
+        </is>
+      </c>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7 / §6): Send to Portal = Full View; enforcement model = FE display gate (view_mode). Standing rules cite bare Full View; build also requires WOL-approve (Open Q6).</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -4856,6 +6677,16 @@
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Work Order Lines -&gt; Create &amp; Edit (spec §1b/§13)).</t>
+        </is>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: add a new line = WO Lines Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -4889,6 +6720,16 @@
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr"/>
+      <c r="H68" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: WO sub-setting 'Review WOs' (spec §B WO Sub-Settings)).</t>
+        </is>
+      </c>
+      <c r="I68" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: 'Review WOs' is a WO sub-setting = FE display gate; no other standing rule addresses it.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -4922,6 +6763,16 @@
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: See Financial Data toggle (spec §5a)).</t>
+        </is>
+      </c>
+      <c r="I69" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: See Financial Data is the app-wide toggle gating Part Sales/Invoicing/Order Parts/Manage AP/AR (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -4955,6 +6806,16 @@
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Invoicing -&gt; View; SFD gates Invoicing (spec §1i/§5a)).</t>
+        </is>
+      </c>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Invoicing View gates the Finance tab; SFD gates Invoicing (enforcement: resource View).</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -4988,6 +6849,16 @@
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Foreman holds the gate: Invoicing -&gt; Create &amp; Edit (spec §1i, Open Q4)).</t>
+        </is>
+      </c>
+      <c r="I71" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: payments = Invoicing Create&amp;Edit; the Office-cannot-create-invoices hard-coded rule does NOT block Office from taking payment.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -5025,6 +6896,16 @@
           <t>Send-to-Terminal is ORG-DEVICE gated, NOT role/permission gated (Pass-12): prod org has no terminal -&gt; hidden for all; staging org HAS a terminal -&gt; shows for any role that can open New Payment. Not a migration/role difference.</t>
         </is>
       </c>
+      <c r="H72" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Foreman has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -5058,6 +6939,16 @@
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr"/>
+      <c r="H73" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Work Orders -&gt; Create &amp; Edit (spec §11, 07 Jul; WO-level audit log)).</t>
+        </is>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: History logs split WO-level (WO Create&amp;Edit) vs line-level (WOL Create&amp;Edit); WO-level = WO Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -5091,6 +6982,16 @@
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr"/>
+      <c r="H74" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -5124,6 +7025,16 @@
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Work Orders -&gt; View (create/edit any note) (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: WO View = create/edit ANY note; WO Delete = delete any note (every role with WO View can see/add notes).</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -5157,6 +7068,16 @@
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr"/>
+      <c r="H76" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Timesheets -&gt; View (spec §1j); clock-in/out + My Timesheets always on).</t>
+        </is>
+      </c>
+      <c r="I76" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: clock in/out + 'My Timesheets' always available regardless of Timesheets perm; the tab tracks Timesheets View (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -5194,6 +7115,16 @@
           <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
+      <c r="H77" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Foreman; gate: Work Orders -&gt; Delete (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I77" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: enforcement model — Delete is a FE display gate (BE enforces only View/Edit); WO Delete also gates Reverse Invoice.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -5227,6 +7158,16 @@
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr"/>
+      <c r="H78" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I78" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -5260,6 +7201,16 @@
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr"/>
+      <c r="H79" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I79" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -5297,6 +7248,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Foreman via approve-decline-REALHOLDER-ALL.json (perms 23). Prod: Foreman.</t>
         </is>
       </c>
+      <c r="H80" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: WO Lines -&gt; Create &amp; Edit + Full View (Open Q6)).</t>
+        </is>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: approve a line = WOL Create&amp;Edit + Full View (FE gate); View Mode is UX not security, but approve is FE-gated by Full View.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -5334,6 +7295,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Foreman via approve-decline-REALHOLDER-ALL.json (perms 23). Prod: Foreman.</t>
         </is>
       </c>
+      <c r="H81" s="14" t="inlineStr">
+        <is>
+          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+        </is>
+      </c>
+      <c r="I81" s="14" t="inlineStr">
+        <is>
+          <t>No standing rule addresses Decline/Set Line Status as a discrete action (grouped with approve under WOL Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -5371,6 +7342,16 @@
           <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
+      <c r="H82" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Technician; gate: View Mode = Full View (spec §3/§4); Open Q6 also: 'anyone who can approve a WOL').</t>
+        </is>
+      </c>
+      <c r="I82" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7 / §6): Send to Portal = Full View; enforcement model = FE display gate (view_mode). Standing rules cite bare Full View; build also requires WOL-approve (Open Q6).</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -5404,6 +7385,16 @@
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr"/>
+      <c r="H83" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Technician (gate: Work Order Lines -&gt; Create &amp; Edit (spec §1b/§13)).</t>
+        </is>
+      </c>
+      <c r="I83" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: add a new line = WO Lines Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -5437,6 +7428,16 @@
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr"/>
+      <c r="H84" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: WO sub-setting 'Review WOs' (spec §B WO Sub-Settings)).</t>
+        </is>
+      </c>
+      <c r="I84" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: 'Review WOs' is a WO sub-setting = FE display gate; no other standing rule addresses it.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -5470,6 +7471,16 @@
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr"/>
+      <c r="H85" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: See Financial Data toggle (spec §5a)).</t>
+        </is>
+      </c>
+      <c r="I85" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: See Financial Data is the app-wide toggle gating Part Sales/Invoicing/Order Parts/Manage AP/AR (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -5503,6 +7514,16 @@
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr"/>
+      <c r="H86" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Technician; gate: Invoicing -&gt; View; SFD gates Invoicing (spec §1i/§5a)).</t>
+        </is>
+      </c>
+      <c r="I86" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Invoicing View gates the Finance tab; SFD gates Invoicing (enforcement: resource View).</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -5540,6 +7561,16 @@
           <t>STAGING observed hidden (role cannot open Finance/New Payment; wocaps-obs.json newPayment=false, live role-scoped session). PROD hidden.</t>
         </is>
       </c>
+      <c r="H87" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: Invoicing -&gt; Create &amp; Edit (spec §1i, Open Q4)).</t>
+        </is>
+      </c>
+      <c r="I87" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: payments = Invoicing Create&amp;Edit; the Office-cannot-create-invoices hard-coded rule does NOT block Office from taking payment.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -5577,6 +7608,16 @@
           <t>Send-to-Terminal is ORG-DEVICE gated, NOT role/permission gated (Pass-12): prod org has no terminal -&gt; hidden for all; staging org HAS a terminal -&gt; shows for any role that can open New Payment. Not a migration/role difference.</t>
         </is>
       </c>
+      <c r="H88" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — Technician cannot open New Payment (no Invoicing C&amp;E) so Send to Terminal is unreachable. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+      <c r="I88" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -5610,6 +7651,16 @@
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr"/>
+      <c r="H89" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Technician; gate: Work Orders -&gt; Create &amp; Edit (spec §11, 07 Jul; WO-level audit log)).</t>
+        </is>
+      </c>
+      <c r="I89" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: History logs split WO-level (WO Create&amp;Edit) vs line-level (WOL Create&amp;Edit); WO-level = WO Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -5643,6 +7694,16 @@
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr"/>
+      <c r="H90" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Technician; gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="I90" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -5676,6 +7737,16 @@
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr"/>
+      <c r="H91" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Technician (gate: Work Orders -&gt; View (create/edit any note) (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I91" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: WO View = create/edit ANY note; WO Delete = delete any note (every role with WO View can see/add notes).</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -5709,6 +7780,16 @@
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr"/>
+      <c r="H92" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Technician; gate: Timesheets -&gt; View (spec §1j); clock-in/out + My Timesheets always on).</t>
+        </is>
+      </c>
+      <c r="I92" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: clock in/out + 'My Timesheets' always available regardless of Timesheets perm; the tab tracks Timesheets View (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -5746,6 +7827,16 @@
           <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
+      <c r="H93" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Technician; gate: Work Orders -&gt; Delete (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I93" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: enforcement model — Delete is a FE display gate (BE enforces only View/Edit); WO Delete also gates Reverse Invoice.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -5779,6 +7870,16 @@
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr"/>
+      <c r="H94" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Technician; gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I94" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -5812,6 +7913,16 @@
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr"/>
+      <c r="H95" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Technician; gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I95" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -5849,6 +7960,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Technician via approve-decline-TECH-PT.json (quick-login tech, perms 6, rendered, Needs Approval present, no Approve/Decline). Prod: Technician.</t>
         </is>
       </c>
+      <c r="H96" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: WO Lines -&gt; Create &amp; Edit + Full View (Open Q6)).</t>
+        </is>
+      </c>
+      <c r="I96" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: approve a line = WOL Create&amp;Edit + Full View (FE gate); View Mode is UX not security, but approve is FE-gated by Full View.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -5886,6 +8007,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Technician via approve-decline-TECH-PT.json (quick-login tech, perms 6, rendered, Needs Approval present, no Approve/Decline). Prod: Technician.</t>
         </is>
       </c>
+      <c r="H97" s="14" t="inlineStr">
+        <is>
+          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+        </is>
+      </c>
+      <c r="I97" s="14" t="inlineStr">
+        <is>
+          <t>No standing rule addresses Decline/Set Line Status as a discrete action (grouped with approve under WOL Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -5923,6 +8054,16 @@
           <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
+      <c r="H98" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Manager (gate: View Mode = Full View (spec §3/§4); Open Q6 also: 'anyone who can approve a WOL').</t>
+        </is>
+      </c>
+      <c r="I98" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7 / §6): Send to Portal = Full View; enforcement model = FE display gate (view_mode). Standing rules cite bare Full View; build also requires WOL-approve (Open Q6).</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -5956,6 +8097,16 @@
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr"/>
+      <c r="H99" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Manager (gate: Work Order Lines -&gt; Create &amp; Edit (spec §1b/§13)).</t>
+        </is>
+      </c>
+      <c r="I99" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: add a new line = WO Lines Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -5989,6 +8140,16 @@
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr"/>
+      <c r="H100" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Parts Manager holds the gate: WO sub-setting 'Review WOs' (spec §B WO Sub-Settings)).</t>
+        </is>
+      </c>
+      <c r="I100" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: 'Review WOs' is a WO sub-setting = FE display gate; no other standing rule addresses it.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -6022,6 +8183,16 @@
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr"/>
+      <c r="H101" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Manager (gate: See Financial Data toggle (spec §5a)).</t>
+        </is>
+      </c>
+      <c r="I101" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: See Financial Data is the app-wide toggle gating Part Sales/Invoicing/Order Parts/Manage AP/AR (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -6055,6 +8226,16 @@
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr"/>
+      <c r="H102" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Manager (gate: Invoicing -&gt; View; SFD gates Invoicing (spec §1i/§5a)).</t>
+        </is>
+      </c>
+      <c r="I102" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Invoicing View gates the Finance tab; SFD gates Invoicing (enforcement: resource View).</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -6088,6 +8269,16 @@
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr"/>
+      <c r="H103" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Parts Manager holds the gate: Invoicing -&gt; Create &amp; Edit (spec §1i, Open Q4)).</t>
+        </is>
+      </c>
+      <c r="I103" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: payments = Invoicing Create&amp;Edit; the Office-cannot-create-invoices hard-coded rule does NOT block Office from taking payment.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -6125,6 +8316,16 @@
           <t>Send-to-Terminal is ORG-DEVICE gated, NOT role/permission gated (Pass-12): prod org has no terminal -&gt; hidden for all; staging org HAS a terminal -&gt; shows for any role that can open New Payment. Not a migration/role difference.</t>
         </is>
       </c>
+      <c r="H104" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (role-gate met) + Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.  Parts Manager meets the spec role-gate; the observed staging-vs-prod difference is ORG-CONFIG, not role/migration.</t>
+        </is>
+      </c>
+      <c r="I104" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -6158,6 +8359,16 @@
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr"/>
+      <c r="H105" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Manager (gate: Work Orders -&gt; Create &amp; Edit (spec §11, 07 Jul; WO-level audit log)).</t>
+        </is>
+      </c>
+      <c r="I105" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: History logs split WO-level (WO Create&amp;Edit) vs line-level (WOL Create&amp;Edit); WO-level = WO Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -6191,6 +8402,16 @@
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr"/>
+      <c r="H106" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Manager (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="I106" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -6224,6 +8445,16 @@
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Manager (gate: Work Orders -&gt; View (create/edit any note) (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I107" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: WO View = create/edit ANY note; WO Delete = delete any note (every role with WO View can see/add notes).</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -6257,6 +8488,16 @@
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr"/>
+      <c r="H108" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Parts Manager; gate: Timesheets -&gt; View (spec §1j); clock-in/out + My Timesheets always on).</t>
+        </is>
+      </c>
+      <c r="I108" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: clock in/out + 'My Timesheets' always available regardless of Timesheets perm; the tab tracks Timesheets View (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -6294,6 +8535,16 @@
           <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
+      <c r="H109" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Parts Manager (gate: Work Orders -&gt; Delete (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I109" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: enforcement model — Delete is a FE display gate (BE enforces only View/Edit); WO Delete also gates Reverse Invoice.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -6327,6 +8578,16 @@
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr"/>
+      <c r="H110" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Parts Manager holds the gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I110" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -6360,6 +8621,16 @@
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr"/>
+      <c r="H111" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Parts Manager holds the gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I111" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -6397,6 +8668,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Parts Manager via approve-decline-REALHOLDER-ALL.json (perms 31, rendered, Approve=true). Prod: Parts Manager.</t>
         </is>
       </c>
+      <c r="H112" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Parts Manager holds the gate: WO Lines -&gt; Create &amp; Edit + Full View (Open Q6)).</t>
+        </is>
+      </c>
+      <c r="I112" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: approve a line = WOL Create&amp;Edit + Full View (FE gate); View Mode is UX not security, but approve is FE-gated by Full View.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -6434,6 +8715,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Parts Manager via approve-decline-REALHOLDER-ALL.json (perms 31, rendered, Approve=true). Prod: Parts Manager.</t>
         </is>
       </c>
+      <c r="H113" s="14" t="inlineStr">
+        <is>
+          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+        </is>
+      </c>
+      <c r="I113" s="14" t="inlineStr">
+        <is>
+          <t>No standing rule addresses Decline/Set Line Status as a discrete action (grouped with approve under WOL Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -6471,6 +8762,16 @@
           <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
+      <c r="H114" s="14" t="inlineStr">
+        <is>
+          <t>Spec inconsistent/ambiguous — §3/§4 grant Send to Portal to ANY Full-View role (incl. Parts Technician), so a bare-Full-View reading would make this staging state NOT per spec; BUT Open Q6 conditions it on 'can approve a WOL', which Parts Technician lacks (no WOL Create&amp;Edit) -&gt; then per spec. Flagged, not resolved.</t>
+        </is>
+      </c>
+      <c r="I114" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7 / §6): Send to Portal = Full View; enforcement model = FE display gate (view_mode). Standing rules cite bare Full View; build also requires WOL-approve (Open Q6).</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -6504,6 +8805,16 @@
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr"/>
+      <c r="H115" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Parts Technician; gate: Work Order Lines -&gt; Create &amp; Edit (spec §1b/§13)).</t>
+        </is>
+      </c>
+      <c r="I115" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: add a new line = WO Lines Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -6537,6 +8848,16 @@
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr"/>
+      <c r="H116" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: WO sub-setting 'Review WOs' (spec §B WO Sub-Settings)).</t>
+        </is>
+      </c>
+      <c r="I116" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: 'Review WOs' is a WO sub-setting = FE display gate; no other standing rule addresses it.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -6570,6 +8891,16 @@
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr"/>
+      <c r="H117" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Technician (gate: See Financial Data toggle (spec §5a)).</t>
+        </is>
+      </c>
+      <c r="I117" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: See Financial Data is the app-wide toggle gating Part Sales/Invoicing/Order Parts/Manage AP/AR (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -6603,6 +8934,16 @@
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr"/>
+      <c r="H118" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Technician (gate: Invoicing -&gt; View; SFD gates Invoicing (spec §1i/§5a)).</t>
+        </is>
+      </c>
+      <c r="I118" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Invoicing View gates the Finance tab; SFD gates Invoicing (enforcement: resource View).</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -6636,6 +8977,16 @@
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr"/>
+      <c r="H119" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Parts Technician holds the gate: Invoicing -&gt; Create &amp; Edit (spec §1i, Open Q4)).</t>
+        </is>
+      </c>
+      <c r="I119" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: payments = Invoicing Create&amp;Edit; the Office-cannot-create-invoices hard-coded rule does NOT block Office from taking payment.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -6673,6 +9024,16 @@
           <t>Send-to-Terminal is ORG-DEVICE gated, NOT role/permission gated (Pass-12): prod org has no terminal -&gt; hidden for all; staging org HAS a terminal -&gt; shows for any role that can open New Payment. Not a migration/role difference.</t>
         </is>
       </c>
+      <c r="H120" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Parts Technician has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+      <c r="I120" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -6706,6 +9067,16 @@
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr"/>
+      <c r="H121" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Parts Technician; gate: Work Orders -&gt; Create &amp; Edit (spec §11, 07 Jul; WO-level audit log)).</t>
+        </is>
+      </c>
+      <c r="I121" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: History logs split WO-level (WO Create&amp;Edit) vs line-level (WOL Create&amp;Edit); WO-level = WO Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -6739,6 +9110,16 @@
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr"/>
+      <c r="H122" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Technician (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="I122" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -6772,6 +9153,16 @@
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr"/>
+      <c r="H123" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Technician (gate: Work Orders -&gt; View (create/edit any note) (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I123" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: WO View = create/edit ANY note; WO Delete = delete any note (every role with WO View can see/add notes).</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -6805,6 +9196,16 @@
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr"/>
+      <c r="H124" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Technician (gate: Timesheets -&gt; View (spec §1j); clock-in/out + My Timesheets always on).</t>
+        </is>
+      </c>
+      <c r="I124" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: clock in/out + 'My Timesheets' always available regardless of Timesheets perm; the tab tracks Timesheets View (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -6842,6 +9243,16 @@
           <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
+      <c r="H125" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Work Orders -&gt; Delete (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I125" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: enforcement model — Delete is a FE display gate (BE enforces only View/Edit); WO Delete also gates Reverse Invoice.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -6875,6 +9286,16 @@
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr"/>
+      <c r="H126" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I126" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -6908,6 +9329,16 @@
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr"/>
+      <c r="H127" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I127" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -6945,6 +9376,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Parts Technician via live-ui-2026-07-15/staging/Parts_Technician/refwo-caps.json (staff/change 201, su 200, perms 19, rendered=true, zero line-action buttons). Prod: Parts Technician.</t>
         </is>
       </c>
+      <c r="H128" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: WO Lines -&gt; Create &amp; Edit + Full View (Open Q6)).</t>
+        </is>
+      </c>
+      <c r="I128" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: approve a line = WOL Create&amp;Edit + Full View (FE gate); View Mode is UX not security, but approve is FE-gated by Full View.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -6982,6 +9423,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Parts Technician via live-ui-2026-07-15/staging/Parts_Technician/refwo-caps.json (staff/change 201, su 200, perms 19, rendered=true, zero line-action buttons). Prod: Parts Technician.</t>
         </is>
       </c>
+      <c r="H129" s="14" t="inlineStr">
+        <is>
+          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+        </is>
+      </c>
+      <c r="I129" s="14" t="inlineStr">
+        <is>
+          <t>No standing rule addresses Decline/Set Line Status as a discrete action (grouped with approve under WOL Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -7019,6 +9470,16 @@
           <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
+      <c r="H130" s="14" t="inlineStr">
+        <is>
+          <t>Spec inconsistent/ambiguous — §3/§4 grant Send to Portal to ANY Full-View role (incl. Sales Representative), so a bare-Full-View reading would make this staging state NOT per spec; BUT Open Q6 conditions it on 'can approve a WOL', which Sales Representative lacks (no WOL Create&amp;Edit) -&gt; then per spec. Flagged, not resolved.</t>
+        </is>
+      </c>
+      <c r="I130" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7 / §6): Send to Portal = Full View; enforcement model = FE display gate (view_mode). Standing rules cite bare Full View; build also requires WOL-approve (Open Q6).</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -7052,6 +9513,16 @@
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr"/>
+      <c r="H131" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Work Order Lines -&gt; Create &amp; Edit (spec §1b/§13)).</t>
+        </is>
+      </c>
+      <c r="I131" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: add a new line = WO Lines Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -7085,6 +9556,16 @@
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr"/>
+      <c r="H132" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: WO sub-setting 'Review WOs' (spec §B WO Sub-Settings)).</t>
+        </is>
+      </c>
+      <c r="I132" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: 'Review WOs' is a WO sub-setting = FE display gate; no other standing rule addresses it.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
@@ -7118,6 +9599,16 @@
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr"/>
+      <c r="H133" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Sales Representative holds the gate: See Financial Data toggle (spec §5a)).</t>
+        </is>
+      </c>
+      <c r="I133" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: See Financial Data is the app-wide toggle gating Part Sales/Invoicing/Order Parts/Manage AP/AR (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -7151,6 +9642,16 @@
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Invoicing -&gt; View; SFD gates Invoicing (spec §1i/§5a)).</t>
+        </is>
+      </c>
+      <c r="I134" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Invoicing View gates the Finance tab; SFD gates Invoicing (enforcement: resource View).</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -7184,6 +9685,16 @@
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr"/>
+      <c r="H135" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Invoicing -&gt; Create &amp; Edit (spec §1i, Open Q4)).</t>
+        </is>
+      </c>
+      <c r="I135" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: payments = Invoicing Create&amp;Edit; the Office-cannot-create-invoices hard-coded rule does NOT block Office from taking payment.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -7221,6 +9732,16 @@
           <t>Send-to-Terminal is ORG-DEVICE gated, NOT role/permission gated (Pass-12): prod org has no terminal -&gt; hidden for all; staging org HAS a terminal -&gt; shows for any role that can open New Payment. Not a migration/role difference.</t>
         </is>
       </c>
+      <c r="H136" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — Sales Representative cannot open New Payment (no Invoicing C&amp;E) so Send to Terminal is unreachable. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+      <c r="I136" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -7254,6 +9775,16 @@
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr"/>
+      <c r="H137" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Work Orders -&gt; Create &amp; Edit (spec §11, 07 Jul; WO-level audit log)).</t>
+        </is>
+      </c>
+      <c r="I137" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: History logs split WO-level (WO Create&amp;Edit) vs line-level (WOL Create&amp;Edit); WO-level = WO Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -7287,6 +9818,16 @@
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr"/>
+      <c r="H138" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="I138" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -7320,6 +9861,16 @@
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr"/>
+      <c r="H139" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Sales Representative holds the gate: Work Orders -&gt; View (create/edit any note) (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I139" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: WO View = create/edit ANY note; WO Delete = delete any note (every role with WO View can see/add notes).</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -7353,6 +9904,16 @@
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr"/>
+      <c r="H140" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Timesheets -&gt; View (spec §1j); clock-in/out + My Timesheets always on).</t>
+        </is>
+      </c>
+      <c r="I140" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: clock in/out + 'My Timesheets' always available regardless of Timesheets perm; the tab tracks Timesheets View (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -7390,6 +9951,16 @@
           <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
+      <c r="H141" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Work Orders -&gt; Delete (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I141" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: enforcement model — Delete is a FE display gate (BE enforces only View/Edit); WO Delete also gates Reverse Invoice.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -7423,6 +9994,16 @@
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr"/>
+      <c r="H142" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I142" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -7456,6 +10037,16 @@
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr"/>
+      <c r="H143" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I143" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -7493,6 +10084,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Sales Representative via approve-decline-RETRY.json (perms 8, rendered, Needs Approval present, no Approve). Prod: Sales Representative + Reporting.</t>
         </is>
       </c>
+      <c r="H144" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: WO Lines -&gt; Create &amp; Edit + Full View (Open Q6)).</t>
+        </is>
+      </c>
+      <c r="I144" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: approve a line = WOL Create&amp;Edit + Full View (FE gate); View Mode is UX not security, but approve is FE-gated by Full View.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -7530,6 +10131,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Sales Representative via approve-decline-RETRY.json (perms 8, rendered, Needs Approval present, no Approve). Prod: Sales Representative + Reporting.</t>
         </is>
       </c>
+      <c r="H145" s="14" t="inlineStr">
+        <is>
+          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+        </is>
+      </c>
+      <c r="I145" s="14" t="inlineStr">
+        <is>
+          <t>No standing rule addresses Decline/Set Line Status as a discrete action (grouped with approve under WOL Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -7567,6 +10178,16 @@
           <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
+      <c r="H146" s="14" t="inlineStr">
+        <is>
+          <t>Spec inconsistent/ambiguous — §3/§4 grant Send to Portal to ANY Full-View role (incl. Office User), so a bare-Full-View reading would make this staging state NOT per spec; BUT Open Q6 conditions it on 'can approve a WOL', which Office User lacks (no WOL Create&amp;Edit) -&gt; then per spec. Flagged, not resolved.</t>
+        </is>
+      </c>
+      <c r="I146" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7 / §6): Send to Portal = Full View; enforcement model = FE display gate (view_mode). Standing rules cite bare Full View; build also requires WOL-approve (Open Q6).</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
@@ -7600,6 +10221,16 @@
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr"/>
+      <c r="H147" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Office User (gate: Work Order Lines -&gt; Create &amp; Edit (spec §1b/§13)).</t>
+        </is>
+      </c>
+      <c r="I147" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: add a new line = WO Lines Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -7633,6 +10264,16 @@
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr"/>
+      <c r="H148" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Office User (gate: WO sub-setting 'Review WOs' (spec §B WO Sub-Settings)).</t>
+        </is>
+      </c>
+      <c r="I148" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: 'Review WOs' is a WO sub-setting = FE display gate; no other standing rule addresses it.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -7666,6 +10307,16 @@
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr"/>
+      <c r="H149" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Office User (gate: See Financial Data toggle (spec §5a)).</t>
+        </is>
+      </c>
+      <c r="I149" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: See Financial Data is the app-wide toggle gating Part Sales/Invoicing/Order Parts/Manage AP/AR (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -7699,6 +10350,16 @@
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr"/>
+      <c r="H150" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Office User (gate: Invoicing -&gt; View; SFD gates Invoicing (spec §1i/§5a)).</t>
+        </is>
+      </c>
+      <c r="I150" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Invoicing View gates the Finance tab; SFD gates Invoicing (enforcement: resource View).</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
@@ -7732,6 +10393,16 @@
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr"/>
+      <c r="H151" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Office User holds the gate: Invoicing -&gt; Create &amp; Edit (spec §1i, Open Q4)).</t>
+        </is>
+      </c>
+      <c r="I151" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: payments = Invoicing Create&amp;Edit; the Office-cannot-create-invoices hard-coded rule does NOT block Office from taking payment.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -7769,6 +10440,16 @@
           <t>Send-to-Terminal is ORG-DEVICE gated, NOT role/permission gated (Pass-12): prod org has no terminal -&gt; hidden for all; staging org HAS a terminal -&gt; shows for any role that can open New Payment. Not a migration/role difference.</t>
         </is>
       </c>
+      <c r="H152" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Office User has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+      <c r="I152" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
@@ -7802,6 +10483,16 @@
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr"/>
+      <c r="H153" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Office User; gate: Work Orders -&gt; Create &amp; Edit (spec §11, 07 Jul; WO-level audit log)).</t>
+        </is>
+      </c>
+      <c r="I153" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: History logs split WO-level (WO Create&amp;Edit) vs line-level (WOL Create&amp;Edit); WO-level = WO Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -7835,6 +10526,16 @@
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr"/>
+      <c r="H154" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Office User; gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="I154" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -7868,6 +10569,16 @@
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr"/>
+      <c r="H155" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Office User (gate: Work Orders -&gt; View (create/edit any note) (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I155" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: WO View = create/edit ANY note; WO Delete = delete any note (every role with WO View can see/add notes).</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
@@ -7901,6 +10612,16 @@
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr"/>
+      <c r="H156" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Office User (gate: Timesheets -&gt; View (spec §1j); clock-in/out + My Timesheets always on).</t>
+        </is>
+      </c>
+      <c r="I156" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: clock in/out + 'My Timesheets' always available regardless of Timesheets perm; the tab tracks Timesheets View (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -7938,6 +10659,16 @@
           <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
+      <c r="H157" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Office User; gate: Work Orders -&gt; Delete (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I157" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: enforcement model — Delete is a FE display gate (BE enforces only View/Edit); WO Delete also gates Reverse Invoice.</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
@@ -7971,6 +10702,16 @@
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr"/>
+      <c r="H158" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Office User; gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I158" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -8004,6 +10745,16 @@
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr"/>
+      <c r="H159" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected reduction (spec does not grant to Office User; gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I159" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
@@ -8041,6 +10792,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Office User via approve-decline-REALHOLDER-ALL.json (perms 25, rendered, Needs Approval present, no Approve). Prod: Office User.</t>
         </is>
       </c>
+      <c r="H160" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Office User (gate: WO Lines -&gt; Create &amp; Edit + Full View (Open Q6)).</t>
+        </is>
+      </c>
+      <c r="I160" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: approve a line = WOL Create&amp;Edit + Full View (FE gate); View Mode is UX not security, but approve is FE-gated by Full View.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
@@ -8078,6 +10839,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Office User via approve-decline-REALHOLDER-ALL.json (perms 25, rendered, Needs Approval present, no Approve). Prod: Office User.</t>
         </is>
       </c>
+      <c r="H161" s="14" t="inlineStr">
+        <is>
+          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+        </is>
+      </c>
+      <c r="I161" s="14" t="inlineStr">
+        <is>
+          <t>No standing rule addresses Decline/Set Line Status as a discrete action (grouped with approve under WOL Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
@@ -8115,6 +10886,16 @@
           <t>prod portal org-customer-portal gated</t>
         </is>
       </c>
+      <c r="H162" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: View Mode = Full View (spec §3/§4); Open Q6 also: 'anyone who can approve a WOL').</t>
+        </is>
+      </c>
+      <c r="I162" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7 / §6): Send to Portal = Full View; enforcement model = FE display gate (view_mode). Standing rules cite bare Full View; build also requires WOL-approve (Open Q6).</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
@@ -8148,6 +10929,16 @@
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr"/>
+      <c r="H163" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Work Order Lines -&gt; Create &amp; Edit (spec §1b/§13)).</t>
+        </is>
+      </c>
+      <c r="I163" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: add a new line = WO Lines Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -8181,6 +10972,16 @@
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr"/>
+      <c r="H164" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: WO sub-setting 'Review WOs' (spec §B WO Sub-Settings)).</t>
+        </is>
+      </c>
+      <c r="I164" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: 'Review WOs' is a WO sub-setting = FE display gate; no other standing rule addresses it.</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
@@ -8214,6 +11015,16 @@
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr"/>
+      <c r="H165" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: See Financial Data toggle (spec §5a)).</t>
+        </is>
+      </c>
+      <c r="I165" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: See Financial Data is the app-wide toggle gating Part Sales/Invoicing/Order Parts/Manage AP/AR (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
@@ -8247,6 +11058,16 @@
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr"/>
+      <c r="H166" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Invoicing -&gt; View; SFD gates Invoicing (spec §1i/§5a)).</t>
+        </is>
+      </c>
+      <c r="I166" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Invoicing View gates the Finance tab; SFD gates Invoicing (enforcement: resource View).</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
@@ -8284,6 +11105,16 @@
           <t>STAGING observed hidden (role cannot open Finance/New Payment; wocaps-obs.json newPayment=false, live role-scoped session). PROD hidden.</t>
         </is>
       </c>
+      <c r="H167" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Invoicing -&gt; Create &amp; Edit (spec §1i, Open Q4)).</t>
+        </is>
+      </c>
+      <c r="I167" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: payments = Invoicing Create&amp;Edit; the Office-cannot-create-invoices hard-coded rule does NOT block Office from taking payment.</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -8321,6 +11152,16 @@
           <t>Send-to-Terminal is ORG-DEVICE gated, NOT role/permission gated (Pass-12): prod org has no terminal -&gt; hidden for all; staging org HAS a terminal -&gt; shows for any role that can open New Payment. Not a migration/role difference.</t>
         </is>
       </c>
+      <c r="H168" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — Time Clock User cannot open New Payment (no Invoicing C&amp;E) so Send to Terminal is unreachable. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+      <c r="I168" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
@@ -8354,6 +11195,16 @@
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr"/>
+      <c r="H169" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Work Orders -&gt; Create &amp; Edit (spec §11, 07 Jul; WO-level audit log)).</t>
+        </is>
+      </c>
+      <c r="I169" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: History logs split WO-level (WO Create&amp;Edit) vs line-level (WOL Create&amp;Edit); WO-level = WO Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
@@ -8387,6 +11238,16 @@
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr"/>
+      <c r="H170" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="I170" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
@@ -8420,6 +11281,16 @@
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr"/>
+      <c r="H171" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Time Clock User holds the gate: Work Orders -&gt; View (create/edit any note) (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I171" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: WO View = create/edit ANY note; WO Delete = delete any note (every role with WO View can see/add notes).</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -8453,6 +11324,16 @@
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr"/>
+      <c r="H172" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Time Clock User holds the gate: Timesheets -&gt; View (spec §1j); clock-in/out + My Timesheets always on).</t>
+        </is>
+      </c>
+      <c r="I172" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: clock in/out + 'My Timesheets' always available regardless of Timesheets perm; the tab tracks Timesheets View (FE gate).</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
@@ -8490,6 +11371,16 @@
           <t>observed on estimate WO (deletable state)</t>
         </is>
       </c>
+      <c r="H173" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Work Orders -&gt; Delete (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="I173" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: enforcement model — Delete is a FE display gate (BE enforces only View/Edit); WO Delete also gates Reverse Invoice.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
@@ -8523,6 +11414,16 @@
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr"/>
+      <c r="H174" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I174" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
@@ -8556,6 +11457,16 @@
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr"/>
+      <c r="H175" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Work Orders -&gt; Create &amp; Edit (spec §1a/§14)).</t>
+        </is>
+      </c>
+      <c r="I175" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: change customer/asset on an existing WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
@@ -8593,6 +11504,16 @@
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Time Clock User via approve-decline-RETRY.json (perms 3, rendered, Needs Approval present, no Approve). Prod: Time Clock User.</t>
         </is>
       </c>
+      <c r="H176" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: WO Lines -&gt; Create &amp; Edit + Full View (Open Q6)).</t>
+        </is>
+      </c>
+      <c r="I176" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: approve a line = WOL Create&amp;Edit + Full View (FE gate); View Mode is UX not security, but approve is FE-gated by Full View.</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
@@ -8628,6 +11549,23 @@
       <c r="G177" s="5" t="inlineStr">
         <is>
           <t>LIVE-OBSERVED both envs 2026-07-16. Staging: Time Clock User via approve-decline-RETRY.json (perms 3, rendered, Needs Approval present, no Approve). Prod: Time Clock User.</t>
+        </is>
+      </c>
+      <c r="H177" s="14" t="inlineStr">
+        <is>
+          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+        </is>
+      </c>
+      <c r="I177" s="14" t="inlineStr">
+        <is>
+          <t>No standing rule addresses Decline/Set Line Status as a discrete action (grouped with approve under WOL Create&amp;Edit).</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="30" t="inlineStr">
+        <is>
+          <t>LEGEND — 'Per Spec (v2)?': Per spec-expected/matches | DEVIATION (spec grants/withholds opposite of staging) | Spec silent (not addressed) | Spec inconsistent/ambiguous | Org-device config gate (out of role model). 'Per Standing Instructions?': Consistent / Conflicts / No rule — cites the specific standing rule. Existing observed verdicts UNCHANGED; columns are ADDED.</t>
         </is>
       </c>
     </row>
@@ -8642,13 +11580,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="54" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8707,6 +11647,16 @@
           <t>Dual verdict</t>
         </is>
       </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Per Spec (v2)?</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Per Standing Instructions?</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -8729,6 +11679,16 @@
           <t>STAGING-MORE (ORG-CONFIG only: staging org has a terminal device, prod org has none; NOT a role/migration difference)</t>
         </is>
       </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (role-gate met) + Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.  Admin meets the spec role-gate; the observed staging-vs-prod difference is ORG-CONFIG, not role/migration.</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -8751,6 +11711,16 @@
           <t>STAGING-MORE (ORG-CONFIG only: staging org has a terminal device, prod org has none; NOT a role/migration difference)</t>
         </is>
       </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (role-gate met) + Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.  Service Manager meets the spec role-gate; the observed staging-vs-prod difference is ORG-CONFIG, not role/migration.</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -8773,6 +11743,16 @@
           <t>STAGING-MORE (ORG-CONFIG only: staging org has a terminal device, prod org has none; NOT a role/migration difference)</t>
         </is>
       </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (role-gate met) + Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.  Senior Service Advisor meets the spec role-gate; the observed staging-vs-prod difference is ORG-CONFIG, not role/migration.</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -8795,6 +11775,16 @@
           <t>STAGING-MORE (ORG-CONFIG only: staging org has a terminal device, prod org has none; NOT a role/migration difference)</t>
         </is>
       </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (role-gate met) + Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.  Parts Manager meets the spec role-gate; the observed staging-vs-prod difference is ORG-CONFIG, not role/migration.</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -8817,6 +11807,16 @@
           <t>STAGING-MORE (ORG-CONFIG only: staging org has a terminal device, prod org has none; NOT a role/migration difference)</t>
         </is>
       </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (role-gate met) + Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.  Service Advisor meets the spec role-gate; the observed staging-vs-prod difference is ORG-CONFIG, not role/migration.</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -8839,6 +11839,16 @@
           <t>STAGING-MORE (ORG-CONFIG only: staging org has a terminal device, prod org has none; NOT a role/migration difference)</t>
         </is>
       </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Foreman has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -8861,6 +11871,16 @@
           <t>STAGING-MORE (ORG-CONFIG only: staging org has a terminal device, prod org has none; NOT a role/migration difference)</t>
         </is>
       </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Office User has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -8883,6 +11903,16 @@
           <t>STAGING-MORE (ORG-CONFIG only: staging org has a terminal device, prod org has none; NOT a role/migration difference)</t>
         </is>
       </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Parts Technician has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -8905,6 +11935,16 @@
           <t>MATCH (both hidden)</t>
         </is>
       </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — Sales Representative cannot open New Payment (no Invoicing C&amp;E) so Send to Terminal is unreachable. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -8927,6 +11967,16 @@
           <t>MATCH (both hidden)</t>
         </is>
       </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — Technician cannot open New Payment (no Invoicing C&amp;E) so Send to Terminal is unreachable. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -8947,6 +11997,23 @@
       <c r="D18" s="28" t="inlineStr">
         <is>
           <t>MATCH (both hidden)</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — Time Clock User cannot open New Payment (no Invoicing C&amp;E) so Send to Terminal is unreachable. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule (Rule 3.7): Send to Terminal = Invoicing C&amp;E + Customer Portal ON; PLUS the build adds an org-device config gate. Enforcement: FE + org-config.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>LEGEND — 'Per Spec (v2)?': Per spec-expected/matches | DEVIATION (spec grants/withholds opposite of staging) | Spec silent (not addressed) | Spec inconsistent/ambiguous | Org-device config gate (out of role model). 'Per Standing Instructions?': Consistent / Conflicts / No rule — cites the specific standing rule. Existing observed verdicts UNCHANGED; columns are ADDED.</t>
         </is>
       </c>
     </row>
@@ -8961,7 +12028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9578,6 +12645,13 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>NOTE (2026-07-16): This tab is a STAGING-ONLY raw observation grid (per-capability columns, no prod comparison / no dual verdict), so it does not carry the row-level 'Per Spec (v2)?' / 'Per Standing Instructions?' annotation columns. Per-capability spec + standing-instruction conformance for every role x capability is annotated on the dual-verdict tabs (Full Dual Matrix, Pass-11, Pass-12, Approve-Decline LIVE, Send to Terminal LIVE, Parts-Module Dual LIVE, New-WO Create Dual LIVE) and summarized on the 'Spec-Standing Conformance' tab.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9589,7 +12663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9603,6 +12677,8 @@
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="46" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1">
@@ -9668,6 +12744,16 @@
           <t>Staging screenshot / Notes</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Per Spec (v2)?</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Per Standing Instructions?</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -9725,6 +12811,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
         </is>
       </c>
+      <c r="L3" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="M3" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -9782,6 +12878,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
         </is>
       </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Vendor &amp; Order Management -&gt; Create &amp; Edit (receive/return parts, spec §1g)).</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: receiving/returning parts to inventory/vendors = Vendor &amp; Order Management Create&amp;Edit (resource Edit). No more specific standing rule.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -9839,6 +12945,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
         </is>
       </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -9896,6 +13012,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
         </is>
       </c>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: Vendor &amp; Order Management -&gt; Create &amp; Edit (receive/return parts, spec §1g)).</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: receiving/returning parts to inventory/vendors = Vendor &amp; Order Management Create&amp;Edit (resource Edit). No more specific standing rule.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -9953,6 +13079,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/parts_orders.png  prod merge: Service Advisor (+ SA Technician, SA No Reports) | Story: Order Parts controls the ability to create a purchase order. FE-gated. (merge components SA Technician, SA No Reports also SHOWN — consistent)</t>
         </is>
       </c>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="M7" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -10010,6 +13146,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/parts_orders.png  prod merge: Service Advisor (+ SA Technician, SA No Reports) | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button. (merge components SA Technician, SA No Reports also SHOWN — consistent)</t>
         </is>
       </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Vendor &amp; Order Management -&gt; Create &amp; Edit (receive/return parts, spec §1g)).</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: receiving/returning parts to inventory/vendors = Vendor &amp; Order Management Create&amp;Edit (resource Edit). No more specific standing rule.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -10067,6 +13213,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
         </is>
       </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Manager (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="M9" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -10124,6 +13280,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
         </is>
       </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Manager (gate: Vendor &amp; Order Management -&gt; Create &amp; Edit (receive/return parts, spec §1g)).</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: receiving/returning parts to inventory/vendors = Vendor &amp; Order Management Create&amp;Edit (resource Edit). No more specific standing rule.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -10181,6 +13347,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/parts_orders.png  confirmed mapping: staging Service Advisor &lt;- prod SA Limited View | Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
         </is>
       </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -10238,6 +13414,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/parts_orders.png  confirmed mapping: staging Service Advisor &lt;- prod SA Limited View | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
         </is>
       </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Vendor &amp; Order Management -&gt; Create &amp; Edit (receive/return parts, spec §1g)).</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: receiving/returning parts to inventory/vendors = Vendor &amp; Order Management Create&amp;Edit (resource Edit). No more specific standing rule.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -10295,6 +13481,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/parts_orders.png  prod: Parts nav hidden but /parts/orders reachable directly | Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
         </is>
       </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -10352,6 +13548,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/parts_orders.png  prod: Parts nav hidden but /parts/orders reachable directly | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
         </is>
       </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Vendor &amp; Order Management -&gt; Create &amp; Edit (receive/return parts, spec §1g)).</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: receiving/returning parts to inventory/vendors = Vendor &amp; Order Management Create&amp;Edit (resource Edit). No more specific standing rule.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -10409,6 +13615,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/parts_orders.png  both envs: /parts/orders page viewable, but no New PO / no Receive | Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
         </is>
       </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Office User (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -10466,6 +13682,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/parts_orders.png  both envs: /parts/orders page viewable, but no New PO / no Receive | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
         </is>
       </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Office User (gate: Vendor &amp; Order Management -&gt; Create &amp; Edit (receive/return parts, spec §1g)).</t>
+        </is>
+      </c>
+      <c r="M16" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: receiving/returning parts to inventory/vendors = Vendor &amp; Order Management Create&amp;Edit (resource Edit). No more specific standing rule.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -10523,6 +13749,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
         </is>
       </c>
+      <c r="L17" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Technician (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="M17" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -10580,6 +13816,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
         </is>
       </c>
+      <c r="L18" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Parts Technician (gate: Vendor &amp; Order Management -&gt; Create &amp; Edit (receive/return parts, spec §1g)).</t>
+        </is>
+      </c>
+      <c r="M18" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: receiving/returning parts to inventory/vendors = Vendor &amp; Order Management Create&amp;Edit (resource Edit). No more specific standing rule.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -10637,6 +13883,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/parts_orders.png  prod merge: Sales Representative (+ Reporting) | Story: Order Parts controls the ability to create a purchase order. FE-gated. (merge components Reporting also hidden — consistent)</t>
         </is>
       </c>
+      <c r="L19" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="M19" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -10694,6 +13950,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/parts_orders.png  prod merge: Sales Representative (+ Reporting) | Pick/Receive against an ordered PO. FE-gated; per-PO Receive button. (merge components Reporting also hidden — consistent)</t>
         </is>
       </c>
+      <c r="L20" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Vendor &amp; Order Management -&gt; Create &amp; Edit (receive/return parts, spec §1g)).</t>
+        </is>
+      </c>
+      <c r="M20" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: receiving/returning parts to inventory/vendors = Vendor &amp; Order Management Create&amp;Edit (resource Edit). No more specific standing rule.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -10751,6 +14017,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
         </is>
       </c>
+      <c r="L21" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="M21" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -10808,6 +14084,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
         </is>
       </c>
+      <c r="L22" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: Vendor &amp; Order Management -&gt; Create &amp; Edit (receive/return parts, spec §1g)).</t>
+        </is>
+      </c>
+      <c r="M22" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: receiving/returning parts to inventory/vendors = Vendor &amp; Order Management Create&amp;Edit (resource Edit). No more specific standing rule.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -10865,6 +14151,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/parts_orders.png  Story: Order Parts controls the ability to create a purchase order. FE-gated.</t>
         </is>
       </c>
+      <c r="L23" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: WO sub-setting 'Order Parts' (woOrderParts; needs WO View + SFD) (spec §1a/§7)).</t>
+        </is>
+      </c>
+      <c r="M23" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Order Parts requires See Financial Data and controls the WO Parts tab (FE sub-setting gate).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -10920,6 +14216,23 @@
       <c r="K24" s="5" t="inlineStr">
         <is>
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/parts_orders.png  Pick/Receive against an ordered PO. FE-gated; per-PO Receive button.</t>
+        </is>
+      </c>
+      <c r="L24" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Vendor &amp; Order Management -&gt; Create &amp; Edit (receive/return parts, spec §1g)).</t>
+        </is>
+      </c>
+      <c r="M24" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with enforcement model: receiving/returning parts to inventory/vendors = Vendor &amp; Order Management Create&amp;Edit (resource Edit). No more specific standing rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>LEGEND — 'Per Spec (v2)?': Per spec-expected/matches | DEVIATION (spec grants/withholds opposite of staging) | Spec silent (not addressed) | Spec inconsistent/ambiguous | Org-device config gate (out of role model). 'Per Standing Instructions?': Consistent / Conflicts / No rule — cites the specific standing rule. Existing observed verdicts UNCHANGED; columns are ADDED.</t>
         </is>
       </c>
     </row>
@@ -10937,7 +14250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10951,6 +14264,8 @@
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="46" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="55" customHeight="1">
@@ -11016,6 +14331,16 @@
           <t>Staging screenshot / Notes</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Per Spec (v2)?</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Per Standing Instructions?</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -11073,6 +14398,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L3" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Work Orders -&gt; Create &amp; Edit (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="M3" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: create a WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -11130,6 +14465,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Customer Management -&gt; Create &amp; Edit (create customer in New-WO flow, 01 Jun; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Create/Edit customer also drives create-a-customer in the New-WO flow (Customer Management Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -11187,6 +14532,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Admin/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
         </is>
       </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Customer Management -&gt; Create &amp; Edit (manage vehicles; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: manage vehicles = Customer Management Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -11244,6 +14599,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: Work Orders -&gt; Create &amp; Edit (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: create a WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -11301,6 +14666,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: Customer Management -&gt; Create &amp; Edit (create customer in New-WO flow, 01 Jun; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M7" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Create/Edit customer also drives create-a-customer in the New-WO flow (Customer Management Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -11358,6 +14733,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Manager/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
         </is>
       </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: Customer Management -&gt; Create &amp; Edit (manage vehicles; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: manage vehicles = Customer Management Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -11415,6 +14800,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog. (merge SA Technician, SA No Reports also SHOWN — consistent)</t>
         </is>
       </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Work Orders -&gt; Create &amp; Edit (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="M9" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: create a WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -11472,6 +14867,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog. (merge SA Technician, SA No Reports also SHOWN — consistent)</t>
         </is>
       </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Customer Management -&gt; Create &amp; Edit (create customer in New-WO flow, 01 Jun; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Create/Edit customer also drives create-a-customer in the New-WO flow (Customer Management Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -11529,6 +14934,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Senior_Service_Advisor/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported. (merge SA Technician, SA No Reports also SHOWN — consistent)</t>
         </is>
       </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Customer Management -&gt; Create &amp; Edit (manage vehicles; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: manage vehicles = Customer Management Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -11586,6 +15001,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Parts Manager holds the gate: Work Orders -&gt; Create &amp; Edit (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: create a WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -11643,6 +15068,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Parts Manager holds the gate: Customer Management -&gt; Create &amp; Edit (create customer in New-WO flow, 01 Jun; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Create/Edit customer also drives create-a-customer in the New-WO flow (Customer Management Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -11700,6 +15135,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Manager/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
         </is>
       </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Parts Manager holds the gate: Customer Management -&gt; Create &amp; Edit (manage vehicles; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: manage vehicles = Customer Management Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -11757,6 +15202,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Work Orders -&gt; Create &amp; Edit (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: create a WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -11814,6 +15269,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Customer Management -&gt; Create &amp; Edit (create customer in New-WO flow, 01 Jun; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M16" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Create/Edit customer also drives create-a-customer in the New-WO flow (Customer Management Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -11871,6 +15336,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Service_Advisor/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
         </is>
       </c>
+      <c r="L17" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Customer Management -&gt; Create &amp; Edit (manage vehicles; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M17" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: manage vehicles = Customer Management Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -11928,6 +15403,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/new_wo_dialog.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L18" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Work Orders -&gt; Create &amp; Edit (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="M18" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: create a WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -11985,6 +15470,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/new_wo_dialog.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L19" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Customer Management -&gt; Create &amp; Edit (create customer in New-WO flow, 01 Jun; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M19" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Create/Edit customer also drives create-a-customer in the New-WO flow (Customer Management Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -12042,6 +15537,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Foreman/new_wo_dialog.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
         </is>
       </c>
+      <c r="L20" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Customer Management -&gt; Create &amp; Edit (manage vehicles; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M20" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: manage vehicles = Customer Management Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -12099,6 +15604,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L21" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Office User (gate: Work Orders -&gt; Create &amp; Edit (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="M21" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: create a WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -12156,6 +15671,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L22" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Office User (gate: Customer Management -&gt; Create &amp; Edit (create customer in New-WO flow, 01 Jun; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M22" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Create/Edit customer also drives create-a-customer in the New-WO flow (Customer Management Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -12213,6 +15738,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Office_User/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
         </is>
       </c>
+      <c r="L23" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Office User (gate: Customer Management -&gt; Create &amp; Edit (manage vehicles; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M23" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: manage vehicles = Customer Management Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -12270,6 +15805,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L24" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Work Orders -&gt; Create &amp; Edit (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="M24" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: create a WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -12327,6 +15872,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L25" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Customer Management -&gt; Create &amp; Edit (create customer in New-WO flow, 01 Jun; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M25" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Create/Edit customer also drives create-a-customer in the New-WO flow (Customer Management Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -12384,6 +15939,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Parts_Technician/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
         </is>
       </c>
+      <c r="L26" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Customer Management -&gt; Create &amp; Edit (manage vehicles; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M26" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: manage vehicles = Customer Management Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -12441,6 +16006,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog. (merge Reporting also hidden — consistent)</t>
         </is>
       </c>
+      <c r="L27" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Work Orders -&gt; Create &amp; Edit (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="M27" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: create a WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -12498,6 +16073,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog. (merge Reporting also hidden — consistent)</t>
         </is>
       </c>
+      <c r="L28" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Customer Management -&gt; Create &amp; Edit (create customer in New-WO flow, 01 Jun; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M28" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Create/Edit customer also drives create-a-customer in the New-WO flow (Customer Management Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -12555,6 +16140,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Sales_Representative/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported. (merge Reporting also hidden — consistent)</t>
         </is>
       </c>
+      <c r="L29" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Customer Management -&gt; Create &amp; Edit (manage vehicles; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M29" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: manage vehicles = Customer Management Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -12612,6 +16207,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L30" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: Work Orders -&gt; Create &amp; Edit (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="M30" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: create a WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -12669,6 +16274,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L31" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: Customer Management -&gt; Create &amp; Edit (create customer in New-WO flow, 01 Jun; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M31" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Create/Edit customer also drives create-a-customer in the New-WO flow (Customer Management Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -12726,6 +16341,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Technician/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
         </is>
       </c>
+      <c r="L32" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: Customer Management -&gt; Create &amp; Edit (manage vehicles; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M32" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: manage vehicles = Customer Management Create&amp;Edit.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -12783,6 +16408,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/new_wo_nobutton.png  workOrdersCreateAndEdit — opens the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L33" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Work Orders -&gt; Create &amp; Edit (spec §1a)).</t>
+        </is>
+      </c>
+      <c r="M33" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: create a WO = WO Create&amp;Edit (BE-enforced resource Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -12840,6 +16475,16 @@
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/new_wo_nobutton.png  customersCreateAndEdit — the inline Add button in the New Work Order dialog.</t>
         </is>
       </c>
+      <c r="L34" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Customer Management -&gt; Create &amp; Edit (create customer in New-WO flow, 01 Jun; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M34" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: Create/Edit customer also drives create-a-customer in the New-WO flow (Customer Management Create&amp;Edit).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -12895,6 +16540,23 @@
       <c r="K35" s="5" t="inlineStr">
         <is>
           <t>/home/user/Manual-test-Cases/build/custom-roles-run/live-ui-2026-07-15/staging/Time_Clock_User/new_wo_nobutton.png  assetsCreateAndEdit — Add button present; enabled only after a customer is chosen (design gate), so presence is reported.</t>
+        </is>
+      </c>
+      <c r="L35" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Customer Management -&gt; Create &amp; Edit (manage vehicles; behind WO Create&amp;Edit)).</t>
+        </is>
+      </c>
+      <c r="M35" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule: manage vehicles = Customer Management Create&amp;Edit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>LEGEND — 'Per Spec (v2)?': Per spec-expected/matches | DEVIATION (spec grants/withholds opposite of staging) | Spec silent (not addressed) | Spec inconsistent/ambiguous | Org-device config gate (out of role model). 'Per Standing Instructions?': Consistent / Conflicts / No rule — cites the specific standing rule. Existing observed verdicts UNCHANGED; columns are ADDED.</t>
         </is>
       </c>
     </row>
@@ -12912,7 +16574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A2:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -12920,9 +16582,10 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
@@ -12960,6 +16623,16 @@
           <t>Evidence / method (observed-only)</t>
         </is>
       </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Per Spec (v2)?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Per Standing Instructions?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -12987,6 +16660,16 @@
           <t>stg: live-ui-2026-07-16/staging/approve-decline-realholder.json + approve_decline_realholder.png  |  prod: live-ui-2026-07-16/production/approve-decline-ALL.json</t>
         </is>
       </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Admin (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -13014,6 +16697,16 @@
           <t>stg: approve-decline-REALHOLDER-ALL.json + Service_Manager/approve_decline_p12b.png (perms 36, rendered, needsApproval)  |  prod: approve-decline-ALL.json</t>
         </is>
       </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -13041,6 +16734,16 @@
           <t>stg: approve-decline-REALHOLDER-ALL.json (perms 31) + approve_decline_p12b.png  |  prod: approve-decline-ALL.json (SA/SA-Tech/SA-NoRep all approve=true)</t>
         </is>
       </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -13068,6 +16771,16 @@
           <t>stg: approve-decline-REALHOLDER-ALL.json (perms 25) + approve_decline_p12b.png  |  prod: approve-decline-ALL.json (Service Advisor - Limited View approve=true)</t>
         </is>
       </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -13095,6 +16808,16 @@
           <t>stg: approve-decline-REALHOLDER-ALL.json (perms 23) + approve_decline_p12b.png  |  prod: approve-decline-ALL.json</t>
         </is>
       </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -13122,6 +16845,16 @@
           <t>stg: approve-decline-TECH-PT.json (quick-login tech, perms 6, rendered, Needs Approval present, no Approve/Decline) + Technician/approve_decline_techkey.png  |  prod: approve-decline-ALL.json (Technician rendered, approve=false)</t>
         </is>
       </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -13149,6 +16882,16 @@
           <t>stg: approve-decline-REALHOLDER-ALL.json (perms 31, rendered, Approve=true) + approve_decline_p12b.png  |  prod: approve-decline-ALL.json (Parts Manager rendered, approve=false)</t>
         </is>
       </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Per spec — expected grant (Parts Manager holds the gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -13176,6 +16919,16 @@
           <t>stg: live-ui-2026-07-15/staging/Parts_Technician/refwo-caps.json (staff/change 201, su 200, perms 19, rendered=true, zero line-action buttons)  |  prod: approve-decline-ALL.json (Parts Technician rendered, approve=false)</t>
         </is>
       </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -13203,6 +16956,16 @@
           <t>stg: approve-decline-REALHOLDER-ALL.json (perms 25, rendered, Needs Approval present, no Approve) + Office_User/approve_decline_p12b.png  |  prod: approve-decline-ALL.json (Office User rendered, approve=false)</t>
         </is>
       </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Office User (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -13230,6 +16993,16 @@
           <t>stg: approve-decline-RETRY.json (perms 8, rendered, Needs Approval present, no Approve) + Sales_Representative/approve_decline_retry.png  |  prod: approve-decline-ALL.json (Sales Rep WO-detail bounced = no access = HIDDEN)</t>
         </is>
       </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -13255,6 +17028,23 @@
       <c r="E14" s="5" t="inlineStr">
         <is>
           <t>stg: approve-decline-RETRY.json (perms 3, rendered, Needs Approval present, no Approve) + Time_Clock_User/approve_decline_retry.png  |  prod: approve-decline-ALL.json (Time Clock WO-detail bounced = no access = HIDDEN)</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Consistent with standing rule for Approve (WOL Create&amp;Edit + Full View, FE gate); NO standing rule addresses Decline as a discrete action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>LEGEND — 'Per Spec (v2)?': Per spec-expected/matches | DEVIATION (spec grants/withholds opposite of staging) | Spec silent (not addressed) | Spec inconsistent/ambiguous | Org-device config gate (out of role model). 'Per Standing Instructions?': Consistent / Conflicts / No rule — cites the specific standing rule. Existing observed verdicts UNCHANGED; columns are ADDED.</t>
         </is>
       </c>
     </row>

--- a/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
+++ b/build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A80"/>
+  <dimension ref="A1:A88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="124" customWidth="1" min="1" max="1"/>
@@ -874,9 +874,6 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-    </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
@@ -929,21 +926,21 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * 'Spec silent — not addressed'   : the spec has no rule for this capability (Issue Credit; Decline/Set Line Status; remove-a-WO-part atom). NOT inferred.</t>
+          <t xml:space="preserve">  * 'Spec silent — not addressed'   : row-level NONE after the 2026-07-16 re-audit (Issue Credit stays spec-silent as a component inside the Finance rows; remove-a-WO-part atom has no annotated row). NOT inferred.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * 'Spec inconsistent/ambiguous'   : the spec contradicts itself for this role/capability (Send to Portal §3/§4 Full-View vs Open Q6 'can approve a WOL';</t>
+          <t xml:space="preserve">  * 'Spec inconsistent/ambiguous'   : the spec contradicts itself for this role/capability (Send to Portal §3/§4 Full-View vs Open Q6 'can approve a WOL' for Office/Parts-Tech/Sales-Rep;</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                      Core OK/Not-OK §1b/03-Jul WOL-C&amp;E vs Key-Decision/07-Jul WO-View). Flagged, never resolved by inference.</t>
+          <t xml:space="preserve">                                      Technician Decline — §1b 'authorize lines' vs §4 approve-only Tech View; Service Manager Reverse — matrix+28-Jun vs migration-table 'cannot reverse'). Flagged, never resolved by inference.</t>
         </is>
       </c>
     </row>
@@ -961,9 +958,6 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
-    </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
@@ -1013,62 +1007,108 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr"/>
-    </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>HEADLINE CONFORMANCE RESULT (297 role x capability rows annotated across 7 tabs):</t>
+          <t>HEADLINE CONFORMANCE RESULT (297 role x capability rows annotated across 7 tabs) — RE-AUDITED + CORRECTED 2026-07-16:</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Per-spec (expected/matches): 276   |   DEVIATION: 7   |   Spec silent: 11   |   Spec inconsistent/ambiguous: 3</t>
+          <t xml:space="preserve">  Per-spec (expected/matches): 283   |   DEVIATION: 9   |   Spec silent: 0 (row-level)   |   Spec inconsistent/ambiguous: 5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">  =&gt; The migration is LARGELY SPEC-ACCURATE: every STAGING-LESS loss and nearly every STAGING-MORE grant maps to an intended spec gate.</t>
+          <t xml:space="preserve">  =&gt; The migration is LARGELY SPEC-ACCURATE: every STAGING-LESS loss and nearly every STAGING-MORE grant maps to an intended spec gate. The non-per-spec rows:</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The only flags: (1) Send to Terminal for Foreman/Office User/Parts Technician = DEVIATION (gating model): build shows it via org-device</t>
+          <t xml:space="preserve">  (1) Send to Terminal for Foreman/Office User/Parts Technician = DEVIATION (gating model): build shows it via the org-device gate although the spec</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">      gate although the spec role-gate requires Customer Portal ON (which those 3 roles have OFF). Org-config, not a role over-grant.</t>
+          <t xml:space="preserve">      role-gate requires Customer Portal ON (those 3 roles have it OFF). Org-config, not a role over-grant. (6 rows across 2 tabs.)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (2) See AP/AR for Senior Service Advisor = DEVIATION: spec grants it (Manage AP/AR ON + Reports ON) but BOTH envs hide it (a MATCH row) —</t>
+          <t xml:space="preserve">  (2) See AP/AR aging for Senior Service Advisor = DEVIATION: spec grants (Reports ON; Manage AP/AR also ON) but BOTH envs hide it — staging does not implement the grant.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">      staging does not implement the spec grant for SSA. (3) Send to Portal for Office User/Parts Tech (STAGING-LESS) + Sales Rep (MATCH) =</t>
+          <t xml:space="preserve">  (3) Office User WO Notes (both envs SHOWN) + Part Return (STAGING-MORE) = DEVIATION: the 14-Jul spec update removed ALL Work Orders access for Office User</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Spec inconsistent/ambiguous (bare Full-View reading vs Open Q6 'can approve a WOL'). See the 'Spec-Standing Conformance' tab.</t>
+          <t xml:space="preserve">      (Work Orders = '—'), so neither surface should be reachable for Office; staging (and prod) still show them. [Corrected 2026-07-16 — previously wrongly 'per spec'.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (4) Spec inconsistent/ambiguous (5): Send to Portal for Office User/Parts Tech (STAGING-LESS) + Sales Rep (MATCH) — Full-View vs Open Q6; Technician Decline —</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      §1b 'authorize lines' vs §4 approve-only Tech View; Service Manager Reverse Invoice — matrix+28-Jun (can reverse) vs migration table ('cannot reverse').</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>RE-AUDIT NOTE (2026-07-16): the 'Per Spec (v2)?' column was re-derived FROM SCRATCH against the canonical spec (current-spec-2026-07-15.md) after annotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  errors were found. Root causes fixed: the spec extract carried the pre-7/14 Office column (WO=V) -&gt; Office WO-Notes/Part-Return were wrongly 'per spec';</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Decline was wrongly blanket 'spec silent' (§1b 'authorize lines' addresses it); the New-WO Create-Customer/Asset rows cited a wrong gate reason (Office/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Parts-Tech/Sales-Rep DO hold Customer Mgmt C&amp;E — the control is absent for lack of WO C&amp;E); AP/AR-aging citations now lead with the operative Reports gate;</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SM Reverse-Invoice flagged spec-inconsistent. Full role x gate truth table + diff: build/custom-roles-run/spec-conformance/spec-truth-table.md.</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1120,428 +1160,576 @@
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
         <is>
-          <t>TALLY (297 annotated rows across 7 tabs):</t>
+          <t>TALLY (297 annotated rows across 7 tabs) — RE-AUDITED + CORRECTED 2026-07-16 (every annotation re-derived from scratch against current-spec-2026-07-15.md; derivation + diff: spec-conformance/spec-truth-table.md):</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Per spec — expected / matches</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>276</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>STAGING grant/withhold agrees with the spec gate (intended).</t>
+      <c r="B7" s="14" t="n">
+        <v>283</v>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>STAGING grant/withhold agrees with the spec gate (intended). Includes the 10 Decline rows re-derived via §1b 'authorize lines' (previously mislabeled spec-silent).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>DEVIATION</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>STAGING is opposite of what the spec prescribes (incl. gating-model divergence).</t>
+      <c r="B8" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>STAGING is opposite of what the spec prescribes (incl. gating-model divergence and MATCH rows where BOTH envs disagree with the spec).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Spec silent — not addressed</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>11</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Spec has no rule (Decline/Set Line Status; Issue Credit; remove-a-WO-part atom).</t>
+      <c r="B9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Row-level: none after the re-audit. Issue Credit remains spec-silent as a COMPONENT inside the Finance rows; remove-a-WO-part as a discrete atom has no annotated row.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Spec inconsistent / ambiguous</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Spec contradicts itself (Send to Portal Full-View vs Open Q6 approve-a-WOL).</t>
+      <c r="B10" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>The spec contradicts itself for the role/capability — flagged, never resolved by inference.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr"/>
+      <c r="A11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>KEY SIGNAL: every STAGING-LESS loss and nearly every STAGING-MORE grant is a SPEC-ACCURATE gate change. The migration is largely faithful.</t>
+          <t>KEY SIGNAL: the migration is LARGELY SPEC-ACCURATE — every STAGING-LESS loss and nearly every STAGING-MORE grant maps to an intended spec gate. Non-per-spec rows below.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>Release-relevant DEVIATIONS / flags to review (the only non-per-spec rows):</t>
+          <t>Release-relevant DEVIATIONS (9 rows):</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Tab</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>Capability</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="31" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="31" t="inlineStr">
         <is>
           <t>Why (spec judgement)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Full Dual Matrix</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Foreman</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Send to Terminal</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>MORE</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Foreman has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Foreman has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-config, not a role over-grant. Spec role-gate = Invoicing C&amp;E + Customer Portal ON (§1i, 06 Jul).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Full Dual Matrix</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Parts Technician</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>Send to Terminal</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>MORE</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Parts Technician has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Parts Technician has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-config, not a role over-grant. Spec role-gate = Invoicing C&amp;E + Customer Portal ON (§1i, 06 Jul).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Full Dual Matrix</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>Office User</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>Send to Terminal</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>MORE</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Office User has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Office User has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-config, not a role over-grant. Spec role-gate = Invoicing C&amp;E + Customer Portal ON (§1i, 06 Jul).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Send to Terminal LIVE</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Foreman has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-config, not a role over-grant. Spec role-gate = Invoicing C&amp;E + Customer Portal ON (§1i, 06 Jul).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Send to Terminal LIVE</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Office User has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-config, not a role over-grant. Spec role-gate = Invoicing C&amp;E + Customer Portal ON (§1i, 06 Jul).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Send to Terminal LIVE</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Parts Technician</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Send to Terminal</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Parts Technician has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-config, not a role over-grant. Spec role-gate = Invoicing C&amp;E + Customer Portal ON (§1i, 06 Jul).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Pass-11 LIVE (2026-07-16)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Senior Service Advisor</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>See AP/AR</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>DEVIATION — spec grants to Senior Service Advisor (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)) but staging hides it (both envs hidden).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Send to Terminal LIVE</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Foreman</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MORE</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Foreman has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Send to Terminal LIVE</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>See AP/AR (aging reports)</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>MATCH (both hidden)</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION — spec grants (Reports = ON in the matrix; §2a aging follows Reports; Manage AP/AR also ON) but staging hides them — staging does not implement the spec grant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Full Dual Matrix</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Office User</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>MORE</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Office User has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Send to Terminal LIVE</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Parts Technician</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Send to Terminal</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>MORE</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>DEVIATION (gating model) — spec requires Customer Portal ON, which Parts Technician has OFF, so the spec ROLE-gate would WITHHOLD Send to Terminal; the build instead gates on org-device presence and shows it. Org-device config gate (NOT a role/spec delta): staging org has a card terminal, prod org has none. Spec role-gate = Invoicing C&amp;E + Customer Portal ON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr"/>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>WO Notes (Notes tab)</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>MATCH (both SHOWN)</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION — 14-Jul spec update removed ALL Work Orders access for Office User (WO = '—'), so the Notes tab should be unreachable; BOTH envs show it. [Corrected 2026-07-16 — was 'per spec'.]</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>SPEC-INCONSISTENT / AMBIGUOUS rows (flagged, not resolved — never inferred):</t>
+          <t>Pass-11 LIVE (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Office User</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Part Return</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>MORE</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>DEVIATION (reachability) — Return itself is ungated (29 Jun; §1a) but §1a requires WO view in practice and the 14-Jul matrix gives Office User NO Work Orders access; staging shows it. [Corrected 2026-07-16 — was 'per spec'.]</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>SPEC-INCONSISTENT / AMBIGUOUS rows (5 — flagged, not resolved, never inferred):</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C26" s="31" t="inlineStr">
         <is>
           <t>Capability</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D26" s="31" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Full Dual Matrix</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Parts Technician</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Send to Portal</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>LESS</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Spec inconsistent/ambiguous — §3/§4 grant Send to Portal to ANY Full-View role (incl. Parts Technician), so a bare-Full-View reading would make this staging state NOT per spec; BUT Open Q6 conditions it on 'can approve a WOL', which Parts Technician lacks (no WOL Create&amp;Edit) -&gt; then per spec. Flagged, not resolved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>§3/§4 bare Full-View would grant; Open Q6 'can approve a WOL' would withhold (no WOL Create&amp;Edit). Flagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Full Dual Matrix</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Office User</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Send to Portal</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>LESS</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Spec inconsistent/ambiguous — §3/§4 grant Send to Portal to ANY Full-View role (incl. Office User), so a bare-Full-View reading would make this staging state NOT per spec; BUT Open Q6 conditions it on 'can approve a WOL', which Office User lacks (no WOL Create&amp;Edit) -&gt; then per spec. Flagged, not resolved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Sales Representative</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Send to Portal</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Spec inconsistent/ambiguous — §3/§4 Full-View would grant; Open Q6 'can approve a WOL' would withhold (Sales Rep lacks WOL Create&amp;Edit). Both envs hidden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr"/>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>§3/§4 bare Full-View would grant; Open Q6 'can approve a WOL' would withhold (no WOL Create&amp;Edit). Flagged.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>SPEC-SILENT capabilities in this deliverable (conformance NOT inferred): Decline line / Set Line Status (11 rows); Issue Credit (bundled in the 'Finance' cap); remove-a-WO-part as a discrete atom (spec only covers return=no gate, move=WOL C&amp;E, remove-lines=WOL Delete).</t>
-        </is>
-      </c>
-    </row>
+          <t>Full Dual Matrix</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Send to Portal</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Same §3/§4-vs-Open-Q6 ambiguity; both envs hidden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Full Dual Matrix</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Decline line</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>MATCH (both hidden)</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>§1b grants Technician WOL Create &amp; Edit ('authorize lines' covers declining) but §4 Tech View blocks only Approve and never mentions Decline — Tech-View treatment of Decline unresolvable. [Re-derived 2026-07-16 — was blanket 'spec silent'.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Pass-11 LIVE (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Service Manager</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Finance — Reverse Invoice component</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>MORE (bundle)</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Matrix (SM WO V/E/D) + 28-Jun rule (Reverse = WO Delete) say SM CAN reverse; migration Behavior-Changes table says SM 'Loses Invoicing Delete (cannot reverse)'; staging shows New Payment + Issue Credit only (no Reverse) — matches the migration table, contradicts the matrix. [Flagged 2026-07-16.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>SPEC-SILENT components (conformance NOT inferred): Issue Credit (inside the 'Finance' rows — no issuance gate anywhere in the spec); remove-a-WO-part as a discrete atom (spec covers only: return = no gate, move = WOL C&amp;E, remove-lines = WOL Delete). 'Decline line' is NO LONGER spec-silent — §1b 'authorize lines' addresses it (re-derived 2026-07-16).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>RE-AUDIT ROOT CAUSE (2026-07-16): the earlier extract (spec-conformance/spec-v2-permission-intent.md §B) carried the PRE-7/14 Office column (Work Orders = V, Part Sales = V; WO-Lines slip '—'), so the generator treated Office as holding WO View -&gt; Office WO Notes + Part Return were wrongly 'per spec'. The generator also blanket-labeled Decline spec-silent, reused the WO-C&amp;E grant set for the New-WO Create-Customer/Asset reason text, missed the SM Reverse migration-table contradiction, and cited Manage AP/AR ahead of the operative Reports gate for the aging-reports surface. All corrected in place; truth table = spec-conformance/spec-truth-table.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1569,7 +1757,7 @@
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>PASS-12 (2026-07-16) — CLOSED the last two residuals: (1) Approve/Decline line BOTH envs, all roles; (2) Send-to-Terminal prod org-gate fully characterized. OBSERVED-LIVE only; never inferred (Rules 10/12). ZERO unexplained NOT-VERIFIED remain.</t>
+          <t>PASS-12 (2026-07-16) — CLOSED the last two residuals: (1) Approve/Decline line BOTH envs, all roles; (2) Send-to-Terminal prod org-gate fully characterized. OBSERVED-LIVE only; never inferred (Rules 10/12). ZERO unexplained unverified cells remain.</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1843,7 @@
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Admin (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec grants to Admin (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
@@ -1697,7 +1885,7 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Service Manager (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
@@ -1739,7 +1927,7 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
@@ -1781,7 +1969,7 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Service Advisor (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -1823,7 +2011,7 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Foreman (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -1865,7 +2053,7 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Technician (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)). NOTE (Technician): §4 Tech View blocks only Approve and never mentions Decline while §1b grants Technician WOL Create &amp; Edit — whether Tech View also withholds Decline is spec-ambiguous; both envs hide it (see the Full Dual Matrix Technician 'Decline line' row, classed Spec inconsistent/ambiguous).</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -1907,7 +2095,7 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>Per spec — expected grant (Parts Manager holds the gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec — expected grant (Parts Manager holds the gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
@@ -1949,7 +2137,7 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -1991,7 +2179,7 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Office User (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec does not grant to Office User (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="H13" s="14" t="inlineStr">
@@ -2033,7 +2221,7 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
@@ -2075,7 +2263,7 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
@@ -2154,7 +2342,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FINAL STATUS: All role-permission capability cells for the priority + broad set are OBSERVED-LIVE across both envs. The only non-role cell is Send-to-Terminal, now a FULLY-CHARACTERIZED org-device-config verdict (not an unexplained NOT-VERIFIED).</t>
+          <t>FINAL STATUS: All role-permission capability cells for the priority + broad set are OBSERVED-LIVE across both envs. The only non-role cell is Send-to-Terminal, now a FULLY-CHARACTERIZED org-device-config verdict (not an unexplained unverified gap).</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2459,7 @@
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Admin (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+          <t>Per spec (matches) — spec grants to Admin: Reports = ON in the matrix (gate: AR/AP AGING reports follow the Reports toggle (§2a: 'a user with Reports ON sees all reports, including AR/AP aging, regardless of Manage AP/AR'; all-or-nothing, decoupled 3 Jul) — NOT Manage AP/AR. Manage AP/AR (§5b) separately gates the Customer/Vendor Unpaid-Invoices/Payments/Credits tabs + sensitive fields; in the matrix the SAME six roles hold both (Admin/Service Manager/Senior Service Advisor/Parts Manager/Office/Sales Rep). Citation corrected 2026-07-16 to lead with the operative Reports gate).</t>
         </is>
       </c>
       <c r="H4" s="14" t="inlineStr">
@@ -2313,7 +2501,7 @@
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Office User (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+          <t>Per spec (matches) — spec grants to Office User: Reports = ON in the matrix (gate: AR/AP AGING reports follow the Reports toggle (§2a: 'a user with Reports ON sees all reports, including AR/AP aging, regardless of Manage AP/AR'; all-or-nothing, decoupled 3 Jul) — NOT Manage AP/AR. Manage AP/AR (§5b) separately gates the Customer/Vendor Unpaid-Invoices/Payments/Credits tabs + sensitive fields; in the matrix the SAME six roles hold both (Admin/Service Manager/Senior Service Advisor/Parts Manager/Office/Sales Rep). Citation corrected 2026-07-16 to lead with the operative Reports gate).</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
@@ -2355,7 +2543,7 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>Per spec — expected grant (Service Manager holds the gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+          <t>Per spec — expected grant (Service Manager holds Reports = ON in the matrix; gate: AR/AP AGING reports follow the Reports toggle (§2a: 'a user with Reports ON sees all reports, including AR/AP aging, regardless of Manage AP/AR'; all-or-nothing, decoupled 3 Jul) — NOT Manage AP/AR. Manage AP/AR (§5b) separately gates the Customer/Vendor Unpaid-Invoices/Payments/Credits tabs + sensitive fields; in the matrix the SAME six roles hold both (Admin/Service Manager/Senior Service Advisor/Parts Manager/Office/Sales Rep). Citation corrected 2026-07-16 to lead with the operative Reports gate).</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
@@ -2397,7 +2585,7 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>Per spec — expected grant (Parts Manager holds the gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+          <t>Per spec — expected grant (Parts Manager holds Reports = ON in the matrix; gate: AR/AP AGING reports follow the Reports toggle (§2a: 'a user with Reports ON sees all reports, including AR/AP aging, regardless of Manage AP/AR'; all-or-nothing, decoupled 3 Jul) — NOT Manage AP/AR. Manage AP/AR (§5b) separately gates the Customer/Vendor Unpaid-Invoices/Payments/Credits tabs + sensitive fields; in the matrix the SAME six roles hold both (Admin/Service Manager/Senior Service Advisor/Parts Manager/Office/Sales Rep). Citation corrected 2026-07-16 to lead with the operative Reports gate).</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
@@ -2439,7 +2627,7 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>Per spec — expected grant (Sales Representative holds the gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+          <t>Per spec — expected grant (Sales Representative holds Reports = ON in the matrix; gate: AR/AP AGING reports follow the Reports toggle (§2a: 'a user with Reports ON sees all reports, including AR/AP aging, regardless of Manage AP/AR'; all-or-nothing, decoupled 3 Jul) — NOT Manage AP/AR. Manage AP/AR (§5b) separately gates the Customer/Vendor Unpaid-Invoices/Payments/Credits tabs + sensitive fields; in the matrix the SAME six roles hold both (Admin/Service Manager/Senior Service Advisor/Parts Manager/Office/Sales Rep). Citation corrected 2026-07-16 to lead with the operative Reports gate).</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -2481,7 +2669,7 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>DEVIATION — spec grants to Senior Service Advisor (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)) but staging hides it (both envs hidden).</t>
+          <t>DEVIATION — spec grants the AR/AP aging reports to Senior Service Advisor (Reports = ON in the matrix — §2a: aging reports follow Reports; Manage AP/AR is ALSO ON, §5b) but staging hides them (both envs hidden — a MATCH row that disagrees with the spec). Staging does not implement the spec grant for Senior Service Advisor. (Re-verified from the matrix 2026-07-16; citation corrected to lead with the operative Reports gate.)</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -2523,7 +2711,7 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Service Advisor (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+          <t>Per spec (matches) — spec does not grant to Service Advisor: Reports = OFF in the matrix (gate: AR/AP AGING reports follow the Reports toggle (§2a: 'a user with Reports ON sees all reports, including AR/AP aging, regardless of Manage AP/AR'; all-or-nothing, decoupled 3 Jul) — NOT Manage AP/AR. Manage AP/AR (§5b) separately gates the Customer/Vendor Unpaid-Invoices/Payments/Credits tabs + sensitive fields; in the matrix the SAME six roles hold both (Admin/Service Manager/Senior Service Advisor/Parts Manager/Office/Sales Rep). Citation corrected 2026-07-16 to lead with the operative Reports gate).</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -2565,7 +2753,7 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Foreman (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+          <t>Per spec (matches) — spec does not grant to Foreman: Reports = OFF in the matrix (gate: AR/AP AGING reports follow the Reports toggle (§2a: 'a user with Reports ON sees all reports, including AR/AP aging, regardless of Manage AP/AR'; all-or-nothing, decoupled 3 Jul) — NOT Manage AP/AR. Manage AP/AR (§5b) separately gates the Customer/Vendor Unpaid-Invoices/Payments/Credits tabs + sensitive fields; in the matrix the SAME six roles hold both (Admin/Service Manager/Senior Service Advisor/Parts Manager/Office/Sales Rep). Citation corrected 2026-07-16 to lead with the operative Reports gate).</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
@@ -2607,7 +2795,7 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Technician (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+          <t>Per spec (matches) — spec does not grant to Technician: Reports = OFF in the matrix (gate: AR/AP AGING reports follow the Reports toggle (§2a: 'a user with Reports ON sees all reports, including AR/AP aging, regardless of Manage AP/AR'; all-or-nothing, decoupled 3 Jul) — NOT Manage AP/AR. Manage AP/AR (§5b) separately gates the Customer/Vendor Unpaid-Invoices/Payments/Credits tabs + sensitive fields; in the matrix the SAME six roles hold both (Admin/Service Manager/Senior Service Advisor/Parts Manager/Office/Sales Rep). Citation corrected 2026-07-16 to lead with the operative Reports gate).</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -2649,7 +2837,7 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+          <t>Per spec (matches) — spec does not grant to Parts Technician: Reports = OFF in the matrix (gate: AR/AP AGING reports follow the Reports toggle (§2a: 'a user with Reports ON sees all reports, including AR/AP aging, regardless of Manage AP/AR'; all-or-nothing, decoupled 3 Jul) — NOT Manage AP/AR. Manage AP/AR (§5b) separately gates the Customer/Vendor Unpaid-Invoices/Payments/Credits tabs + sensitive fields; in the matrix the SAME six roles hold both (Admin/Service Manager/Senior Service Advisor/Parts Manager/Office/Sales Rep). Citation corrected 2026-07-16 to lead with the operative Reports gate).</t>
         </is>
       </c>
       <c r="H13" s="14" t="inlineStr">
@@ -2691,7 +2879,7 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Manage AP/AR toggle (tabs/fields, §5b) / AR-AP aging = Reports toggle (all-or-nothing, decoupled 3 Jul)).</t>
+          <t>Per spec (matches) — spec does not grant to Time Clock User: Reports = OFF in the matrix (gate: AR/AP AGING reports follow the Reports toggle (§2a: 'a user with Reports ON sees all reports, including AR/AP aging, regardless of Manage AP/AR'; all-or-nothing, decoupled 3 Jul) — NOT Manage AP/AR. Manage AP/AR (§5b) separately gates the Customer/Vendor Unpaid-Invoices/Payments/Credits tabs + sensitive fields; in the matrix the SAME six roles hold both (Admin/Service Manager/Senior Service Advisor/Parts Manager/Office/Sales Rep). Citation corrected 2026-07-16 to lead with the operative Reports gate).</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
@@ -3111,7 +3299,7 @@
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>Per spec — expected grant (Office User holds the gate: NO permission gate — return a WO part is available to everyone (29 Jun; §1a)).</t>
+          <t>DEVIATION (reachability) — the Return control itself has NO permission gate (spec §1a: 'Returning a part from a WOL does not require a permission'; 29 Jun: 'Everyone has access to Return a part from a WO'), BUT §1a adds 'In practice, the user will need WO view so they can see the point', and the current matrix (14 Jul Office update) gives Office User NO Work Orders access ('—'). So per the current spec Office User cannot reach a WO part to return; staging shows it (STAGING-MORE) = beyond the current spec. Same root cause as the Office WO-visibility deviation (see the Office User WO Notes row). [Corrected 2026-07-16 — previously wrongly 'Per spec — expected grant'.]</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
@@ -3195,7 +3383,7 @@
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Admin (gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+          <t>Per spec (matches) — New Payment = Invoicing -&gt; Create &amp; Edit (§1i, Open Q4), which Admin holds; Reverse Invoice = Work Orders -&gt; Delete (28 Jun), which Admin holds (Reverse shown per spec). Issue Credit = SPEC SILENT (no issuance gate anywhere in the spec — only Credits-TAB visibility, §5b).</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
@@ -3237,7 +3425,7 @@
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>Per spec — expected grant (Service Manager holds the gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+          <t>Spec inconsistent — on the Reverse component (the New Payment grant itself is per spec): New Payment = Invoicing -&gt; Create &amp; Edit (§1i), which Service Manager holds (expected grant, STAGING-MORE). Reverse Invoice = Work Orders -&gt; Delete (28 Jun) and the matrix gives Service Manager WO V/E/D (would GRANT Reverse), BUT the migration 'Behavior Changes' table says Service Manager 'Loses Invoicing Delete (cannot reverse)'. Staging shows only New Payment + Issue Credit (no Reverse) — matching the migration table and contradicting the matrix + 28-Jun gate. Flagged, not resolved. [Corrected 2026-07-16 — previously 'Per spec — expected grant' with no Reverse flag.] Issue Credit = SPEC SILENT (no issuance gate anywhere in the spec — only Credits-TAB visibility, §5b).</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
@@ -3279,7 +3467,7 @@
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>Per spec — expected grant (Parts Manager holds the gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+          <t>Per spec — expected grant (Parts Manager holds Invoicing -&gt; Create &amp; Edit, §1i = New Payment); Reverse correctly absent (Parts Manager has no Work Orders -&gt; Delete; Reverse = WO Delete, 28 Jun). Issue Credit = SPEC SILENT (no issuance gate anywhere in the spec — only Credits-TAB visibility, §5b).</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
@@ -3321,7 +3509,7 @@
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>Per spec — expected grant (Parts Technician holds the gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+          <t>Per spec — expected grant (Parts Technician holds Invoicing -&gt; Create &amp; Edit, §1i = New Payment); Reverse correctly absent (no Work Orders -&gt; Delete; Reverse = WO Delete, 28 Jun). Issue Credit = SPEC SILENT (no issuance gate anywhere in the spec — only Credits-TAB visibility, §5b).</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
@@ -3363,7 +3551,7 @@
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>Per spec — expected grant (Foreman holds the gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+          <t>Per spec — expected grant (Foreman holds Invoicing -&gt; Create &amp; Edit, §1i = New Payment); Reverse correctly absent (no Work Orders -&gt; Delete; Reverse = WO Delete, 28 Jun). Issue Credit = SPEC SILENT (no issuance gate anywhere in the spec — only Credits-TAB visibility, §5b).</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
@@ -3405,7 +3593,7 @@
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>Per spec — expected grant (Office User holds the gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+          <t>Per spec — expected grant (Office User holds Invoicing -&gt; Create &amp; Edit — §1i; and the spec explicitly says Office users 'are expected to be able to make payments but not create invoices'); Reverse correctly absent (no Work Orders -&gt; Delete). NOTE (14-Jul Office update): the matrix removed ALL Work Orders access for Office User, so per the current spec this Finance surface is reached via Customers/Part Sales entry points (§1i View), not the work-order screen where it was observed — the Office WO-visibility delta is logged as the Office WO Notes / Part Return DEVIATIONs. Issue Credit = SPEC SILENT (no issuance gate anywhere in the spec — only Credits-TAB visibility, §5b).</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
@@ -3447,7 +3635,7 @@
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+          <t>Per spec (matches) — New Payment = Invoicing -&gt; Create &amp; Edit (§1i), which Senior Service Advisor holds; Reverse Invoice = Work Orders -&gt; Delete (28 Jun), which Senior Service Advisor holds (Reverse shown per spec; migration table confirms 'Invoicing FULL' expansion). Issue Credit = SPEC SILENT (no issuance gate anywhere in the spec — only Credits-TAB visibility, §5b).</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
@@ -3489,7 +3677,7 @@
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Service Advisor (gate: Invoicing -&gt; Create &amp; Edit for New Payment (§1i); Reverse=WO Delete (28 Jun); Issue Credit=SPEC SILENT). (Reverse=WO Delete; Issue Credit is SPEC SILENT.)</t>
+          <t>Per spec (matches) — New Payment = Invoicing -&gt; Create &amp; Edit (§1i), which Service Advisor holds; Reverse Invoice = Work Orders -&gt; Delete (28 Jun), which Service Advisor does NOT hold (WO = V/E) — staging correctly hides Reverse (prod SA-Limited-View showing Reverse is the legacy model). Issue Credit = SPEC SILENT (no issuance gate anywhere in the spec — only Credits-TAB visibility, §5b).</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
@@ -4465,7 +4653,7 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+          <t>Per spec (matches) — spec grants to Admin (gate: Work Order Lines -&gt; Create &amp; Edit — spec §1b 'authorize lines' covers declining a pending line (corrected 2026-07-16: previously mislabeled 'spec silent')).</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
@@ -5173,7 +5361,7 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: Work Order Lines -&gt; Create &amp; Edit — spec §1b 'authorize lines' covers declining a pending line (corrected 2026-07-16: previously mislabeled 'spec silent')).</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
@@ -5881,7 +6069,7 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Work Order Lines -&gt; Create &amp; Edit — spec §1b 'authorize lines' covers declining a pending line (corrected 2026-07-16: previously mislabeled 'spec silent')).</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
@@ -6589,7 +6777,7 @@
       </c>
       <c r="H65" s="14" t="inlineStr">
         <is>
-          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Work Order Lines -&gt; Create &amp; Edit — spec §1b 'authorize lines' covers declining a pending line (corrected 2026-07-16: previously mislabeled 'spec silent')).</t>
         </is>
       </c>
       <c r="I65" s="14" t="inlineStr">
@@ -7297,7 +7485,7 @@
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
-          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Work Order Lines -&gt; Create &amp; Edit — spec §1b 'authorize lines' covers declining a pending line (corrected 2026-07-16: previously mislabeled 'spec silent')).</t>
         </is>
       </c>
       <c r="I81" s="14" t="inlineStr">
@@ -8009,7 +8197,7 @@
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
-          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+          <t>Spec inconsistent/ambiguous — §1b grants Technician WO Lines Create &amp; Edit, whose scope includes 'authorize lines' (declining is part of authorizing), but the §4 Tech View restrictions block only Approve ('Cannot approve lines' / 'No approve action') and never mention Decline. Whether Tech View also withholds Decline is not resolvable from the spec; both envs hide it for Technician. Flagged, not inferred. [Corrected 2026-07-16 — previously blanket 'spec silent'.]</t>
         </is>
       </c>
       <c r="I97" s="14" t="inlineStr">
@@ -8717,7 +8905,7 @@
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
-          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+          <t>Per spec — expected grant (Parts Manager holds the gate: Work Order Lines -&gt; Create &amp; Edit — spec §1b 'authorize lines' covers declining a pending line (corrected 2026-07-16: previously mislabeled 'spec silent')).</t>
         </is>
       </c>
       <c r="I113" s="14" t="inlineStr">
@@ -9425,7 +9613,7 @@
       </c>
       <c r="H129" s="14" t="inlineStr">
         <is>
-          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Work Order Lines -&gt; Create &amp; Edit — spec §1b 'authorize lines' covers declining a pending line (corrected 2026-07-16: previously mislabeled 'spec silent'); Parts Technician has no WOL Create &amp; Edit in the matrix).</t>
         </is>
       </c>
       <c r="I129" s="14" t="inlineStr">
@@ -10133,7 +10321,7 @@
       </c>
       <c r="H145" s="14" t="inlineStr">
         <is>
-          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Work Order Lines -&gt; Create &amp; Edit — spec §1b 'authorize lines' covers declining a pending line (corrected 2026-07-16: previously mislabeled 'spec silent'); Sales Representative has no WOL Create &amp; Edit in the matrix).</t>
         </is>
       </c>
       <c r="I145" s="14" t="inlineStr">
@@ -10309,7 +10497,7 @@
       <c r="G149" s="5" t="inlineStr"/>
       <c r="H149" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Office User (gate: See Financial Data toggle (spec §5a)).</t>
+          <t>Per spec (matches) — spec grants to Office User (gate: See Financial Data toggle (spec §5a)). NOTE (14-Jul 'Updated Office Role definition'): the matrix now gives Office User NO Work Orders access ('—'), so per the current spec this surface would be reached via Customers/Part Sales entry points rather than the work-order screen where it was observed; the Office WO-visibility delta itself is logged as the Office WO Notes / Part Return DEVIATIONs (this row's own gate — which Office User holds — is unchanged).</t>
         </is>
       </c>
       <c r="I149" s="14" t="inlineStr">
@@ -10352,7 +10540,7 @@
       <c r="G150" s="5" t="inlineStr"/>
       <c r="H150" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Office User (gate: Invoicing -&gt; View; SFD gates Invoicing (spec §1i/§5a)).</t>
+          <t>Per spec (matches) — spec grants to Office User (gate: Invoicing -&gt; View; SFD gates Invoicing (spec §1i/§5a)). NOTE (14-Jul 'Updated Office Role definition'): the matrix now gives Office User NO Work Orders access ('—'), so per the current spec this surface would be reached via Customers/Part Sales entry points rather than the work-order screen where it was observed; the Office WO-visibility delta itself is logged as the Office WO Notes / Part Return DEVIATIONs (this row's own gate — which Office User holds — is unchanged).</t>
         </is>
       </c>
       <c r="I150" s="14" t="inlineStr">
@@ -10395,7 +10583,7 @@
       <c r="G151" s="5" t="inlineStr"/>
       <c r="H151" s="14" t="inlineStr">
         <is>
-          <t>Per spec — expected grant (Office User holds the gate: Invoicing -&gt; Create &amp; Edit (spec §1i, Open Q4)).</t>
+          <t>Per spec — expected grant (Office User holds the gate: Invoicing -&gt; Create &amp; Edit (spec §1i, Open Q4)). NOTE (14-Jul 'Updated Office Role definition'): the matrix now gives Office User NO Work Orders access ('—'), so per the current spec this surface would be reached via Customers/Part Sales entry points rather than the work-order screen where it was observed; the Office WO-visibility delta itself is logged as the Office WO Notes / Part Return DEVIATIONs (this row's own gate — which Office User holds — is unchanged).</t>
         </is>
       </c>
       <c r="I151" s="14" t="inlineStr">
@@ -10571,7 +10759,7 @@
       <c r="G155" s="5" t="inlineStr"/>
       <c r="H155" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Office User (gate: Work Orders -&gt; View (create/edit any note) (spec §1a)).</t>
+          <t>DEVIATION — the current spec (14 Jul 'Updated Office Role definition') gives Office User NO Work Orders access at all (Permission Matrix: Work Orders = '—'), so the Notes tab (gated by Work Orders -&gt; View, spec §1a) should NOT be reachable for Office User; BOTH envs show it (both SHOWN — a MATCH row that disagrees with the spec). Staging does not implement the 14-Jul Office reduction. (Spec wrinkle also flagged: the matrix WO Lines row still shows 'V' for Office although §1b/matrix-note say WOL View is inherited from Work Orders View.) [Corrected 2026-07-16 — previously wrongly 'Per spec (matches)': the earlier extract carried the pre-7/14 Office column (Work Orders = V).]</t>
         </is>
       </c>
       <c r="I155" s="14" t="inlineStr">
@@ -10614,7 +10802,7 @@
       <c r="G156" s="5" t="inlineStr"/>
       <c r="H156" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Office User (gate: Timesheets -&gt; View (spec §1j); clock-in/out + My Timesheets always on).</t>
+          <t>Per spec (matches) — spec grants to Office User (gate: Timesheets -&gt; View (spec §1j); clock-in/out + My Timesheets always on). NOTE (14-Jul 'Updated Office Role definition'): the matrix now gives Office User NO Work Orders access ('—'), so per the current spec this surface would be reached via Customers/Part Sales entry points rather than the work-order screen where it was observed; the Office WO-visibility delta itself is logged as the Office WO Notes / Part Return DEVIATIONs (this row's own gate — which Office User holds — is unchanged).</t>
         </is>
       </c>
       <c r="I156" s="14" t="inlineStr">
@@ -10841,7 +11029,7 @@
       </c>
       <c r="H161" s="14" t="inlineStr">
         <is>
-          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+          <t>Per spec (matches) — spec does not grant to Office User (gate: Work Order Lines -&gt; Create &amp; Edit — spec §1b 'authorize lines' covers declining a pending line (corrected 2026-07-16: previously mislabeled 'spec silent'); Office User has no WOL Create &amp; Edit in the matrix).</t>
         </is>
       </c>
       <c r="I161" s="14" t="inlineStr">
@@ -11553,7 +11741,7 @@
       </c>
       <c r="H177" s="14" t="inlineStr">
         <is>
-          <t>Spec silent — Decline/Set Line Status not addressed (spec only says 'authorize lines'). No conformance inferred.</t>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Work Order Lines -&gt; Create &amp; Edit — spec §1b 'authorize lines' covers declining a pending line (corrected 2026-07-16: previously mislabeled 'spec silent'); Time Clock User has no WOL Create &amp; Edit in the matrix).</t>
         </is>
       </c>
       <c r="I177" s="14" t="inlineStr">
@@ -15673,7 +15861,7 @@
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Office User (gate: Customer Management -&gt; Create &amp; Edit (create customer in New-WO flow, 01 Jun; behind WO Create&amp;Edit)).</t>
+          <t>Per spec (matches) — the control is correctly absent, but the REASON is corrected (2026-07-16): Office User DOES hold Customer Management -&gt; Create &amp; Edit in the matrix (Customers row), so the earlier 'spec does not grant Customer Management C&amp;E' reading was WRONG. The Add control is unreachable per spec because Office User lacks Work Orders -&gt; Create &amp; Edit — indeed the 14-Jul update removed ALL Work Orders access for Office User, so the New Work Order dialog itself never opens. Compound gate: Work Orders C&amp;E (reach the New-WO dialog) + Customer Management C&amp;E (Create Customer in the New-WO flow (01 Jun change log; §1d Edit)).</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
@@ -15740,7 +15928,7 @@
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Office User (gate: Customer Management -&gt; Create &amp; Edit (manage vehicles; behind WO Create&amp;Edit)).</t>
+          <t>Per spec (matches) — the control is correctly absent, but the REASON is corrected (2026-07-16): Office User DOES hold Customer Management -&gt; Create &amp; Edit in the matrix (Customers row), so the earlier 'spec does not grant Customer Management C&amp;E' reading was WRONG. The Add control is unreachable per spec because Office User lacks Work Orders -&gt; Create &amp; Edit — indeed the 14-Jul update removed ALL Work Orders access for Office User, so the New Work Order dialog itself never opens. Compound gate: Work Orders C&amp;E (reach the New-WO dialog) + Customer Management C&amp;E (Create Asset ('manage vehicles', §1d Edit)).</t>
         </is>
       </c>
       <c r="M23" s="14" t="inlineStr">
@@ -15874,7 +16062,7 @@
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Customer Management -&gt; Create &amp; Edit (create customer in New-WO flow, 01 Jun; behind WO Create&amp;Edit)).</t>
+          <t>Per spec (matches) — the control is correctly absent, but the REASON is corrected (2026-07-16): Parts Technician DOES hold Customer Management -&gt; Create &amp; Edit in the matrix (Customers row), so the earlier 'spec does not grant Customer Management C&amp;E' reading was WRONG. The Add control is unreachable per spec because Parts Technician lacks Work Orders -&gt; Create &amp; Edit, so the New Work Order dialog itself never opens. Compound gate: Work Orders C&amp;E (reach the New-WO dialog) + Customer Management C&amp;E (Create Customer in the New-WO flow (01 Jun change log; §1d Edit)).</t>
         </is>
       </c>
       <c r="M25" s="14" t="inlineStr">
@@ -15941,7 +16129,7 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Customer Management -&gt; Create &amp; Edit (manage vehicles; behind WO Create&amp;Edit)).</t>
+          <t>Per spec (matches) — the control is correctly absent, but the REASON is corrected (2026-07-16): Parts Technician DOES hold Customer Management -&gt; Create &amp; Edit in the matrix (Customers row), so the earlier 'spec does not grant Customer Management C&amp;E' reading was WRONG. The Add control is unreachable per spec because Parts Technician lacks Work Orders -&gt; Create &amp; Edit, so the New Work Order dialog itself never opens. Compound gate: Work Orders C&amp;E (reach the New-WO dialog) + Customer Management C&amp;E (Create Asset ('manage vehicles', §1d Edit)).</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
@@ -16075,7 +16263,7 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Customer Management -&gt; Create &amp; Edit (create customer in New-WO flow, 01 Jun; behind WO Create&amp;Edit)).</t>
+          <t>Per spec (matches) — the control is correctly absent, but the REASON is corrected (2026-07-16): Sales Representative DOES hold Customer Management -&gt; Create &amp; Edit in the matrix (Customers row), so the earlier 'spec does not grant Customer Management C&amp;E' reading was WRONG. The Add control is unreachable per spec because Sales Representative lacks Work Orders -&gt; Create &amp; Edit, so the New Work Order dialog itself never opens. Compound gate: Work Orders C&amp;E (reach the New-WO dialog) + Customer Management C&amp;E (Create Customer in the New-WO flow (01 Jun change log; §1d Edit)).</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
@@ -16142,7 +16330,7 @@
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Customer Management -&gt; Create &amp; Edit (manage vehicles; behind WO Create&amp;Edit)).</t>
+          <t>Per spec (matches) — the control is correctly absent, but the REASON is corrected (2026-07-16): Sales Representative DOES hold Customer Management -&gt; Create &amp; Edit in the matrix (Customers row), so the earlier 'spec does not grant Customer Management C&amp;E' reading was WRONG. The Add control is unreachable per spec because Sales Representative lacks Work Orders -&gt; Create &amp; Edit, so the New Work Order dialog itself never opens. Compound gate: Work Orders C&amp;E (reach the New-WO dialog) + Customer Management C&amp;E (Create Asset ('manage vehicles', §1d Edit)).</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr">
@@ -16662,7 +16850,7 @@
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Admin (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec grants to Admin (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="G4" s="14" t="inlineStr">
@@ -16699,7 +16887,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Service Manager (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec grants to Service Manager (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -16736,7 +16924,7 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec grants to Senior Service Advisor (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -16773,7 +16961,7 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Service Advisor (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec grants to Service Advisor (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -16810,7 +16998,7 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec grants to Foreman (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec grants to Foreman (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -16847,7 +17035,7 @@
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Technician (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec does not grant to Technician (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)). NOTE (Technician): §4 Tech View blocks only Approve and never mentions Decline while §1b grants Technician WOL Create &amp; Edit — whether Tech View also withholds Decline is spec-ambiguous; both envs hide it (see the Full Dual Matrix Technician 'Decline line' row, classed Spec inconsistent/ambiguous).</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -16884,7 +17072,7 @@
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Per spec — expected grant (Parts Manager holds the gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec — expected grant (Parts Manager holds the gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -16921,7 +17109,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec does not grant to Parts Technician (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -16958,7 +17146,7 @@
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Office User (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec does not grant to Office User (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -16995,7 +17183,7 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec does not grant to Sales Representative (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -17032,7 +17220,7 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Approve = WOL Create&amp;Edit + Full View; Decline = SPEC SILENT). (Decline component is SPEC SILENT.)</t>
+          <t>Per spec (matches) — spec does not grant to Time Clock User (gate: Approve = WOL Create &amp; Edit + Full View (§1b 'authorize lines' + §4 Tech-View approve-block / Open Q6); Decline = WOL Create &amp; Edit (§1b 'authorize lines' — NOT spec-silent; corrected 2026-07-16)).</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
